--- a/reports/screener_2026-08-30.xlsx
+++ b/reports/screener_2026-08-30.xlsx
@@ -1278,10 +1278,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="CJ2" t="n">
-        <v>5.851607493390991</v>
+        <v>5.851607492840716</v>
       </c>
       <c r="CK2" t="n">
-        <v>10.85473190024029</v>
+        <v>10.85473189921953</v>
       </c>
       <c r="CL2" t="n">
         <v>41.59696831847682</v>
@@ -1290,7 +1290,7 @@
         <v>27.90166392450355</v>
       </c>
       <c r="CN2" t="n">
-        <v>71.91590901746441</v>
+        <v>71.91590901512991</v>
       </c>
       <c r="CO2" t="n">
         <v>19.76753935237404</v>
@@ -1628,10 +1628,10 @@
         <v>13.46000003814697</v>
       </c>
       <c r="CJ3" t="n">
-        <v>14.84732057000014</v>
+        <v>14.8473205387898</v>
       </c>
       <c r="CK3" t="n">
-        <v>27.54177965735026</v>
+        <v>27.54177959945507</v>
       </c>
       <c r="CL3" t="n">
         <v>38.93995644223742</v>
@@ -1640,13 +1640,13 @@
         <v>23.51205793312256</v>
       </c>
       <c r="CN3" t="n">
-        <v>75.5448285957473</v>
+        <v>75.54482865353735</v>
       </c>
       <c r="CO3" t="n">
-        <v>48.52515937946949</v>
+        <v>48.52515940240973</v>
       </c>
       <c r="CP3" t="n">
-        <v>26.80868494893448</v>
+        <v>26.80868504522712</v>
       </c>
       <c r="CQ3" t="n">
         <v>8.920136085713818</v>
@@ -1978,10 +1978,10 @@
         <v>24.61000061035156</v>
       </c>
       <c r="CJ4" t="n">
-        <v>16.31411912109865</v>
+        <v>16.31411911267199</v>
       </c>
       <c r="CK4" t="n">
-        <v>30.26269096963799</v>
+        <v>30.26269095400653</v>
       </c>
       <c r="CL4" t="n">
         <v>72.30210822331667</v>
@@ -1990,19 +1990,19 @@
         <v>52.41049602817493</v>
       </c>
       <c r="CN4" t="n">
-        <v>127.9950261271193</v>
+        <v>127.9950261297231</v>
       </c>
       <c r="CO4" t="n">
-        <v>26.12261083743122</v>
+        <v>26.12261083863716</v>
       </c>
       <c r="CP4" t="n">
-        <v>63.19894114730609</v>
+        <v>63.19894116538502</v>
       </c>
       <c r="CQ4" t="n">
         <v>42.85100954601229</v>
       </c>
       <c r="CR4" t="n">
-        <v>47.8579761253132</v>
+        <v>47.8579761259221</v>
       </c>
       <c r="CS4" t="n">
         <v>47.63075278709361</v>
@@ -2023,7 +2023,7 @@
         <v>74.18803919229917</v>
       </c>
       <c r="CY4" t="n">
-        <v>94.46556252901097</v>
+        <v>94.46556253148518</v>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
@@ -2336,10 +2336,10 @@
         <v>4.119999885559082</v>
       </c>
       <c r="CJ5" t="n">
-        <v>3.742641514200839</v>
+        <v>3.742641517861567</v>
       </c>
       <c r="CK5" t="n">
-        <v>6.942600008842556</v>
+        <v>6.942600015633207</v>
       </c>
       <c r="CL5" t="n">
         <v>12.63657372306894</v>
@@ -2348,19 +2348,19 @@
         <v>8.512687176725057</v>
       </c>
       <c r="CN5" t="n">
-        <v>24.29899389621988</v>
+        <v>24.2989938935693</v>
       </c>
       <c r="CO5" t="n">
-        <v>11.19276558851729</v>
+        <v>11.19276558700668</v>
       </c>
       <c r="CP5" t="n">
-        <v>10.1975051773985</v>
+        <v>10.19750516827538</v>
       </c>
       <c r="CQ5" t="n">
         <v>5.258139118319559</v>
       </c>
       <c r="CR5" t="n">
-        <v>8.354701758153251</v>
+        <v>8.354701758127199</v>
       </c>
       <c r="CS5" t="n">
         <v>8.512687176725057</v>
@@ -2381,7 +2381,7 @@
         <v>85.95676388017426</v>
       </c>
       <c r="CY5" t="n">
-        <v>102.784028888863</v>
+        <v>102.7840288882306</v>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
@@ -2696,10 +2696,10 @@
         <v>4.5</v>
       </c>
       <c r="CJ6" t="n">
-        <v>3.282970782701641</v>
+        <v>3.282970770769473</v>
       </c>
       <c r="CK6" t="n">
-        <v>6.089910801911545</v>
+        <v>6.089910779777372</v>
       </c>
       <c r="CL6" t="n">
         <v>12.96195652173913</v>
@@ -2708,7 +2708,7 @@
         <v>8.728772626887835</v>
       </c>
       <c r="CN6" t="n">
-        <v>24.66556325170065</v>
+        <v>24.66556321538536</v>
       </c>
       <c r="CO6" t="n">
         <v>11.57513776217851</v>
@@ -2720,7 +2720,7 @@
         <v>5.383571029035719</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.60598121645608</v>
+        <v>11.60598120810615</v>
       </c>
       <c r="CS6" t="n">
         <v>11.57513776217851</v>
@@ -2741,7 +2741,7 @@
         <v>131.5027552435702</v>
       </c>
       <c r="CY6" t="n">
-        <v>157.9106936990239</v>
+        <v>157.9106935134701</v>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>1.836517861131659</v>
       </c>
       <c r="DL6" t="n">
-        <v>-41.72317990102352</v>
+        <v>-41.72318362747433</v>
       </c>
       <c r="DM6" t="b">
         <v>1</v>
@@ -3046,10 +3046,10 @@
         <v>48.34000015258789</v>
       </c>
       <c r="CJ7" t="n">
-        <v>18.42191766034588</v>
+        <v>18.42191762293993</v>
       </c>
       <c r="CK7" t="n">
-        <v>34.1726572599416</v>
+        <v>34.17265719055356</v>
       </c>
       <c r="CL7" t="n">
         <v>74.65093263657221</v>
@@ -3058,23 +3058,23 @@
         <v>55.91472932652801</v>
       </c>
       <c r="CN7" t="n">
-        <v>99.83445496223254</v>
+        <v>99.83445502080644</v>
       </c>
       <c r="CO7" t="n">
-        <v>47.86104930791952</v>
+        <v>47.8610493169606</v>
       </c>
       <c r="CP7" t="n">
-        <v>58.90972725125358</v>
+        <v>58.90972732643655</v>
       </c>
       <c r="CQ7" t="inlineStr"/>
       <c r="CR7" t="n">
-        <v>43.77663921619479</v>
+        <v>43.77663919175657</v>
       </c>
       <c r="CS7" t="n">
-        <v>41.01685328393056</v>
+        <v>41.01685325375708</v>
       </c>
       <c r="CT7" t="n">
-        <v>36.91516795553751</v>
+        <v>36.91516792838138</v>
       </c>
       <c r="CU7" t="n">
         <v>4</v>
@@ -3086,10 +3086,10 @@
         <v>4.1</v>
       </c>
       <c r="CX7" t="n">
-        <v>-23.63432387461164</v>
+        <v>-23.63432393078898</v>
       </c>
       <c r="CY7" t="n">
-        <v>-9.440134302831183</v>
+        <v>-9.440134353386053</v>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
@@ -3404,10 +3404,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CJ8" t="n">
-        <v>6.403272793702906</v>
+        <v>6.403272799399811</v>
       </c>
       <c r="CK8" t="n">
-        <v>11.87807103231889</v>
+        <v>11.87807104288665</v>
       </c>
       <c r="CL8" t="n">
         <v>25.39987759130195</v>
@@ -3416,19 +3416,19 @@
         <v>18.63509665364473</v>
       </c>
       <c r="CN8" t="n">
-        <v>35.24419671738814</v>
+        <v>35.24419670813639</v>
       </c>
       <c r="CO8" t="n">
-        <v>12.29886961932753</v>
+        <v>12.29886961824623</v>
       </c>
       <c r="CP8" t="n">
-        <v>20.39435313533854</v>
+        <v>20.39435312340193</v>
       </c>
       <c r="CQ8" t="n">
         <v>18.40902666520164</v>
       </c>
       <c r="CR8" t="n">
-        <v>20.32278448778878</v>
+        <v>20.32278448611708</v>
       </c>
       <c r="CS8" t="n">
         <v>18.63509665364473</v>
@@ -3449,7 +3449,7 @@
         <v>6.825396127602112</v>
       </c>
       <c r="CY8" t="n">
-        <v>29.44448875595251</v>
+        <v>29.44448874530474</v>
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
@@ -3774,10 +3774,10 @@
         <v>42.70000076293945</v>
       </c>
       <c r="CJ9" t="n">
-        <v>125.1015275491483</v>
+        <v>125.1015269589179</v>
       </c>
       <c r="CK9" t="n">
-        <v>232.0633336036701</v>
+        <v>232.0633325087928</v>
       </c>
       <c r="CL9" t="n">
         <v>134.3883634463059</v>
@@ -3789,7 +3789,7 @@
         <v>304.2755398784284</v>
       </c>
       <c r="CO9" t="n">
-        <v>55.15675999999999</v>
+        <v>56.09255333333333</v>
       </c>
       <c r="CP9" t="n">
         <v>122.7244677509661</v>
@@ -3798,13 +3798,13 @@
         <v>54.40212095818906</v>
       </c>
       <c r="CR9" t="n">
-        <v>139.9216375662463</v>
+        <v>140.0386115222745</v>
       </c>
       <c r="CS9" t="n">
-        <v>123.9129976500572</v>
+        <v>123.912997354942</v>
       </c>
       <c r="CT9" t="n">
-        <v>111.5216978850515</v>
+        <v>111.5216976194478</v>
       </c>
       <c r="CU9" t="n">
         <v>8</v>
@@ -3816,10 +3816,10 @@
         <v>5.6</v>
       </c>
       <c r="CX9" t="n">
-        <v>161.1749318324237</v>
+        <v>161.174931210401</v>
       </c>
       <c r="CY9" t="n">
-        <v>227.6853280239008</v>
+        <v>227.9592717099387</v>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         <v>32.47999954223633</v>
       </c>
       <c r="CJ10" t="n">
-        <v>45.35763233460455</v>
+        <v>45.35763229455593</v>
       </c>
       <c r="CK10" t="n">
-        <v>84.13840798069145</v>
+        <v>84.13840790640127</v>
       </c>
       <c r="CL10" t="n">
         <v>68.20285165366582</v>
@@ -4158,7 +4158,7 @@
         <v>25.67266223983068</v>
       </c>
       <c r="CR10" t="n">
-        <v>77.40483387543517</v>
+        <v>77.40483385910106</v>
       </c>
       <c r="CS10" t="n">
         <v>68.20285165366582</v>
@@ -4179,7 +4179,7 @@
         <v>88.98573692551506</v>
       </c>
       <c r="CY10" t="n">
-        <v>138.3153785909988</v>
+        <v>138.315378540709</v>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
@@ -4502,37 +4502,37 @@
         <v>32.84999847412109</v>
       </c>
       <c r="CJ11" t="n">
-        <v>24.40198175753305</v>
+        <v>24.40198169497178</v>
       </c>
       <c r="CK11" t="n">
-        <v>32.23832812877129</v>
+        <v>32.23832857587811</v>
       </c>
       <c r="CL11" t="n">
-        <v>33.80534679768205</v>
+        <v>33.80534735319096</v>
       </c>
       <c r="CM11" t="n">
         <v>20.85130777065122</v>
       </c>
       <c r="CN11" t="n">
-        <v>48.27773686236829</v>
+        <v>48.27773734824932</v>
       </c>
       <c r="CO11" t="n">
-        <v>50.98532072971253</v>
+        <v>50.985320809989</v>
       </c>
       <c r="CP11" t="n">
-        <v>16.498567099624</v>
+        <v>16.49856746507192</v>
       </c>
       <c r="CQ11" t="n">
         <v>24.29339039885633</v>
       </c>
       <c r="CR11" t="n">
-        <v>31.41899744314985</v>
+        <v>31.41899767710733</v>
       </c>
       <c r="CS11" t="n">
-        <v>28.32015494315218</v>
+        <v>28.32015513542495</v>
       </c>
       <c r="CT11" t="n">
-        <v>25.48813944883696</v>
+        <v>25.48813962188245</v>
       </c>
       <c r="CU11" t="n">
         <v>8</v>
@@ -4544,10 +4544,10 @@
         <v>3.1</v>
       </c>
       <c r="CX11" t="n">
-        <v>-22.41053079830045</v>
+        <v>-22.41053027152571</v>
       </c>
       <c r="CY11" t="n">
-        <v>-4.356167724325999</v>
+        <v>-4.356167012126622</v>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
@@ -4872,10 +4872,10 @@
         <v>47.31000137329102</v>
       </c>
       <c r="CJ12" t="n">
-        <v>131.3186535240124</v>
+        <v>131.3186533146316</v>
       </c>
       <c r="CK12" t="n">
-        <v>243.596102287043</v>
+        <v>243.5961018986416</v>
       </c>
       <c r="CL12" t="n">
         <v>134.5187807287781</v>
@@ -4896,13 +4896,13 @@
         <v>53.17581509382557</v>
       </c>
       <c r="CR12" t="n">
-        <v>142.2124818265677</v>
+        <v>142.212481751845</v>
       </c>
       <c r="CS12" t="n">
-        <v>127.0811096608068</v>
+        <v>127.0811095561164</v>
       </c>
       <c r="CT12" t="n">
-        <v>114.3729986947261</v>
+        <v>114.3729986005047</v>
       </c>
       <c r="CU12" t="n">
         <v>8</v>
@@ -4914,10 +4914,10 @@
         <v>5.7</v>
       </c>
       <c r="CX12" t="n">
-        <v>141.7522624704375</v>
+        <v>141.7522622712802</v>
       </c>
       <c r="CY12" t="n">
-        <v>200.5970782043861</v>
+        <v>200.5970780464432</v>
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
         <v>-1.560432066163409</v>
       </c>
       <c r="DL12" t="n">
-        <v>-10.93846372884365</v>
+        <v>-10.93847029890879</v>
       </c>
       <c r="DM12" t="b">
         <v>1</v>
@@ -5232,10 +5232,10 @@
         <v>7.239999771118164</v>
       </c>
       <c r="CJ13" t="n">
-        <v>3.268913169515907</v>
+        <v>3.268913169251517</v>
       </c>
       <c r="CK13" t="n">
-        <v>6.063833929452008</v>
+        <v>6.063833928961563</v>
       </c>
       <c r="CL13" t="n">
         <v>20.4541571358882</v>
@@ -5244,10 +5244,10 @@
         <v>14.0164620450613</v>
       </c>
       <c r="CN13" t="n">
-        <v>32.91359934754694</v>
+        <v>32.91359934675771</v>
       </c>
       <c r="CO13" t="n">
-        <v>11.23890095237088</v>
+        <v>10.95072400487419</v>
       </c>
       <c r="CP13" t="n">
         <v>18.67889066749036</v>
@@ -5564,10 +5564,10 @@
         <v>19.30999946594238</v>
       </c>
       <c r="CJ14" t="n">
-        <v>13.27286332418177</v>
+        <v>13.27286325438968</v>
       </c>
       <c r="CK14" t="n">
-        <v>24.62116146635718</v>
+        <v>24.62116133689286</v>
       </c>
       <c r="CL14" t="n">
         <v>19.98886663466692</v>
@@ -5576,7 +5576,7 @@
         <v>12.49234273346821</v>
       </c>
       <c r="CN14" t="n">
-        <v>33.8271937267662</v>
+        <v>33.8271936504311</v>
       </c>
       <c r="CO14" t="n">
         <v>22.8984489302328</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="CQ14" t="inlineStr"/>
       <c r="CR14" t="n">
-        <v>20.19533508885966</v>
+        <v>20.19533503904556</v>
       </c>
       <c r="CS14" t="n">
         <v>21.44365778244985</v>
@@ -5607,7 +5607,7 @@
         <v>-0.05545034714474761</v>
       </c>
       <c r="CY14" t="n">
-        <v>4.58485576076153</v>
+        <v>4.584855502791019</v>
       </c>
       <c r="CZ14" t="inlineStr">
         <is>
@@ -5930,10 +5930,10 @@
         <v>17.21999931335449</v>
       </c>
       <c r="CJ15" t="n">
-        <v>10.55474910713745</v>
+        <v>10.55474911966993</v>
       </c>
       <c r="CK15" t="n">
-        <v>19.57905959373997</v>
+        <v>19.57905961698772</v>
       </c>
       <c r="CL15" t="n">
         <v>37.03977125031607</v>
@@ -5942,25 +5942,25 @@
         <v>36.56718452753732</v>
       </c>
       <c r="CN15" t="n">
-        <v>41.35653254003213</v>
+        <v>41.35653254539012</v>
       </c>
       <c r="CO15" t="n">
-        <v>34.0320101125353</v>
+        <v>34.03201010988473</v>
       </c>
       <c r="CP15" t="n">
-        <v>18.38517857432961</v>
+        <v>18.38517855979395</v>
       </c>
       <c r="CQ15" t="n">
         <v>31.59171947190627</v>
       </c>
       <c r="CR15" t="n">
-        <v>31.22163658148524</v>
+        <v>31.2216365831166</v>
       </c>
       <c r="CS15" t="n">
-        <v>34.0320101125353</v>
+        <v>34.03201010988473</v>
       </c>
       <c r="CT15" t="n">
-        <v>30.62880910128177</v>
+        <v>30.62880909889626</v>
       </c>
       <c r="CU15" t="n">
         <v>7</v>
@@ -5972,10 +5972,10 @@
         <v>3.9</v>
       </c>
       <c r="CX15" t="n">
-        <v>77.86765576423946</v>
+        <v>77.86765575038635</v>
       </c>
       <c r="CY15" t="n">
-        <v>81.31032419537998</v>
+        <v>81.31032420485363</v>
       </c>
       <c r="CZ15" t="inlineStr">
         <is>
@@ -6290,37 +6290,37 @@
         <v>10.10999965667725</v>
       </c>
       <c r="CJ16" t="n">
-        <v>10.13143133318238</v>
+        <v>10.13143130491909</v>
       </c>
       <c r="CK16" t="n">
-        <v>18.70783417981315</v>
+        <v>18.70783425994277</v>
       </c>
       <c r="CL16" t="n">
-        <v>24.60234617795361</v>
+        <v>24.60234635196295</v>
       </c>
       <c r="CM16" t="n">
         <v>17.7286584153084</v>
       </c>
       <c r="CN16" t="n">
-        <v>37.29788758946659</v>
+        <v>37.2978876149876</v>
       </c>
       <c r="CO16" t="n">
-        <v>24.48673101600906</v>
+        <v>24.48673102821477</v>
       </c>
       <c r="CP16" t="n">
-        <v>11.97788209513519</v>
+        <v>11.97788215706571</v>
       </c>
       <c r="CQ16" t="n">
         <v>10.10999965667725</v>
       </c>
       <c r="CR16" t="n">
-        <v>19.3803463079432</v>
+        <v>19.38034634863482</v>
       </c>
       <c r="CS16" t="n">
-        <v>18.21824629756077</v>
+        <v>18.21824633762559</v>
       </c>
       <c r="CT16" t="n">
-        <v>16.3964216678047</v>
+        <v>16.39642170386303</v>
       </c>
       <c r="CU16" t="n">
         <v>8</v>
@@ -6332,10 +6332,10 @@
         <v>3.7</v>
       </c>
       <c r="CX16" t="n">
-        <v>62.18023961034979</v>
+        <v>62.18023996700985</v>
       </c>
       <c r="CY16" t="n">
-        <v>91.69482656849812</v>
+        <v>91.6948269709869</v>
       </c>
       <c r="CZ16" t="inlineStr">
         <is>
@@ -6652,10 +6652,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="CJ17" t="n">
-        <v>5.044849560029598</v>
+        <v>5.044849607343542</v>
       </c>
       <c r="CK17" t="n">
-        <v>9.358195933854903</v>
+        <v>9.358196021622271</v>
       </c>
       <c r="CL17" t="n">
         <v>8.579313567043014</v>
@@ -6726,7 +6726,7 @@
         <v>-1.814801360066387</v>
       </c>
       <c r="DL17" t="n">
-        <v>-28.51676265378231</v>
+        <v>-28.51675560376472</v>
       </c>
       <c r="DM17" t="b">
         <v>1</v>
@@ -7002,10 +7002,10 @@
         <v>10.97000026702881</v>
       </c>
       <c r="CJ18" t="n">
-        <v>9.497073381107768</v>
+        <v>9.497073386656075</v>
       </c>
       <c r="CK18" t="n">
-        <v>17.61707112195491</v>
+        <v>17.61707113224702</v>
       </c>
       <c r="CL18" t="n">
         <v>21.98978873496697</v>
@@ -7014,25 +7014,25 @@
         <v>12.98356721691296</v>
       </c>
       <c r="CN18" t="n">
-        <v>32.25283421753215</v>
+        <v>32.25283420071414</v>
       </c>
       <c r="CO18" t="n">
-        <v>25.67848958322784</v>
+        <v>25.67848957910868</v>
       </c>
       <c r="CP18" t="n">
-        <v>12.06312330019246</v>
+        <v>12.06312328223459</v>
       </c>
       <c r="CQ18" t="n">
         <v>9.632374997322403</v>
       </c>
       <c r="CR18" t="n">
-        <v>17.71429031915218</v>
+        <v>17.71429031627035</v>
       </c>
       <c r="CS18" t="n">
-        <v>15.30031916943394</v>
+        <v>15.30031917457999</v>
       </c>
       <c r="CT18" t="n">
-        <v>13.77028725249054</v>
+        <v>13.77028725712199</v>
       </c>
       <c r="CU18" t="n">
         <v>8</v>
@@ -7044,10 +7044,10 @@
         <v>3.4</v>
       </c>
       <c r="CX18" t="n">
-        <v>25.52677226342661</v>
+        <v>25.52677230564582</v>
       </c>
       <c r="CY18" t="n">
-        <v>61.479397337791</v>
+        <v>61.4793973115209</v>
       </c>
       <c r="CZ18" t="inlineStr">
         <is>
@@ -7362,10 +7362,10 @@
         <v>10.63000011444092</v>
       </c>
       <c r="CJ19" t="n">
-        <v>3.315435253377434</v>
+        <v>3.315435246486174</v>
       </c>
       <c r="CK19" t="n">
-        <v>6.15013239501514</v>
+        <v>6.150132382231853</v>
       </c>
       <c r="CL19" t="n">
         <v>19.53502101474926</v>
@@ -7374,13 +7374,13 @@
         <v>18.41366451165369</v>
       </c>
       <c r="CN19" t="n">
-        <v>20.99443609270429</v>
+        <v>20.99443609322563</v>
       </c>
       <c r="CO19" t="n">
-        <v>15.82814310647173</v>
+        <v>15.82814310783014</v>
       </c>
       <c r="CP19" t="n">
-        <v>13.08852152044672</v>
+        <v>13.08852152918539</v>
       </c>
       <c r="CQ19" t="n">
         <v>29.73646810990179</v>
@@ -7436,7 +7436,7 @@
         <v>-21.14242970755025</v>
       </c>
       <c r="DL19" t="n">
-        <v>-35.62180269808549</v>
+        <v>-35.6218103618902</v>
       </c>
       <c r="DM19" t="b">
         <v>1</v>
@@ -7712,10 +7712,10 @@
         <v>27.42000007629395</v>
       </c>
       <c r="CJ20" t="n">
-        <v>7.265285064599618</v>
+        <v>7.26528504676932</v>
       </c>
       <c r="CK20" t="n">
-        <v>13.47710379483229</v>
+        <v>13.47710376175709</v>
       </c>
       <c r="CL20" t="n">
         <v>35.82988175649849</v>
@@ -7724,19 +7724,19 @@
         <v>28.32096620307184</v>
       </c>
       <c r="CN20" t="n">
-        <v>44.64824887607762</v>
+        <v>44.64824890268274</v>
       </c>
       <c r="CO20" t="n">
-        <v>26.46426766618676</v>
+        <v>26.46426767063081</v>
       </c>
       <c r="CP20" t="n">
-        <v>28.983357471153</v>
+        <v>28.98335750335024</v>
       </c>
       <c r="CQ20" t="n">
         <v>24.27856406616775</v>
       </c>
       <c r="CR20" t="n">
-        <v>28.85748426199825</v>
+        <v>28.85748426630843</v>
       </c>
       <c r="CS20" t="n">
         <v>28.32096620307184</v>
@@ -7757,7 +7757,7 @@
         <v>-7.042780773727464</v>
       </c>
       <c r="CY20" t="n">
-        <v>5.242466016428238</v>
+        <v>5.24246603214733</v>
       </c>
       <c r="CZ20" t="inlineStr">
         <is>
@@ -7796,7 +7796,7 @@
         <v>-2.176241867315365</v>
       </c>
       <c r="DL20" t="n">
-        <v>-22.27487236182183</v>
+        <v>-22.27486391968831</v>
       </c>
       <c r="DM20" t="b">
         <v>1</v>
@@ -8080,10 +8080,10 @@
         <v>22.60000038146973</v>
       </c>
       <c r="CJ21" t="n">
-        <v>3.184692831012528</v>
+        <v>3.18469283068234</v>
       </c>
       <c r="CK21" t="n">
-        <v>5.90760520152824</v>
+        <v>5.907605200915739</v>
       </c>
       <c r="CL21" t="n">
         <v>33.79796896777358</v>
@@ -8092,7 +8092,7 @@
         <v>28.20908778885038</v>
       </c>
       <c r="CN21" t="n">
-        <v>43.29409767000241</v>
+        <v>43.29409766948067</v>
       </c>
       <c r="CO21" t="n">
         <v>10.85340539909456</v>
@@ -8410,10 +8410,10 @@
         <v>39.45000076293945</v>
       </c>
       <c r="CJ22" t="n">
-        <v>36.11966587797076</v>
+        <v>36.11966574648073</v>
       </c>
       <c r="CK22" t="n">
-        <v>52.59023351832543</v>
+        <v>52.59023332687595</v>
       </c>
       <c r="CL22" t="n">
         <v>48.55384709284856</v>
@@ -8430,13 +8430,13 @@
       </c>
       <c r="CQ22" t="inlineStr"/>
       <c r="CR22" t="n">
-        <v>48.97182503796222</v>
+        <v>48.97182495722735</v>
       </c>
       <c r="CS22" t="n">
-        <v>50.572040305587</v>
+        <v>50.57204020986226</v>
       </c>
       <c r="CT22" t="n">
-        <v>45.51483627502829</v>
+        <v>45.51483618887603</v>
       </c>
       <c r="CU22" t="n">
         <v>4</v>
@@ -8448,10 +8448,10 @@
         <v>1.6</v>
       </c>
       <c r="CX22" t="n">
-        <v>15.37347375107363</v>
+        <v>15.37347353269021</v>
       </c>
       <c r="CY22" t="n">
-        <v>24.13643622528865</v>
+        <v>24.13643602063753</v>
       </c>
       <c r="CZ22" t="inlineStr">
         <is>
@@ -8774,10 +8774,10 @@
         <v>34.68999862670898</v>
       </c>
       <c r="CJ23" t="n">
-        <v>3.441931001267119</v>
+        <v>3.441930997438182</v>
       </c>
       <c r="CK23" t="n">
-        <v>6.384782007350505</v>
+        <v>6.384782000247827</v>
       </c>
       <c r="CL23" t="n">
         <v>32.87857523633004</v>
@@ -8786,7 +8786,7 @@
         <v>23.03538757661248</v>
       </c>
       <c r="CN23" t="n">
-        <v>40.667883649383</v>
+        <v>40.66788364554859</v>
       </c>
       <c r="CO23" t="n">
         <v>10.66394352514633</v>
@@ -9104,35 +9104,35 @@
         <v>12.84000015258789</v>
       </c>
       <c r="CJ24" t="n">
-        <v>8.62048133808174</v>
+        <v>8.620481350717007</v>
       </c>
       <c r="CK24" t="n">
-        <v>13.75169155164174</v>
+        <v>13.75169153709569</v>
       </c>
       <c r="CL24" t="n">
-        <v>18.28822738468463</v>
+        <v>18.28822733853445</v>
       </c>
       <c r="CM24" t="n">
         <v>17.29599079072038</v>
       </c>
       <c r="CN24" t="n">
-        <v>22.79369009216899</v>
+        <v>22.79369008003408</v>
       </c>
       <c r="CO24" t="n">
-        <v>17.22078296695734</v>
+        <v>17.22078296345124</v>
       </c>
       <c r="CP24" t="n">
-        <v>9.132575779855479</v>
+        <v>9.132575758329024</v>
       </c>
       <c r="CQ24" t="inlineStr"/>
       <c r="CR24" t="n">
-        <v>14.47029581034136</v>
+        <v>14.47029579744959</v>
       </c>
       <c r="CS24" t="n">
-        <v>15.48623725929954</v>
+        <v>15.48623725027346</v>
       </c>
       <c r="CT24" t="n">
-        <v>13.93761353336959</v>
+        <v>13.93761352524612</v>
       </c>
       <c r="CU24" t="n">
         <v>4</v>
@@ -9144,10 +9144,10 @@
         <v>2.1</v>
       </c>
       <c r="CX24" t="n">
-        <v>8.548390714469534</v>
+        <v>8.548390651202631</v>
       </c>
       <c r="CY24" t="n">
-        <v>12.6970065294344</v>
+        <v>12.69700642903122</v>
       </c>
       <c r="CZ24" t="inlineStr">
         <is>
@@ -9448,10 +9448,10 @@
         <v>39.09999847412109</v>
       </c>
       <c r="CJ25" t="n">
-        <v>19.98838165232127</v>
+        <v>19.98838179307365</v>
       </c>
       <c r="CK25" t="n">
-        <v>37.07844796505595</v>
+        <v>37.07844822615161</v>
       </c>
       <c r="CL25" t="n">
         <v>55.88726858490879</v>
@@ -9460,23 +9460,23 @@
         <v>42.23733079208057</v>
       </c>
       <c r="CN25" t="n">
-        <v>62.05594568752193</v>
+        <v>62.05594545770821</v>
       </c>
       <c r="CO25" t="n">
-        <v>45.10179304171956</v>
+        <v>45.10179299773866</v>
       </c>
       <c r="CP25" t="n">
-        <v>31.29948488805238</v>
+        <v>31.29948460998198</v>
       </c>
       <c r="CQ25" t="inlineStr"/>
       <c r="CR25" t="n">
-        <v>39.51397281100139</v>
+        <v>39.51397290046818</v>
       </c>
       <c r="CS25" t="n">
-        <v>41.09012050338775</v>
+        <v>41.09012061194514</v>
       </c>
       <c r="CT25" t="n">
-        <v>36.98110845304898</v>
+        <v>36.98110855075063</v>
       </c>
       <c r="CU25" t="n">
         <v>4</v>
@@ -9488,10 +9488,10 @@
         <v>2.8</v>
       </c>
       <c r="CX25" t="n">
-        <v>-5.41915627560583</v>
+        <v>-5.419156025729476</v>
       </c>
       <c r="CY25" t="n">
-        <v>1.058757936152599</v>
+        <v>1.058758164967899</v>
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>-6.526424187021751</v>
       </c>
       <c r="DL25" t="n">
-        <v>-19.71089251072075</v>
+        <v>-19.71091149301828</v>
       </c>
       <c r="DM25" t="b">
         <v>1</v>
@@ -9814,10 +9814,10 @@
         <v>6.010000228881836</v>
       </c>
       <c r="CJ26" t="n">
-        <v>7.12914295604707</v>
+        <v>7.129142970191428</v>
       </c>
       <c r="CK26" t="n">
-        <v>13.22456018346731</v>
+        <v>13.2245602097051</v>
       </c>
       <c r="CL26" t="n">
         <v>5.700250753950201</v>
@@ -9838,7 +9838,7 @@
         <v>5.504458217875779</v>
       </c>
       <c r="CR26" t="n">
-        <v>7.427901824374547</v>
+        <v>7.427901829422314</v>
       </c>
       <c r="CS26" t="n">
         <v>5.916792043641768</v>
@@ -9859,7 +9859,7 @@
         <v>-11.39579639802557</v>
       </c>
       <c r="CY26" t="n">
-        <v>23.59237173866984</v>
+        <v>23.59237182265932</v>
       </c>
       <c r="CZ26" t="inlineStr">
         <is>
@@ -10158,10 +10158,10 @@
         <v>14.96000003814697</v>
       </c>
       <c r="CJ27" t="n">
-        <v>9.299118829019461</v>
+        <v>9.299118809475491</v>
       </c>
       <c r="CK27" t="n">
-        <v>17.2498654278311</v>
+        <v>17.24986539157704</v>
       </c>
       <c r="CL27" t="n">
         <v>30.82737177378653</v>
@@ -10170,23 +10170,23 @@
         <v>29.3357145487105</v>
       </c>
       <c r="CN27" t="n">
-        <v>34.72617273512254</v>
+        <v>34.72617273123145</v>
       </c>
       <c r="CO27" t="n">
-        <v>25.37913234406078</v>
+        <v>25.37913234803104</v>
       </c>
       <c r="CP27" t="n">
-        <v>15.31657764647493</v>
+        <v>15.31657767077668</v>
       </c>
       <c r="CQ27" t="inlineStr"/>
       <c r="CR27" t="n">
-        <v>20.68887209367447</v>
+        <v>20.68887208071752</v>
       </c>
       <c r="CS27" t="n">
-        <v>21.31449888594594</v>
+        <v>21.31449886980404</v>
       </c>
       <c r="CT27" t="n">
-        <v>19.18304899735135</v>
+        <v>19.18304898282364</v>
       </c>
       <c r="CU27" t="n">
         <v>4</v>
@@ -10198,10 +10198,10 @@
         <v>3.3</v>
       </c>
       <c r="CX27" t="n">
-        <v>28.22893682109551</v>
+        <v>28.22893672398514</v>
       </c>
       <c r="CY27" t="n">
-        <v>38.29459920400578</v>
+        <v>38.29459911739519</v>
       </c>
       <c r="CZ27" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>-3.17151959331623</v>
       </c>
       <c r="DL27" t="n">
-        <v>-17.75794205146741</v>
+        <v>-17.75793314155376</v>
       </c>
       <c r="DM27" t="b">
         <v>1</v>
@@ -10516,37 +10516,37 @@
         <v>26.64999961853027</v>
       </c>
       <c r="CJ28" t="n">
-        <v>17.04081914555074</v>
+        <v>17.04081916310323</v>
       </c>
       <c r="CK28" t="n">
-        <v>28.24466298961362</v>
+        <v>28.24466299174</v>
       </c>
       <c r="CL28" t="n">
-        <v>47.3030634411532</v>
+        <v>47.303063395991</v>
       </c>
       <c r="CM28" t="n">
         <v>53.09041087001181</v>
       </c>
       <c r="CN28" t="n">
-        <v>56.22823555621964</v>
+        <v>56.22823556182855</v>
       </c>
       <c r="CO28" t="n">
-        <v>42.93945176688816</v>
+        <v>42.93945176369508</v>
       </c>
       <c r="CP28" t="n">
-        <v>23.53452110954218</v>
+        <v>23.53452108991007</v>
       </c>
       <c r="CQ28" t="n">
         <v>30.99183173163939</v>
       </c>
       <c r="CR28" t="n">
-        <v>37.42162457632735</v>
+        <v>37.42162457098989</v>
       </c>
       <c r="CS28" t="n">
-        <v>36.96564174926377</v>
+        <v>36.96564174766723</v>
       </c>
       <c r="CT28" t="n">
-        <v>33.26907757433739</v>
+        <v>33.26907757290051</v>
       </c>
       <c r="CU28" t="n">
         <v>8</v>
@@ -10558,10 +10558,10 @@
         <v>3.3</v>
       </c>
       <c r="CX28" t="n">
-        <v>24.83706585573362</v>
+        <v>24.83706585034193</v>
       </c>
       <c r="CY28" t="n">
-        <v>40.41885595490722</v>
+        <v>40.41885593487924</v>
       </c>
       <c r="CZ28" t="inlineStr">
         <is>
@@ -10876,37 +10876,37 @@
         <v>15.11999988555908</v>
       </c>
       <c r="CJ29" t="n">
-        <v>5.865830796106986</v>
+        <v>5.865830788677193</v>
       </c>
       <c r="CK29" t="n">
-        <v>8.474845208228476</v>
+        <v>8.474845214413056</v>
       </c>
       <c r="CL29" t="n">
-        <v>10.77599630151474</v>
+        <v>10.77599632302773</v>
       </c>
       <c r="CM29" t="n">
         <v>11.55627711976371</v>
       </c>
       <c r="CN29" t="n">
-        <v>9.774262758716311</v>
+        <v>9.774262770671955</v>
       </c>
       <c r="CO29" t="n">
-        <v>14.91642323703296</v>
+        <v>14.91642323966363</v>
       </c>
       <c r="CP29" t="n">
-        <v>5.368455502201046</v>
+        <v>5.368455514231369</v>
       </c>
       <c r="CQ29" t="n">
         <v>10.8369287109083</v>
       </c>
       <c r="CR29" t="n">
-        <v>9.696127454309066</v>
+        <v>9.696127460169617</v>
       </c>
       <c r="CS29" t="n">
-        <v>10.27512953011553</v>
+        <v>10.27512954684984</v>
       </c>
       <c r="CT29" t="n">
-        <v>9.247616577103976</v>
+        <v>9.247616592164857</v>
       </c>
       <c r="CU29" t="n">
         <v>8</v>
@@ -10918,10 +10918,10 @@
         <v>2.8</v>
       </c>
       <c r="CX29" t="n">
-        <v>-38.83851423877155</v>
+        <v>-38.83851413916255</v>
       </c>
       <c r="CY29" t="n">
-        <v>-35.87217243586282</v>
+        <v>-35.87217239710257</v>
       </c>
       <c r="CZ29" t="inlineStr">
         <is>
@@ -11236,37 +11236,37 @@
         <v>38.70000076293945</v>
       </c>
       <c r="CJ30" t="n">
-        <v>30.84756145961468</v>
+        <v>30.84756136567085</v>
       </c>
       <c r="CK30" t="n">
-        <v>35.74245442473018</v>
+        <v>35.74245449883714</v>
       </c>
       <c r="CL30" t="n">
-        <v>39.06003421916135</v>
+        <v>39.06003441910111</v>
       </c>
       <c r="CM30" t="n">
         <v>49.9060657389037</v>
       </c>
       <c r="CN30" t="n">
-        <v>60.73976153776389</v>
+        <v>60.73976164225601</v>
       </c>
       <c r="CO30" t="n">
-        <v>16.61273117662608</v>
+        <v>16.61273118579321</v>
       </c>
       <c r="CP30" t="n">
-        <v>17.68241854768684</v>
+        <v>17.68241871418536</v>
       </c>
       <c r="CQ30" t="n">
         <v>28.82212409504474</v>
       </c>
       <c r="CR30" t="n">
-        <v>34.92664389994143</v>
+        <v>34.92664395747401</v>
       </c>
       <c r="CS30" t="n">
-        <v>33.29500794217243</v>
+        <v>33.29500793225399</v>
       </c>
       <c r="CT30" t="n">
-        <v>29.96550714795519</v>
+        <v>29.9655071390286</v>
       </c>
       <c r="CU30" t="n">
         <v>8</v>
@@ -11278,10 +11278,10 @@
         <v>3.7</v>
       </c>
       <c r="CX30" t="n">
-        <v>-22.56975049816726</v>
+        <v>-22.5697505212334</v>
       </c>
       <c r="CY30" t="n">
-        <v>-9.750275939558961</v>
+        <v>-9.750275790895968</v>
       </c>
       <c r="CZ30" t="inlineStr">
         <is>
@@ -11578,35 +11578,35 @@
         <v>16.93000030517578</v>
       </c>
       <c r="CJ31" t="n">
-        <v>10.07593946881644</v>
+        <v>10.07593960608275</v>
       </c>
       <c r="CK31" t="n">
-        <v>17.56133915983863</v>
+        <v>17.56133913665739</v>
       </c>
       <c r="CL31" t="n">
-        <v>28.8325885130935</v>
+        <v>28.83258808224258</v>
       </c>
       <c r="CM31" t="n">
         <v>29.26650917734455</v>
       </c>
       <c r="CN31" t="n">
-        <v>32.09021934382206</v>
+        <v>32.09021933517218</v>
       </c>
       <c r="CO31" t="n">
-        <v>27.62963449401778</v>
+        <v>27.6296344633191</v>
       </c>
       <c r="CP31" t="n">
-        <v>14.228316384647</v>
+        <v>14.22831621396458</v>
       </c>
       <c r="CQ31" t="inlineStr"/>
       <c r="CR31" t="n">
-        <v>21.02487540894159</v>
+        <v>21.02487532207546</v>
       </c>
       <c r="CS31" t="n">
-        <v>22.5954868269282</v>
+        <v>22.59548679998825</v>
       </c>
       <c r="CT31" t="n">
-        <v>20.33593814423538</v>
+        <v>20.33593811998942</v>
       </c>
       <c r="CU31" t="n">
         <v>4</v>
@@ -11618,10 +11618,10 @@
         <v>2.9</v>
       </c>
       <c r="CX31" t="n">
-        <v>20.11776596376285</v>
+        <v>20.11776582054987</v>
       </c>
       <c r="CY31" t="n">
-        <v>24.18709409304578</v>
+        <v>24.18709357995585</v>
       </c>
       <c r="CZ31" t="inlineStr">
         <is>
@@ -11940,37 +11940,37 @@
         <v>44.06000137329102</v>
       </c>
       <c r="CJ32" t="n">
-        <v>31.96233902274301</v>
+        <v>31.96233910772903</v>
       </c>
       <c r="CK32" t="n">
-        <v>43.40419626504693</v>
+        <v>43.40419610462463</v>
       </c>
       <c r="CL32" t="n">
-        <v>49.69482714320432</v>
+        <v>49.69482682739612</v>
       </c>
       <c r="CM32" t="n">
         <v>47.301358204649</v>
       </c>
       <c r="CN32" t="n">
-        <v>69.17232321949791</v>
+        <v>69.17232304338198</v>
       </c>
       <c r="CO32" t="n">
-        <v>58.77995438993259</v>
+        <v>58.77995435502147</v>
       </c>
       <c r="CP32" t="n">
-        <v>24.46050917783012</v>
+        <v>24.46050898016625</v>
       </c>
       <c r="CQ32" t="n">
         <v>76.33330481362214</v>
       </c>
       <c r="CR32" t="n">
-        <v>50.13860152956575</v>
+        <v>50.13860142957382</v>
       </c>
       <c r="CS32" t="n">
-        <v>48.49809267392666</v>
+        <v>48.49809251602256</v>
       </c>
       <c r="CT32" t="n">
-        <v>43.648283406534</v>
+        <v>43.64828326442031</v>
       </c>
       <c r="CU32" t="n">
         <v>8</v>
@@ -11982,10 +11982,10 @@
         <v>3.1</v>
       </c>
       <c r="CX32" t="n">
-        <v>-0.9344483747715016</v>
+        <v>-0.9344486973173138</v>
       </c>
       <c r="CY32" t="n">
-        <v>13.79618694238069</v>
+        <v>13.79618671543581</v>
       </c>
       <c r="CZ32" t="inlineStr">
         <is>
@@ -12290,10 +12290,10 @@
         <v>53.7400016784668</v>
       </c>
       <c r="CJ33" t="n">
-        <v>10.50731956795014</v>
+        <v>10.50731956327966</v>
       </c>
       <c r="CK33" t="n">
-        <v>19.49107779854751</v>
+        <v>19.49107778988377</v>
       </c>
       <c r="CL33" t="n">
         <v>62.18821154931746</v>
@@ -12302,7 +12302,7 @@
         <v>46.54098234247379</v>
       </c>
       <c r="CN33" t="n">
-        <v>83.24912656142394</v>
+        <v>83.24912655571329</v>
       </c>
       <c r="CO33" t="n">
         <v>11.76833333333333</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="CQ33" t="inlineStr"/>
       <c r="CR33" t="n">
-        <v>13.92224356661033</v>
+        <v>13.92224356216559</v>
       </c>
       <c r="CS33" t="n">
         <v>11.76833333333333</v>
@@ -12333,7 +12333,7 @@
         <v>-80.29121758616556</v>
       </c>
       <c r="CY33" t="n">
-        <v>-74.09333246785353</v>
+        <v>-74.09333247612435</v>
       </c>
       <c r="CZ33" t="inlineStr">
         <is>
@@ -12638,10 +12638,10 @@
         <v>29.46999931335449</v>
       </c>
       <c r="CJ34" t="n">
-        <v>15.40499614525348</v>
+        <v>15.40499610458543</v>
       </c>
       <c r="CK34" t="n">
-        <v>28.57626784944521</v>
+        <v>28.57626777400598</v>
       </c>
       <c r="CL34" t="n">
         <v>53.78477836114972</v>
@@ -12650,23 +12650,23 @@
         <v>48.59041952862963</v>
       </c>
       <c r="CN34" t="n">
-        <v>59.55728564090104</v>
+        <v>59.55728565180924</v>
       </c>
       <c r="CO34" t="n">
-        <v>36.60763962993459</v>
+        <v>36.60763963743898</v>
       </c>
       <c r="CP34" t="n">
-        <v>29.60722465810817</v>
+        <v>29.60722471425936</v>
       </c>
       <c r="CQ34" t="inlineStr"/>
       <c r="CR34" t="n">
-        <v>33.59342049644575</v>
+        <v>33.59342046929503</v>
       </c>
       <c r="CS34" t="n">
-        <v>32.5919537396899</v>
+        <v>32.59195370572248</v>
       </c>
       <c r="CT34" t="n">
-        <v>29.33275836572091</v>
+        <v>29.33275833515023</v>
       </c>
       <c r="CU34" t="n">
         <v>4</v>
@@ -12678,10 +12678,10 @@
         <v>3.5</v>
       </c>
       <c r="CX34" t="n">
-        <v>-0.4656971524644393</v>
+        <v>-0.4656972561993489</v>
       </c>
       <c r="CY34" t="n">
-        <v>13.99192833106959</v>
+        <v>13.99192823893953</v>
       </c>
       <c r="CZ34" t="inlineStr">
         <is>
@@ -12998,10 +12998,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="CJ35" t="n">
-        <v>12.95070196212595</v>
+        <v>12.95070191627523</v>
       </c>
       <c r="CK35" t="n">
-        <v>18.85622205685539</v>
+        <v>18.85622199009674</v>
       </c>
       <c r="CL35" t="n">
         <v>16.51297649354425</v>
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CN35" t="inlineStr"/>
       <c r="CO35" t="n">
-        <v>13.95326101288333</v>
+        <v>14.12767677554437</v>
       </c>
       <c r="CP35" t="n">
         <v>4.241657423479087</v>
@@ -13020,7 +13020,7 @@
         <v>14.71449508364002</v>
       </c>
       <c r="CR35" t="n">
-        <v>15.99671598258106</v>
+        <v>16.02578525758967</v>
       </c>
       <c r="CS35" t="n">
         <v>15.61373578859213</v>
@@ -13041,7 +13041,7 @@
         <v>35.11887235740878</v>
       </c>
       <c r="CY35" t="n">
-        <v>53.81458239747236</v>
+        <v>54.09409466742301</v>
       </c>
       <c r="CZ35" t="inlineStr">
         <is>
@@ -13356,37 +13356,37 @@
         <v>18.73999977111816</v>
       </c>
       <c r="CJ36" t="n">
-        <v>8.790659640692011</v>
+        <v>8.790659630786015</v>
       </c>
       <c r="CK36" t="n">
-        <v>9.149702328356627</v>
+        <v>9.149702328877998</v>
       </c>
       <c r="CL36" t="n">
-        <v>9.503707803063788</v>
+        <v>9.503707814314847</v>
       </c>
       <c r="CM36" t="n">
         <v>16.79875791329259</v>
       </c>
       <c r="CN36" t="n">
-        <v>9.013907502659793</v>
+        <v>9.013907511228686</v>
       </c>
       <c r="CO36" t="n">
-        <v>17.3677507839341</v>
+        <v>17.36775078637179</v>
       </c>
       <c r="CP36" t="n">
-        <v>3.803999721349142</v>
+        <v>3.803999732681604</v>
       </c>
       <c r="CQ36" t="n">
         <v>16.19033501601518</v>
       </c>
       <c r="CR36" t="n">
-        <v>11.3273525886704</v>
+        <v>11.32735259169609</v>
       </c>
       <c r="CS36" t="n">
-        <v>9.326705065710208</v>
+        <v>9.326705071596422</v>
       </c>
       <c r="CT36" t="n">
-        <v>8.394034559139188</v>
+        <v>8.39403456443678</v>
       </c>
       <c r="CU36" t="n">
         <v>8</v>
@@ -13398,10 +13398,10 @@
         <v>4.6</v>
       </c>
       <c r="CX36" t="n">
-        <v>-55.20792603169633</v>
+        <v>-55.20792600342742</v>
       </c>
       <c r="CY36" t="n">
-        <v>-39.55521490385519</v>
+        <v>-39.55521488770957</v>
       </c>
       <c r="CZ36" t="inlineStr">
         <is>
@@ -14340,10 +14340,10 @@
         <v>10.35999965667725</v>
       </c>
       <c r="CJ2" t="n">
-        <v>5.851607493390991</v>
+        <v>5.851607492840716</v>
       </c>
       <c r="CK2" t="n">
-        <v>10.85473190024029</v>
+        <v>10.85473189921953</v>
       </c>
       <c r="CL2" t="n">
         <v>41.59696831847682</v>
@@ -14352,7 +14352,7 @@
         <v>27.90166392450355</v>
       </c>
       <c r="CN2" t="n">
-        <v>71.91590901746441</v>
+        <v>71.91590901512991</v>
       </c>
       <c r="CO2" t="n">
         <v>19.76753935237404</v>
@@ -14690,10 +14690,10 @@
         <v>13.46000003814697</v>
       </c>
       <c r="CJ3" t="n">
-        <v>14.84732057000014</v>
+        <v>14.8473205387898</v>
       </c>
       <c r="CK3" t="n">
-        <v>27.54177965735026</v>
+        <v>27.54177959945507</v>
       </c>
       <c r="CL3" t="n">
         <v>38.93995644223742</v>
@@ -14702,13 +14702,13 @@
         <v>23.51205793312256</v>
       </c>
       <c r="CN3" t="n">
-        <v>75.5448285957473</v>
+        <v>75.54482865353735</v>
       </c>
       <c r="CO3" t="n">
-        <v>48.52515937946949</v>
+        <v>48.52515940240973</v>
       </c>
       <c r="CP3" t="n">
-        <v>26.80868494893448</v>
+        <v>26.80868504522712</v>
       </c>
       <c r="CQ3" t="n">
         <v>8.920136085713818</v>
@@ -15040,10 +15040,10 @@
         <v>24.61000061035156</v>
       </c>
       <c r="CJ4" t="n">
-        <v>16.31411912109865</v>
+        <v>16.31411911267199</v>
       </c>
       <c r="CK4" t="n">
-        <v>30.26269096963799</v>
+        <v>30.26269095400653</v>
       </c>
       <c r="CL4" t="n">
         <v>72.30210822331667</v>
@@ -15052,19 +15052,19 @@
         <v>52.41049602817493</v>
       </c>
       <c r="CN4" t="n">
-        <v>127.9950261271193</v>
+        <v>127.9950261297231</v>
       </c>
       <c r="CO4" t="n">
-        <v>26.12261083743122</v>
+        <v>26.12261083863716</v>
       </c>
       <c r="CP4" t="n">
-        <v>63.19894114730609</v>
+        <v>63.19894116538502</v>
       </c>
       <c r="CQ4" t="n">
         <v>42.85100954601229</v>
       </c>
       <c r="CR4" t="n">
-        <v>47.8579761253132</v>
+        <v>47.8579761259221</v>
       </c>
       <c r="CS4" t="n">
         <v>47.63075278709361</v>
@@ -15085,7 +15085,7 @@
         <v>74.18803919229917</v>
       </c>
       <c r="CY4" t="n">
-        <v>94.46556252901097</v>
+        <v>94.46556253148518</v>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
@@ -15398,10 +15398,10 @@
         <v>4.119999885559082</v>
       </c>
       <c r="CJ5" t="n">
-        <v>3.742641514200839</v>
+        <v>3.742641517861567</v>
       </c>
       <c r="CK5" t="n">
-        <v>6.942600008842556</v>
+        <v>6.942600015633207</v>
       </c>
       <c r="CL5" t="n">
         <v>12.63657372306894</v>
@@ -15410,19 +15410,19 @@
         <v>8.512687176725057</v>
       </c>
       <c r="CN5" t="n">
-        <v>24.29899389621988</v>
+        <v>24.2989938935693</v>
       </c>
       <c r="CO5" t="n">
-        <v>11.19276558851729</v>
+        <v>11.19276558700668</v>
       </c>
       <c r="CP5" t="n">
-        <v>10.1975051773985</v>
+        <v>10.19750516827538</v>
       </c>
       <c r="CQ5" t="n">
         <v>5.258139118319559</v>
       </c>
       <c r="CR5" t="n">
-        <v>8.354701758153251</v>
+        <v>8.354701758127199</v>
       </c>
       <c r="CS5" t="n">
         <v>8.512687176725057</v>
@@ -15443,7 +15443,7 @@
         <v>85.95676388017426</v>
       </c>
       <c r="CY5" t="n">
-        <v>102.784028888863</v>
+        <v>102.7840288882306</v>
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
@@ -15758,10 +15758,10 @@
         <v>4.5</v>
       </c>
       <c r="CJ6" t="n">
-        <v>3.282970782701641</v>
+        <v>3.282970770769473</v>
       </c>
       <c r="CK6" t="n">
-        <v>6.089910801911545</v>
+        <v>6.089910779777372</v>
       </c>
       <c r="CL6" t="n">
         <v>12.96195652173913</v>
@@ -15770,7 +15770,7 @@
         <v>8.728772626887835</v>
       </c>
       <c r="CN6" t="n">
-        <v>24.66556325170065</v>
+        <v>24.66556321538536</v>
       </c>
       <c r="CO6" t="n">
         <v>11.57513776217851</v>
@@ -15782,7 +15782,7 @@
         <v>5.383571029035719</v>
       </c>
       <c r="CR6" t="n">
-        <v>11.60598121645608</v>
+        <v>11.60598120810615</v>
       </c>
       <c r="CS6" t="n">
         <v>11.57513776217851</v>
@@ -15803,7 +15803,7 @@
         <v>131.5027552435702</v>
       </c>
       <c r="CY6" t="n">
-        <v>157.9106936990239</v>
+        <v>157.9106935134701</v>
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>1.836517861131659</v>
       </c>
       <c r="DL6" t="n">
-        <v>-41.72317990102352</v>
+        <v>-41.72318362747433</v>
       </c>
       <c r="DM6" t="b">
         <v>1</v>
@@ -16108,10 +16108,10 @@
         <v>48.34000015258789</v>
       </c>
       <c r="CJ7" t="n">
-        <v>18.42191766034588</v>
+        <v>18.42191762293993</v>
       </c>
       <c r="CK7" t="n">
-        <v>34.1726572599416</v>
+        <v>34.17265719055356</v>
       </c>
       <c r="CL7" t="n">
         <v>74.65093263657221</v>
@@ -16120,23 +16120,23 @@
         <v>55.91472932652801</v>
       </c>
       <c r="CN7" t="n">
-        <v>99.83445496223254</v>
+        <v>99.83445502080644</v>
       </c>
       <c r="CO7" t="n">
-        <v>47.86104930791952</v>
+        <v>47.8610493169606</v>
       </c>
       <c r="CP7" t="n">
-        <v>58.90972725125358</v>
+        <v>58.90972732643655</v>
       </c>
       <c r="CQ7" t="inlineStr"/>
       <c r="CR7" t="n">
-        <v>43.77663921619479</v>
+        <v>43.77663919175657</v>
       </c>
       <c r="CS7" t="n">
-        <v>41.01685328393056</v>
+        <v>41.01685325375708</v>
       </c>
       <c r="CT7" t="n">
-        <v>36.91516795553751</v>
+        <v>36.91516792838138</v>
       </c>
       <c r="CU7" t="n">
         <v>4</v>
@@ -16148,10 +16148,10 @@
         <v>4.1</v>
       </c>
       <c r="CX7" t="n">
-        <v>-23.63432387461164</v>
+        <v>-23.63432393078898</v>
       </c>
       <c r="CY7" t="n">
-        <v>-9.440134302831183</v>
+        <v>-9.440134353386053</v>
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
@@ -16690,10 +16690,10 @@
         <v>15.69999980926514</v>
       </c>
       <c r="CJ9" t="n">
-        <v>6.403272793702906</v>
+        <v>6.403272799399811</v>
       </c>
       <c r="CK9" t="n">
-        <v>11.87807103231889</v>
+        <v>11.87807104288665</v>
       </c>
       <c r="CL9" t="n">
         <v>25.39987759130195</v>
@@ -16702,19 +16702,19 @@
         <v>18.63509665364473</v>
       </c>
       <c r="CN9" t="n">
-        <v>35.24419671738814</v>
+        <v>35.24419670813639</v>
       </c>
       <c r="CO9" t="n">
-        <v>12.29886961932753</v>
+        <v>12.29886961824623</v>
       </c>
       <c r="CP9" t="n">
-        <v>20.39435313533854</v>
+        <v>20.39435312340193</v>
       </c>
       <c r="CQ9" t="n">
         <v>18.40902666520164</v>
       </c>
       <c r="CR9" t="n">
-        <v>20.32278448778878</v>
+        <v>20.32278448611708</v>
       </c>
       <c r="CS9" t="n">
         <v>18.63509665364473</v>
@@ -16735,7 +16735,7 @@
         <v>6.825396127602112</v>
       </c>
       <c r="CY9" t="n">
-        <v>29.44448875595251</v>
+        <v>29.44448874530474</v>
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
@@ -17060,10 +17060,10 @@
         <v>42.70000076293945</v>
       </c>
       <c r="CJ10" t="n">
-        <v>125.1015275491483</v>
+        <v>125.1015269589179</v>
       </c>
       <c r="CK10" t="n">
-        <v>232.0633336036701</v>
+        <v>232.0633325087928</v>
       </c>
       <c r="CL10" t="n">
         <v>134.3883634463059</v>
@@ -17075,7 +17075,7 @@
         <v>304.2755398784284</v>
       </c>
       <c r="CO10" t="n">
-        <v>55.15675999999999</v>
+        <v>56.09255333333333</v>
       </c>
       <c r="CP10" t="n">
         <v>122.7244677509661</v>
@@ -17084,13 +17084,13 @@
         <v>54.40212095818906</v>
       </c>
       <c r="CR10" t="n">
-        <v>139.9216375662463</v>
+        <v>140.0386115222745</v>
       </c>
       <c r="CS10" t="n">
-        <v>123.9129976500572</v>
+        <v>123.912997354942</v>
       </c>
       <c r="CT10" t="n">
-        <v>111.5216978850515</v>
+        <v>111.5216976194478</v>
       </c>
       <c r="CU10" t="n">
         <v>8</v>
@@ -17102,10 +17102,10 @@
         <v>5.6</v>
       </c>
       <c r="CX10" t="n">
-        <v>161.1749318324237</v>
+        <v>161.174931210401</v>
       </c>
       <c r="CY10" t="n">
-        <v>227.6853280239008</v>
+        <v>227.9592717099387</v>
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
@@ -17420,10 +17420,10 @@
         <v>32.47999954223633</v>
       </c>
       <c r="CJ11" t="n">
-        <v>45.35763233460455</v>
+        <v>45.35763229455593</v>
       </c>
       <c r="CK11" t="n">
-        <v>84.13840798069145</v>
+        <v>84.13840790640127</v>
       </c>
       <c r="CL11" t="n">
         <v>68.20285165366582</v>
@@ -17444,7 +17444,7 @@
         <v>25.67266223983068</v>
       </c>
       <c r="CR11" t="n">
-        <v>77.40483387543517</v>
+        <v>77.40483385910106</v>
       </c>
       <c r="CS11" t="n">
         <v>68.20285165366582</v>
@@ -17465,7 +17465,7 @@
         <v>88.98573692551506</v>
       </c>
       <c r="CY11" t="n">
-        <v>138.3153785909988</v>
+        <v>138.315378540709</v>
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
@@ -17780,10 +17780,10 @@
         <v>6.920000076293945</v>
       </c>
       <c r="CJ12" t="n">
-        <v>6.500811646585628</v>
+        <v>6.50081164054339</v>
       </c>
       <c r="CK12" t="n">
-        <v>12.05900560441634</v>
+        <v>12.05900559320799</v>
       </c>
       <c r="CL12" t="n">
         <v>40.39207092990959</v>
@@ -17792,7 +17792,7 @@
         <v>27.23293457569906</v>
       </c>
       <c r="CN12" t="n">
-        <v>85.8199842275806</v>
+        <v>85.81998419031571</v>
       </c>
       <c r="CO12" t="n">
         <v>51.88018214566937</v>
@@ -18134,37 +18134,37 @@
         <v>32.84999847412109</v>
       </c>
       <c r="CJ13" t="n">
-        <v>24.40198175753305</v>
+        <v>24.40198169497178</v>
       </c>
       <c r="CK13" t="n">
-        <v>32.23832812877129</v>
+        <v>32.23832857587811</v>
       </c>
       <c r="CL13" t="n">
-        <v>33.80534679768205</v>
+        <v>33.80534735319096</v>
       </c>
       <c r="CM13" t="n">
         <v>20.85130777065122</v>
       </c>
       <c r="CN13" t="n">
-        <v>48.27773686236829</v>
+        <v>48.27773734824932</v>
       </c>
       <c r="CO13" t="n">
-        <v>50.98532072971253</v>
+        <v>50.985320809989</v>
       </c>
       <c r="CP13" t="n">
-        <v>16.498567099624</v>
+        <v>16.49856746507192</v>
       </c>
       <c r="CQ13" t="n">
         <v>24.29339039885633</v>
       </c>
       <c r="CR13" t="n">
-        <v>31.41899744314985</v>
+        <v>31.41899767710733</v>
       </c>
       <c r="CS13" t="n">
-        <v>28.32015494315218</v>
+        <v>28.32015513542495</v>
       </c>
       <c r="CT13" t="n">
-        <v>25.48813944883696</v>
+        <v>25.48813962188245</v>
       </c>
       <c r="CU13" t="n">
         <v>8</v>
@@ -18176,10 +18176,10 @@
         <v>3.1</v>
       </c>
       <c r="CX13" t="n">
-        <v>-22.41053079830045</v>
+        <v>-22.41053027152571</v>
       </c>
       <c r="CY13" t="n">
-        <v>-4.356167724325999</v>
+        <v>-4.356167012126622</v>
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
@@ -18504,10 +18504,10 @@
         <v>47.31000137329102</v>
       </c>
       <c r="CJ14" t="n">
-        <v>131.3186535240124</v>
+        <v>131.3186533146316</v>
       </c>
       <c r="CK14" t="n">
-        <v>243.596102287043</v>
+        <v>243.5961018986416</v>
       </c>
       <c r="CL14" t="n">
         <v>134.5187807287781</v>
@@ -18528,13 +18528,13 @@
         <v>53.17581509382557</v>
       </c>
       <c r="CR14" t="n">
-        <v>142.2124818265677</v>
+        <v>142.212481751845</v>
       </c>
       <c r="CS14" t="n">
-        <v>127.0811096608068</v>
+        <v>127.0811095561164</v>
       </c>
       <c r="CT14" t="n">
-        <v>114.3729986947261</v>
+        <v>114.3729986005047</v>
       </c>
       <c r="CU14" t="n">
         <v>8</v>
@@ -18546,10 +18546,10 @@
         <v>5.7</v>
       </c>
       <c r="CX14" t="n">
-        <v>141.7522624704375</v>
+        <v>141.7522622712802</v>
       </c>
       <c r="CY14" t="n">
-        <v>200.5970782043861</v>
+        <v>200.5970780464432</v>
       </c>
       <c r="CZ14" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>-1.560432066163409</v>
       </c>
       <c r="DL14" t="n">
-        <v>-10.93846372884365</v>
+        <v>-10.93847029890879</v>
       </c>
       <c r="DM14" t="b">
         <v>1</v>
@@ -19200,10 +19200,10 @@
         <v>13.80000019073486</v>
       </c>
       <c r="CJ16" t="n">
-        <v>10.01824948501665</v>
+        <v>10.01824945480682</v>
       </c>
       <c r="CK16" t="n">
-        <v>18.58385279470589</v>
+        <v>18.58385273866666</v>
       </c>
       <c r="CL16" t="n">
         <v>49.41891960195592</v>
@@ -19212,23 +19212,23 @@
         <v>48.6151297750832</v>
       </c>
       <c r="CN16" t="n">
-        <v>68.76522849909007</v>
+        <v>68.76522844086412</v>
       </c>
       <c r="CO16" t="n">
-        <v>33.7657969264196</v>
+        <v>33.76579693110877</v>
       </c>
       <c r="CP16" t="n">
-        <v>29.36037665076843</v>
+        <v>29.36037668601968</v>
       </c>
       <c r="CQ16" t="inlineStr"/>
       <c r="CR16" t="n">
-        <v>33.92285644102714</v>
+        <v>33.92285642391045</v>
       </c>
       <c r="CS16" t="n">
-        <v>33.7657969264196</v>
+        <v>33.76579693110877</v>
       </c>
       <c r="CT16" t="n">
-        <v>30.38921723377764</v>
+        <v>30.3892172379979</v>
       </c>
       <c r="CU16" t="n">
         <v>3</v>
@@ -19240,10 +19240,10 @@
         <v>4.9</v>
       </c>
       <c r="CX16" t="n">
-        <v>120.2117160417183</v>
+        <v>120.2117160722999</v>
       </c>
       <c r="CY16" t="n">
-        <v>145.8177968997601</v>
+        <v>145.8177967757262</v>
       </c>
       <c r="CZ16" t="inlineStr">
         <is>
@@ -19554,10 +19554,10 @@
         <v>7.239999771118164</v>
       </c>
       <c r="CJ17" t="n">
-        <v>3.268913169515907</v>
+        <v>3.268913169251517</v>
       </c>
       <c r="CK17" t="n">
-        <v>6.063833929452008</v>
+        <v>6.063833928961563</v>
       </c>
       <c r="CL17" t="n">
         <v>20.4541571358882</v>
@@ -19566,10 +19566,10 @@
         <v>14.0164620450613</v>
       </c>
       <c r="CN17" t="n">
-        <v>32.91359934754694</v>
+        <v>32.91359934675771</v>
       </c>
       <c r="CO17" t="n">
-        <v>11.23890095237088</v>
+        <v>10.95072400487419</v>
       </c>
       <c r="CP17" t="n">
         <v>18.67889066749036</v>
@@ -19886,10 +19886,10 @@
         <v>19.30999946594238</v>
       </c>
       <c r="CJ18" t="n">
-        <v>13.27286332418177</v>
+        <v>13.27286325438968</v>
       </c>
       <c r="CK18" t="n">
-        <v>24.62116146635718</v>
+        <v>24.62116133689286</v>
       </c>
       <c r="CL18" t="n">
         <v>19.98886663466692</v>
@@ -19898,7 +19898,7 @@
         <v>12.49234273346821</v>
       </c>
       <c r="CN18" t="n">
-        <v>33.8271937267662</v>
+        <v>33.8271936504311</v>
       </c>
       <c r="CO18" t="n">
         <v>22.8984489302328</v>
@@ -19908,7 +19908,7 @@
       </c>
       <c r="CQ18" t="inlineStr"/>
       <c r="CR18" t="n">
-        <v>20.19533508885966</v>
+        <v>20.19533503904556</v>
       </c>
       <c r="CS18" t="n">
         <v>21.44365778244985</v>
@@ -19929,7 +19929,7 @@
         <v>-0.05545034714474761</v>
       </c>
       <c r="CY18" t="n">
-        <v>4.58485576076153</v>
+        <v>4.584855502791019</v>
       </c>
       <c r="CZ18" t="inlineStr">
         <is>
@@ -20252,10 +20252,10 @@
         <v>17.21999931335449</v>
       </c>
       <c r="CJ19" t="n">
-        <v>10.55474910713745</v>
+        <v>10.55474911966993</v>
       </c>
       <c r="CK19" t="n">
-        <v>19.57905959373997</v>
+        <v>19.57905961698772</v>
       </c>
       <c r="CL19" t="n">
         <v>37.03977125031607</v>
@@ -20264,25 +20264,25 @@
         <v>36.56718452753732</v>
       </c>
       <c r="CN19" t="n">
-        <v>41.35653254003213</v>
+        <v>41.35653254539012</v>
       </c>
       <c r="CO19" t="n">
-        <v>34.0320101125353</v>
+        <v>34.03201010988473</v>
       </c>
       <c r="CP19" t="n">
-        <v>18.38517857432961</v>
+        <v>18.38517855979395</v>
       </c>
       <c r="CQ19" t="n">
         <v>31.59171947190627</v>
       </c>
       <c r="CR19" t="n">
-        <v>31.22163658148524</v>
+        <v>31.2216365831166</v>
       </c>
       <c r="CS19" t="n">
-        <v>34.0320101125353</v>
+        <v>34.03201010988473</v>
       </c>
       <c r="CT19" t="n">
-        <v>30.62880910128177</v>
+        <v>30.62880909889626</v>
       </c>
       <c r="CU19" t="n">
         <v>7</v>
@@ -20294,10 +20294,10 @@
         <v>3.9</v>
       </c>
       <c r="CX19" t="n">
-        <v>77.86765576423946</v>
+        <v>77.86765575038635</v>
       </c>
       <c r="CY19" t="n">
-        <v>81.31032419537998</v>
+        <v>81.31032420485363</v>
       </c>
       <c r="CZ19" t="inlineStr">
         <is>
@@ -20612,37 +20612,37 @@
         <v>10.10999965667725</v>
       </c>
       <c r="CJ20" t="n">
-        <v>10.13143133318238</v>
+        <v>10.13143130491909</v>
       </c>
       <c r="CK20" t="n">
-        <v>18.70783417981315</v>
+        <v>18.70783425994277</v>
       </c>
       <c r="CL20" t="n">
-        <v>24.60234617795361</v>
+        <v>24.60234635196295</v>
       </c>
       <c r="CM20" t="n">
         <v>17.7286584153084</v>
       </c>
       <c r="CN20" t="n">
-        <v>37.29788758946659</v>
+        <v>37.2978876149876</v>
       </c>
       <c r="CO20" t="n">
-        <v>24.48673101600906</v>
+        <v>24.48673102821477</v>
       </c>
       <c r="CP20" t="n">
-        <v>11.97788209513519</v>
+        <v>11.97788215706571</v>
       </c>
       <c r="CQ20" t="n">
         <v>10.10999965667725</v>
       </c>
       <c r="CR20" t="n">
-        <v>19.3803463079432</v>
+        <v>19.38034634863482</v>
       </c>
       <c r="CS20" t="n">
-        <v>18.21824629756077</v>
+        <v>18.21824633762559</v>
       </c>
       <c r="CT20" t="n">
-        <v>16.3964216678047</v>
+        <v>16.39642170386303</v>
       </c>
       <c r="CU20" t="n">
         <v>8</v>
@@ -20654,10 +20654,10 @@
         <v>3.7</v>
       </c>
       <c r="CX20" t="n">
-        <v>62.18023961034979</v>
+        <v>62.18023996700985</v>
       </c>
       <c r="CY20" t="n">
-        <v>91.69482656849812</v>
+        <v>91.6948269709869</v>
       </c>
       <c r="CZ20" t="inlineStr">
         <is>
@@ -20974,10 +20974,10 @@
         <v>3.490000009536743</v>
       </c>
       <c r="CJ21" t="n">
-        <v>5.044849560029598</v>
+        <v>5.044849607343542</v>
       </c>
       <c r="CK21" t="n">
-        <v>9.358195933854903</v>
+        <v>9.358196021622271</v>
       </c>
       <c r="CL21" t="n">
         <v>8.579313567043014</v>
@@ -21048,7 +21048,7 @@
         <v>-1.814801360066387</v>
       </c>
       <c r="DL21" t="n">
-        <v>-28.51676265378231</v>
+        <v>-28.51675560376472</v>
       </c>
       <c r="DM21" t="b">
         <v>1</v>
@@ -21324,37 +21324,37 @@
         <v>35.20000076293945</v>
       </c>
       <c r="CJ22" t="n">
-        <v>25.30945517262612</v>
+        <v>25.30945519526922</v>
       </c>
       <c r="CK22" t="n">
-        <v>31.0567095465457</v>
+        <v>31.05670951275091</v>
       </c>
       <c r="CL22" t="n">
-        <v>34.16642437968186</v>
+        <v>34.1664243119362</v>
       </c>
       <c r="CM22" t="n">
         <v>36.55813791194976</v>
       </c>
       <c r="CN22" t="n">
-        <v>48.3044456149437</v>
+        <v>48.3044455690549</v>
       </c>
       <c r="CO22" t="n">
-        <v>49.08093709514336</v>
+        <v>49.08093708517718</v>
       </c>
       <c r="CP22" t="n">
-        <v>16.11152996054647</v>
+        <v>16.11152990963571</v>
       </c>
       <c r="CQ22" t="n">
         <v>30.9183777534985</v>
       </c>
       <c r="CR22" t="n">
-        <v>33.93825217936693</v>
+        <v>33.93825215615905</v>
       </c>
       <c r="CS22" t="n">
-        <v>32.61156696311378</v>
+        <v>32.61156691234356</v>
       </c>
       <c r="CT22" t="n">
-        <v>29.3504102668024</v>
+        <v>29.3504102211092</v>
       </c>
       <c r="CU22" t="n">
         <v>8</v>
@@ -21366,10 +21366,10 @@
         <v>3</v>
       </c>
       <c r="CX22" t="n">
-        <v>-16.61815445838237</v>
+        <v>-16.6181545881926</v>
       </c>
       <c r="CY22" t="n">
-        <v>-3.584512943820617</v>
+        <v>-3.584513009752111</v>
       </c>
       <c r="CZ22" t="inlineStr">
         <is>
@@ -21680,10 +21680,10 @@
         <v>10.97000026702881</v>
       </c>
       <c r="CJ23" t="n">
-        <v>9.497073381107768</v>
+        <v>9.497073386656075</v>
       </c>
       <c r="CK23" t="n">
-        <v>17.61707112195491</v>
+        <v>17.61707113224702</v>
       </c>
       <c r="CL23" t="n">
         <v>21.98978873496697</v>
@@ -21692,25 +21692,25 @@
         <v>12.98356721691296</v>
       </c>
       <c r="CN23" t="n">
-        <v>32.25283421753215</v>
+        <v>32.25283420071414</v>
       </c>
       <c r="CO23" t="n">
-        <v>25.67848958322784</v>
+        <v>25.67848957910868</v>
       </c>
       <c r="CP23" t="n">
-        <v>12.06312330019246</v>
+        <v>12.06312328223459</v>
       </c>
       <c r="CQ23" t="n">
         <v>9.632374997322403</v>
       </c>
       <c r="CR23" t="n">
-        <v>17.71429031915218</v>
+        <v>17.71429031627035</v>
       </c>
       <c r="CS23" t="n">
-        <v>15.30031916943394</v>
+        <v>15.30031917457999</v>
       </c>
       <c r="CT23" t="n">
-        <v>13.77028725249054</v>
+        <v>13.77028725712199</v>
       </c>
       <c r="CU23" t="n">
         <v>8</v>
@@ -21722,10 +21722,10 @@
         <v>3.4</v>
       </c>
       <c r="CX23" t="n">
-        <v>25.52677226342661</v>
+        <v>25.52677230564582</v>
       </c>
       <c r="CY23" t="n">
-        <v>61.479397337791</v>
+        <v>61.4793973115209</v>
       </c>
       <c r="CZ23" t="inlineStr">
         <is>
@@ -22040,10 +22040,10 @@
         <v>10.63000011444092</v>
       </c>
       <c r="CJ24" t="n">
-        <v>3.315435253377434</v>
+        <v>3.315435246486174</v>
       </c>
       <c r="CK24" t="n">
-        <v>6.15013239501514</v>
+        <v>6.150132382231853</v>
       </c>
       <c r="CL24" t="n">
         <v>19.53502101474926</v>
@@ -22052,13 +22052,13 @@
         <v>18.41366451165369</v>
       </c>
       <c r="CN24" t="n">
-        <v>20.99443609270429</v>
+        <v>20.99443609322563</v>
       </c>
       <c r="CO24" t="n">
-        <v>15.82814310647173</v>
+        <v>15.82814310783014</v>
       </c>
       <c r="CP24" t="n">
-        <v>13.08852152044672</v>
+        <v>13.08852152918539</v>
       </c>
       <c r="CQ24" t="n">
         <v>29.73646810990179</v>
@@ -22114,7 +22114,7 @@
         <v>-21.14242970755025</v>
       </c>
       <c r="DL24" t="n">
-        <v>-35.62180269808549</v>
+        <v>-35.6218103618902</v>
       </c>
       <c r="DM24" t="b">
         <v>1</v>
@@ -22398,10 +22398,10 @@
         <v>14.72999954223633</v>
       </c>
       <c r="CJ25" t="n">
-        <v>4.523502086078591</v>
+        <v>4.523502094443318</v>
       </c>
       <c r="CK25" t="n">
-        <v>8.391096369675786</v>
+        <v>8.391096385192354</v>
       </c>
       <c r="CL25" t="n">
         <v>24.2149496196813</v>
@@ -22410,25 +22410,25 @@
         <v>20.36807772582785</v>
       </c>
       <c r="CN25" t="n">
-        <v>29.43735272701935</v>
+        <v>29.43735272038758</v>
       </c>
       <c r="CO25" t="n">
-        <v>16.79287740027581</v>
+        <v>16.79287739853672</v>
       </c>
       <c r="CP25" t="n">
-        <v>18.44681921390274</v>
+        <v>18.44681920060149</v>
       </c>
       <c r="CQ25" t="n">
         <v>14.61024983224005</v>
       </c>
       <c r="CR25" t="n">
-        <v>18.89448898408899</v>
+        <v>18.89448898320962</v>
       </c>
       <c r="CS25" t="n">
-        <v>18.44681921390274</v>
+        <v>18.44681920060149</v>
       </c>
       <c r="CT25" t="n">
-        <v>16.60213729251247</v>
+        <v>16.60213728054134</v>
       </c>
       <c r="CU25" t="n">
         <v>7</v>
@@ -22440,10 +22440,10 @@
         <v>6.5</v>
       </c>
       <c r="CX25" t="n">
-        <v>12.70969320065511</v>
+        <v>12.70969311938475</v>
       </c>
       <c r="CY25" t="n">
-        <v>28.27216273776205</v>
+        <v>28.27216273179214</v>
       </c>
       <c r="CZ25" t="inlineStr">
         <is>
@@ -23104,10 +23104,10 @@
         <v>14.31999969482422</v>
       </c>
       <c r="CJ27" t="n">
-        <v>8.981535421199682</v>
+        <v>8.981535430420973</v>
       </c>
       <c r="CK27" t="n">
-        <v>16.66074820632541</v>
+        <v>16.6607482234309</v>
       </c>
       <c r="CL27" t="n">
         <v>13.52387711735003</v>
@@ -23128,7 +23128,7 @@
         <v>6.210695553020633</v>
       </c>
       <c r="CR27" t="n">
-        <v>11.29322925586511</v>
+        <v>11.29322925962608</v>
       </c>
       <c r="CS27" t="n">
         <v>10.99565184259889</v>
@@ -23149,7 +23149,7 @@
         <v>-30.89324811985986</v>
       </c>
       <c r="CY27" t="n">
-        <v>-21.13666552697689</v>
+        <v>-21.13666550071312</v>
       </c>
       <c r="CZ27" t="inlineStr">
         <is>
@@ -23460,10 +23460,10 @@
         <v>27.42000007629395</v>
       </c>
       <c r="CJ28" t="n">
-        <v>7.265285064599618</v>
+        <v>7.26528504676932</v>
       </c>
       <c r="CK28" t="n">
-        <v>13.47710379483229</v>
+        <v>13.47710376175709</v>
       </c>
       <c r="CL28" t="n">
         <v>35.82988175649849</v>
@@ -23472,19 +23472,19 @@
         <v>28.32096620307184</v>
       </c>
       <c r="CN28" t="n">
-        <v>44.64824887607762</v>
+        <v>44.64824890268274</v>
       </c>
       <c r="CO28" t="n">
-        <v>26.46426766618676</v>
+        <v>26.46426767063081</v>
       </c>
       <c r="CP28" t="n">
-        <v>28.983357471153</v>
+        <v>28.98335750335024</v>
       </c>
       <c r="CQ28" t="n">
         <v>24.27856406616775</v>
       </c>
       <c r="CR28" t="n">
-        <v>28.85748426199825</v>
+        <v>28.85748426630843</v>
       </c>
       <c r="CS28" t="n">
         <v>28.32096620307184</v>
@@ -23505,7 +23505,7 @@
         <v>-7.042780773727464</v>
       </c>
       <c r="CY28" t="n">
-        <v>5.242466016428238</v>
+        <v>5.24246603214733</v>
       </c>
       <c r="CZ28" t="inlineStr">
         <is>
@@ -23544,7 +23544,7 @@
         <v>-2.176241867315365</v>
       </c>
       <c r="DL28" t="n">
-        <v>-22.27487236182183</v>
+        <v>-22.27486391968831</v>
       </c>
       <c r="DM28" t="b">
         <v>1</v>
@@ -23820,10 +23820,10 @@
         <v>23.79999923706055</v>
       </c>
       <c r="CJ29" t="n">
-        <v>12.34802659921232</v>
+        <v>12.34802658968168</v>
       </c>
       <c r="CK29" t="n">
-        <v>22.90558934153884</v>
+        <v>22.90558932385952</v>
       </c>
       <c r="CL29" t="n">
         <v>61.59179490059613</v>
@@ -23832,13 +23832,13 @@
         <v>51.73586889978424</v>
       </c>
       <c r="CN29" t="n">
-        <v>87.07810606304278</v>
+        <v>87.07810606134656</v>
       </c>
       <c r="CO29" t="n">
-        <v>34.83309172400272</v>
+        <v>33.74455760921434</v>
       </c>
       <c r="CP29" t="n">
-        <v>45.92960715987113</v>
+        <v>45.92960717518571</v>
       </c>
       <c r="CQ29" t="n">
         <v>5.609791711095563</v>
@@ -24186,10 +24186,10 @@
         <v>22.60000038146973</v>
       </c>
       <c r="CJ30" t="n">
-        <v>3.184692831012528</v>
+        <v>3.18469283068234</v>
       </c>
       <c r="CK30" t="n">
-        <v>5.90760520152824</v>
+        <v>5.907605200915739</v>
       </c>
       <c r="CL30" t="n">
         <v>33.79796896777358</v>
@@ -24198,7 +24198,7 @@
         <v>28.20908778885038</v>
       </c>
       <c r="CN30" t="n">
-        <v>43.29409767000241</v>
+        <v>43.29409766948067</v>
       </c>
       <c r="CO30" t="n">
         <v>10.85340539909456</v>
@@ -24516,10 +24516,10 @@
         <v>39.45000076293945</v>
       </c>
       <c r="CJ31" t="n">
-        <v>36.11966587797076</v>
+        <v>36.11966574648073</v>
       </c>
       <c r="CK31" t="n">
-        <v>52.59023351832543</v>
+        <v>52.59023332687595</v>
       </c>
       <c r="CL31" t="n">
         <v>48.55384709284856</v>
@@ -24536,13 +24536,13 @@
       </c>
       <c r="CQ31" t="inlineStr"/>
       <c r="CR31" t="n">
-        <v>48.97182503796222</v>
+        <v>48.97182495722735</v>
       </c>
       <c r="CS31" t="n">
-        <v>50.572040305587</v>
+        <v>50.57204020986226</v>
       </c>
       <c r="CT31" t="n">
-        <v>45.51483627502829</v>
+        <v>45.51483618887603</v>
       </c>
       <c r="CU31" t="n">
         <v>4</v>
@@ -24554,10 +24554,10 @@
         <v>1.6</v>
       </c>
       <c r="CX31" t="n">
-        <v>15.37347375107363</v>
+        <v>15.37347353269021</v>
       </c>
       <c r="CY31" t="n">
-        <v>24.13643622528865</v>
+        <v>24.13643602063753</v>
       </c>
       <c r="CZ31" t="inlineStr">
         <is>
@@ -24872,10 +24872,10 @@
         <v>11.92000007629395</v>
       </c>
       <c r="CJ32" t="n">
-        <v>2.063410196006522</v>
+        <v>2.063410192240472</v>
       </c>
       <c r="CK32" t="n">
-        <v>3.827625913592099</v>
+        <v>3.827625906606074</v>
       </c>
       <c r="CL32" t="n">
         <v>27.37261715960048</v>
@@ -24884,7 +24884,7 @@
         <v>23.19321737174429</v>
       </c>
       <c r="CN32" t="n">
-        <v>35.99440968604862</v>
+        <v>35.99440967691089</v>
       </c>
       <c r="CO32" t="n">
         <v>8.985947463999999</v>
@@ -25200,35 +25200,35 @@
         <v>23.04999923706055</v>
       </c>
       <c r="CJ33" t="n">
-        <v>16.54461552319857</v>
+        <v>16.54461540975388</v>
       </c>
       <c r="CK33" t="n">
-        <v>29.57431141734741</v>
+        <v>29.57431143455015</v>
       </c>
       <c r="CL33" t="n">
-        <v>49.88257113774699</v>
+        <v>49.88257150880213</v>
       </c>
       <c r="CM33" t="n">
         <v>49.40798271639872</v>
       </c>
       <c r="CN33" t="n">
-        <v>61.60540340239055</v>
+        <v>61.60540335634547</v>
       </c>
       <c r="CO33" t="n">
-        <v>45.67365135610321</v>
+        <v>45.67365138077939</v>
       </c>
       <c r="CP33" t="n">
-        <v>24.48336420896027</v>
+        <v>24.48336434922328</v>
       </c>
       <c r="CQ33" t="inlineStr"/>
       <c r="CR33" t="n">
-        <v>35.41878735859905</v>
+        <v>35.41878743347139</v>
       </c>
       <c r="CS33" t="n">
-        <v>37.62398138672531</v>
+        <v>37.62398140766477</v>
       </c>
       <c r="CT33" t="n">
-        <v>33.86158324805278</v>
+        <v>33.86158326689829</v>
       </c>
       <c r="CU33" t="n">
         <v>4</v>
@@ -25240,10 +25240,10 @@
         <v>3</v>
       </c>
       <c r="CX33" t="n">
-        <v>46.90492133990622</v>
+        <v>46.90492142166549</v>
       </c>
       <c r="CY33" t="n">
-        <v>53.66068776979201</v>
+        <v>53.66068809461779</v>
       </c>
       <c r="CZ33" t="inlineStr">
         <is>
@@ -25554,10 +25554,10 @@
         <v>33.38999938964844</v>
       </c>
       <c r="CJ34" t="n">
-        <v>7.919773850179173</v>
+        <v>7.919773878941919</v>
       </c>
       <c r="CK34" t="n">
-        <v>14.69118049208237</v>
+        <v>14.69118054543726</v>
       </c>
       <c r="CL34" t="n">
         <v>63.74891814306077</v>
@@ -25566,7 +25566,7 @@
         <v>37.2141137927402</v>
       </c>
       <c r="CN34" t="n">
-        <v>88.14507561199352</v>
+        <v>88.14507567001634</v>
       </c>
       <c r="CO34" t="n">
         <v>22.94410877968384</v>
@@ -25904,10 +25904,10 @@
         <v>33.36000061035156</v>
       </c>
       <c r="CJ35" t="n">
-        <v>15.11688473796417</v>
+        <v>15.11688468736917</v>
       </c>
       <c r="CK35" t="n">
-        <v>28.04182118892354</v>
+        <v>28.04182109506981</v>
       </c>
       <c r="CL35" t="n">
         <v>20.05535426892732</v>
@@ -25916,7 +25916,7 @@
         <v>36.99750756788258</v>
       </c>
       <c r="CN35" t="n">
-        <v>27.00891076908082</v>
+        <v>27.00891073694244</v>
       </c>
       <c r="CO35" t="n">
         <v>15.03391666666667</v>
@@ -25928,7 +25928,7 @@
         <v>79.30503918682102</v>
       </c>
       <c r="CR35" t="n">
-        <v>22.4627357806472</v>
+        <v>22.46273575542047</v>
       </c>
       <c r="CS35" t="n">
         <v>20.05535426892732</v>
@@ -25949,7 +25949,7 @@
         <v>-45.89382940108894</v>
       </c>
       <c r="CY35" t="n">
-        <v>-32.66566136189745</v>
+        <v>-32.66566143751714</v>
       </c>
       <c r="CZ35" t="inlineStr">
         <is>
@@ -26268,10 +26268,10 @@
         <v>34.68999862670898</v>
       </c>
       <c r="CJ36" t="n">
-        <v>3.441931001267119</v>
+        <v>3.441930997438182</v>
       </c>
       <c r="CK36" t="n">
-        <v>6.384782007350505</v>
+        <v>6.384782000247827</v>
       </c>
       <c r="CL36" t="n">
         <v>32.87857523633004</v>
@@ -26280,7 +26280,7 @@
         <v>23.03538757661248</v>
       </c>
       <c r="CN36" t="n">
-        <v>40.667883649383</v>
+        <v>40.66788364554859</v>
       </c>
       <c r="CO36" t="n">
         <v>10.66394352514633</v>
@@ -26598,35 +26598,35 @@
         <v>12.84000015258789</v>
       </c>
       <c r="CJ37" t="n">
-        <v>8.62048133808174</v>
+        <v>8.620481350717007</v>
       </c>
       <c r="CK37" t="n">
-        <v>13.75169155164174</v>
+        <v>13.75169153709569</v>
       </c>
       <c r="CL37" t="n">
-        <v>18.28822738468463</v>
+        <v>18.28822733853445</v>
       </c>
       <c r="CM37" t="n">
         <v>17.29599079072038</v>
       </c>
       <c r="CN37" t="n">
-        <v>22.79369009216899</v>
+        <v>22.79369008003408</v>
       </c>
       <c r="CO37" t="n">
-        <v>17.22078296695734</v>
+        <v>17.22078296345124</v>
       </c>
       <c r="CP37" t="n">
-        <v>9.132575779855479</v>
+        <v>9.132575758329024</v>
       </c>
       <c r="CQ37" t="inlineStr"/>
       <c r="CR37" t="n">
-        <v>14.47029581034136</v>
+        <v>14.47029579744959</v>
       </c>
       <c r="CS37" t="n">
-        <v>15.48623725929954</v>
+        <v>15.48623725027346</v>
       </c>
       <c r="CT37" t="n">
-        <v>13.93761353336959</v>
+        <v>13.93761352524612</v>
       </c>
       <c r="CU37" t="n">
         <v>4</v>
@@ -26638,10 +26638,10 @@
         <v>2.1</v>
       </c>
       <c r="CX37" t="n">
-        <v>8.548390714469534</v>
+        <v>8.548390651202631</v>
       </c>
       <c r="CY37" t="n">
-        <v>12.6970065294344</v>
+        <v>12.69700642903122</v>
       </c>
       <c r="CZ37" t="inlineStr">
         <is>
@@ -26942,10 +26942,10 @@
         <v>39.09999847412109</v>
       </c>
       <c r="CJ38" t="n">
-        <v>19.98838165232127</v>
+        <v>19.98838179307365</v>
       </c>
       <c r="CK38" t="n">
-        <v>37.07844796505595</v>
+        <v>37.07844822615161</v>
       </c>
       <c r="CL38" t="n">
         <v>55.88726858490879</v>
@@ -26954,23 +26954,23 @@
         <v>42.23733079208057</v>
       </c>
       <c r="CN38" t="n">
-        <v>62.05594568752193</v>
+        <v>62.05594545770821</v>
       </c>
       <c r="CO38" t="n">
-        <v>45.10179304171956</v>
+        <v>45.10179299773866</v>
       </c>
       <c r="CP38" t="n">
-        <v>31.29948488805238</v>
+        <v>31.29948460998198</v>
       </c>
       <c r="CQ38" t="inlineStr"/>
       <c r="CR38" t="n">
-        <v>39.51397281100139</v>
+        <v>39.51397290046818</v>
       </c>
       <c r="CS38" t="n">
-        <v>41.09012050338775</v>
+        <v>41.09012061194514</v>
       </c>
       <c r="CT38" t="n">
-        <v>36.98110845304898</v>
+        <v>36.98110855075063</v>
       </c>
       <c r="CU38" t="n">
         <v>4</v>
@@ -26982,10 +26982,10 @@
         <v>2.8</v>
       </c>
       <c r="CX38" t="n">
-        <v>-5.41915627560583</v>
+        <v>-5.419156025729476</v>
       </c>
       <c r="CY38" t="n">
-        <v>1.058757936152599</v>
+        <v>1.058758164967899</v>
       </c>
       <c r="CZ38" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>-6.526424187021751</v>
       </c>
       <c r="DL38" t="n">
-        <v>-19.71089251072075</v>
+        <v>-19.71091149301828</v>
       </c>
       <c r="DM38" t="b">
         <v>1</v>
@@ -27308,10 +27308,10 @@
         <v>6.010000228881836</v>
       </c>
       <c r="CJ39" t="n">
-        <v>7.12914295604707</v>
+        <v>7.129142970191428</v>
       </c>
       <c r="CK39" t="n">
-        <v>13.22456018346731</v>
+        <v>13.2245602097051</v>
       </c>
       <c r="CL39" t="n">
         <v>5.700250753950201</v>
@@ -27332,7 +27332,7 @@
         <v>5.504458217875779</v>
       </c>
       <c r="CR39" t="n">
-        <v>7.427901824374547</v>
+        <v>7.427901829422314</v>
       </c>
       <c r="CS39" t="n">
         <v>5.916792043641768</v>
@@ -27353,7 +27353,7 @@
         <v>-11.39579639802557</v>
       </c>
       <c r="CY39" t="n">
-        <v>23.59237173866984</v>
+        <v>23.59237182265932</v>
       </c>
       <c r="CZ39" t="inlineStr">
         <is>
@@ -27652,10 +27652,10 @@
         <v>14.96000003814697</v>
       </c>
       <c r="CJ40" t="n">
-        <v>9.299118829019461</v>
+        <v>9.299118809475491</v>
       </c>
       <c r="CK40" t="n">
-        <v>17.2498654278311</v>
+        <v>17.24986539157704</v>
       </c>
       <c r="CL40" t="n">
         <v>30.82737177378653</v>
@@ -27664,23 +27664,23 @@
         <v>29.3357145487105</v>
       </c>
       <c r="CN40" t="n">
-        <v>34.72617273512254</v>
+        <v>34.72617273123145</v>
       </c>
       <c r="CO40" t="n">
-        <v>25.37913234406078</v>
+        <v>25.37913234803104</v>
       </c>
       <c r="CP40" t="n">
-        <v>15.31657764647493</v>
+        <v>15.31657767077668</v>
       </c>
       <c r="CQ40" t="inlineStr"/>
       <c r="CR40" t="n">
-        <v>20.68887209367447</v>
+        <v>20.68887208071752</v>
       </c>
       <c r="CS40" t="n">
-        <v>21.31449888594594</v>
+        <v>21.31449886980404</v>
       </c>
       <c r="CT40" t="n">
-        <v>19.18304899735135</v>
+        <v>19.18304898282364</v>
       </c>
       <c r="CU40" t="n">
         <v>4</v>
@@ -27692,10 +27692,10 @@
         <v>3.3</v>
       </c>
       <c r="CX40" t="n">
-        <v>28.22893682109551</v>
+        <v>28.22893672398514</v>
       </c>
       <c r="CY40" t="n">
-        <v>38.29459920400578</v>
+        <v>38.29459911739519</v>
       </c>
       <c r="CZ40" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>-3.17151959331623</v>
       </c>
       <c r="DL40" t="n">
-        <v>-17.75794205146741</v>
+        <v>-17.75793314155376</v>
       </c>
       <c r="DM40" t="b">
         <v>1</v>
@@ -28010,10 +28010,10 @@
         <v>12.75</v>
       </c>
       <c r="CJ41" t="n">
-        <v>1.570253761967148</v>
+        <v>1.570253753985819</v>
       </c>
       <c r="CK41" t="n">
-        <v>2.912820728449059</v>
+        <v>2.912820713643694</v>
       </c>
       <c r="CL41" t="n">
         <v>12.56040892193308</v>
@@ -28022,7 +28022,7 @@
         <v>9.175696506445684</v>
       </c>
       <c r="CN41" t="n">
-        <v>15.85379573736357</v>
+        <v>15.85379572905587</v>
       </c>
       <c r="CO41" t="n">
         <v>6.104046666666666</v>
@@ -28080,7 +28080,7 @@
         <v>-14.19919048066149</v>
       </c>
       <c r="DL41" t="n">
-        <v>-29.85972104196217</v>
+        <v>-29.85972843358833</v>
       </c>
       <c r="DM41" t="b">
         <v>0</v>
@@ -28356,37 +28356,37 @@
         <v>26.64999961853027</v>
       </c>
       <c r="CJ42" t="n">
-        <v>17.04081914555074</v>
+        <v>17.04081916310323</v>
       </c>
       <c r="CK42" t="n">
-        <v>28.24466298961362</v>
+        <v>28.24466299174</v>
       </c>
       <c r="CL42" t="n">
-        <v>47.3030634411532</v>
+        <v>47.303063395991</v>
       </c>
       <c r="CM42" t="n">
         <v>53.09041087001181</v>
       </c>
       <c r="CN42" t="n">
-        <v>56.22823555621964</v>
+        <v>56.22823556182855</v>
       </c>
       <c r="CO42" t="n">
-        <v>42.93945176688816</v>
+        <v>42.93945176369508</v>
       </c>
       <c r="CP42" t="n">
-        <v>23.53452110954218</v>
+        <v>23.53452108991007</v>
       </c>
       <c r="CQ42" t="n">
         <v>30.99183173163939</v>
       </c>
       <c r="CR42" t="n">
-        <v>37.42162457632735</v>
+        <v>37.42162457098989</v>
       </c>
       <c r="CS42" t="n">
-        <v>36.96564174926377</v>
+        <v>36.96564174766723</v>
       </c>
       <c r="CT42" t="n">
-        <v>33.26907757433739</v>
+        <v>33.26907757290051</v>
       </c>
       <c r="CU42" t="n">
         <v>8</v>
@@ -28398,10 +28398,10 @@
         <v>3.3</v>
       </c>
       <c r="CX42" t="n">
-        <v>24.83706585573362</v>
+        <v>24.83706585034193</v>
       </c>
       <c r="CY42" t="n">
-        <v>40.41885595490722</v>
+        <v>40.41885593487924</v>
       </c>
       <c r="CZ42" t="inlineStr">
         <is>
@@ -28716,37 +28716,37 @@
         <v>15.11999988555908</v>
       </c>
       <c r="CJ43" t="n">
-        <v>5.865830796106986</v>
+        <v>5.865830788677193</v>
       </c>
       <c r="CK43" t="n">
-        <v>8.474845208228476</v>
+        <v>8.474845214413056</v>
       </c>
       <c r="CL43" t="n">
-        <v>10.77599630151474</v>
+        <v>10.77599632302773</v>
       </c>
       <c r="CM43" t="n">
         <v>11.55627711976371</v>
       </c>
       <c r="CN43" t="n">
-        <v>9.774262758716311</v>
+        <v>9.774262770671955</v>
       </c>
       <c r="CO43" t="n">
-        <v>14.91642323703296</v>
+        <v>14.91642323966363</v>
       </c>
       <c r="CP43" t="n">
-        <v>5.368455502201046</v>
+        <v>5.368455514231369</v>
       </c>
       <c r="CQ43" t="n">
         <v>10.8369287109083</v>
       </c>
       <c r="CR43" t="n">
-        <v>9.696127454309066</v>
+        <v>9.696127460169617</v>
       </c>
       <c r="CS43" t="n">
-        <v>10.27512953011553</v>
+        <v>10.27512954684984</v>
       </c>
       <c r="CT43" t="n">
-        <v>9.247616577103976</v>
+        <v>9.247616592164857</v>
       </c>
       <c r="CU43" t="n">
         <v>8</v>
@@ -28758,10 +28758,10 @@
         <v>2.8</v>
       </c>
       <c r="CX43" t="n">
-        <v>-38.83851423877155</v>
+        <v>-38.83851413916255</v>
       </c>
       <c r="CY43" t="n">
-        <v>-35.87217243586282</v>
+        <v>-35.87217239710257</v>
       </c>
       <c r="CZ43" t="inlineStr">
         <is>
@@ -29076,10 +29076,10 @@
         <v>11.77000045776367</v>
       </c>
       <c r="CJ44" t="n">
-        <v>4.784269064230426</v>
+        <v>4.784269074292063</v>
       </c>
       <c r="CK44" t="n">
-        <v>8.874819114147439</v>
+        <v>8.874819132811776</v>
       </c>
       <c r="CL44" t="n">
         <v>25.44086558978281</v>
@@ -29088,25 +29088,25 @@
         <v>28.63793221437547</v>
       </c>
       <c r="CN44" t="n">
-        <v>23.6167692462746</v>
+        <v>23.61676925495629</v>
       </c>
       <c r="CO44" t="n">
-        <v>14.24977379844433</v>
+        <v>14.24977379744902</v>
       </c>
       <c r="CP44" t="n">
-        <v>13.10602503645083</v>
+        <v>13.10602502746377</v>
       </c>
       <c r="CQ44" t="n">
         <v>4.870861694358507</v>
       </c>
       <c r="CR44" t="n">
-        <v>18.98769749991258</v>
+        <v>18.98769750280652</v>
       </c>
       <c r="CS44" t="n">
-        <v>18.93327152235947</v>
+        <v>18.93327152620266</v>
       </c>
       <c r="CT44" t="n">
-        <v>17.03994437012352</v>
+        <v>17.03994437358239</v>
       </c>
       <c r="CU44" t="n">
         <v>6</v>
@@ -29118,10 +29118,10 @@
         <v>6</v>
       </c>
       <c r="CX44" t="n">
-        <v>44.77437304502154</v>
+        <v>44.7743730744087</v>
       </c>
       <c r="CY44" t="n">
-        <v>61.32282719995994</v>
+        <v>61.32282722454736</v>
       </c>
       <c r="CZ44" t="inlineStr">
         <is>
@@ -29432,10 +29432,10 @@
         <v>9.069999694824219</v>
       </c>
       <c r="CJ45" t="n">
-        <v>2.472824455218899</v>
+        <v>2.472824459691816</v>
       </c>
       <c r="CK45" t="n">
-        <v>4.587089364431057</v>
+        <v>4.587089372728318</v>
       </c>
       <c r="CL45" t="n">
         <v>13.23540704365869</v>
@@ -29444,19 +29444,19 @@
         <v>14.96700525293176</v>
       </c>
       <c r="CN45" t="n">
-        <v>10.35281120611356</v>
+        <v>10.35281120673552</v>
       </c>
       <c r="CO45" t="n">
-        <v>7.309831173973449</v>
+        <v>7.309831173542495</v>
       </c>
       <c r="CP45" t="n">
-        <v>6.779397752649116</v>
+        <v>6.779397748705074</v>
       </c>
       <c r="CQ45" t="n">
         <v>10.12863973392969</v>
       </c>
       <c r="CR45" t="n">
-        <v>9.622883075383905</v>
+        <v>9.622883076033078</v>
       </c>
       <c r="CS45" t="n">
         <v>10.12863973392969</v>
@@ -29477,7 +29477,7 @@
         <v>0.5046975441313828</v>
       </c>
       <c r="CY45" t="n">
-        <v>6.095737587237049</v>
+        <v>6.095737594394435</v>
       </c>
       <c r="CZ45" t="inlineStr">
         <is>
@@ -29788,37 +29788,37 @@
         <v>38.70000076293945</v>
       </c>
       <c r="CJ46" t="n">
-        <v>30.84756145961468</v>
+        <v>30.84756136567085</v>
       </c>
       <c r="CK46" t="n">
-        <v>35.74245442473018</v>
+        <v>35.74245449883714</v>
       </c>
       <c r="CL46" t="n">
-        <v>39.06003421916135</v>
+        <v>39.06003441910111</v>
       </c>
       <c r="CM46" t="n">
         <v>49.9060657389037</v>
       </c>
       <c r="CN46" t="n">
-        <v>60.73976153776389</v>
+        <v>60.73976164225601</v>
       </c>
       <c r="CO46" t="n">
-        <v>16.61273117662608</v>
+        <v>16.61273118579321</v>
       </c>
       <c r="CP46" t="n">
-        <v>17.68241854768684</v>
+        <v>17.68241871418536</v>
       </c>
       <c r="CQ46" t="n">
         <v>28.82212409504474</v>
       </c>
       <c r="CR46" t="n">
-        <v>34.92664389994143</v>
+        <v>34.92664395747401</v>
       </c>
       <c r="CS46" t="n">
-        <v>33.29500794217243</v>
+        <v>33.29500793225399</v>
       </c>
       <c r="CT46" t="n">
-        <v>29.96550714795519</v>
+        <v>29.9655071390286</v>
       </c>
       <c r="CU46" t="n">
         <v>8</v>
@@ -29830,10 +29830,10 @@
         <v>3.7</v>
       </c>
       <c r="CX46" t="n">
-        <v>-22.56975049816726</v>
+        <v>-22.5697505212334</v>
       </c>
       <c r="CY46" t="n">
-        <v>-9.750275939558961</v>
+        <v>-9.750275790895968</v>
       </c>
       <c r="CZ46" t="inlineStr">
         <is>
@@ -30156,10 +30156,10 @@
         <v>33.34999847412109</v>
       </c>
       <c r="CJ47" t="n">
-        <v>14.44223110532837</v>
+        <v>14.44223109978265</v>
       </c>
       <c r="CK47" t="n">
-        <v>26.79033870038413</v>
+        <v>26.79033869009682</v>
       </c>
       <c r="CL47" t="n">
         <v>55.86440958054417</v>
@@ -30168,25 +30168,25 @@
         <v>43.13942726989067</v>
       </c>
       <c r="CN47" t="n">
-        <v>72.71632254625109</v>
+        <v>72.71632255312052</v>
       </c>
       <c r="CO47" t="n">
-        <v>38.50528575964233</v>
+        <v>38.50528576101282</v>
       </c>
       <c r="CP47" t="n">
-        <v>40.90342108140798</v>
+        <v>40.9034210918956</v>
       </c>
       <c r="CQ47" t="n">
         <v>21.66331906695809</v>
       </c>
       <c r="CR47" t="n">
-        <v>42.79750342929692</v>
+        <v>42.79750343050267</v>
       </c>
       <c r="CS47" t="n">
-        <v>40.90342108140798</v>
+        <v>40.9034210918956</v>
       </c>
       <c r="CT47" t="n">
-        <v>36.81307897326719</v>
+        <v>36.81307898270605</v>
       </c>
       <c r="CU47" t="n">
         <v>7</v>
@@ -30198,10 +30198,10 @@
         <v>5</v>
       </c>
       <c r="CX47" t="n">
-        <v>10.38404994780846</v>
+        <v>10.38404997611089</v>
       </c>
       <c r="CY47" t="n">
-        <v>28.32835198630337</v>
+        <v>28.32835198991881</v>
       </c>
       <c r="CZ47" t="inlineStr">
         <is>
@@ -30510,10 +30510,10 @@
         <v>6.570000171661377</v>
       </c>
       <c r="CJ48" t="n">
-        <v>7.812280576072481</v>
+        <v>7.812280647233666</v>
       </c>
       <c r="CK48" t="n">
-        <v>11.37468051876153</v>
+        <v>11.37468062237222</v>
       </c>
       <c r="CL48" t="n">
         <v>8.114964582574622</v>
@@ -30532,7 +30532,7 @@
         <v>5.379803695646386</v>
       </c>
       <c r="CR48" t="n">
-        <v>8.416219329448266</v>
+        <v>8.416219358576912</v>
       </c>
       <c r="CS48" t="n">
         <v>8.471557624874304</v>
@@ -30553,7 +30553,7 @@
         <v>16.04873155519062</v>
       </c>
       <c r="CY48" t="n">
-        <v>28.10074748171627</v>
+        <v>28.10074792507464</v>
       </c>
       <c r="CZ48" t="inlineStr">
         <is>
@@ -30846,35 +30846,35 @@
         <v>16.93000030517578</v>
       </c>
       <c r="CJ49" t="n">
-        <v>10.07593946881644</v>
+        <v>10.07593960608275</v>
       </c>
       <c r="CK49" t="n">
-        <v>17.56133915983863</v>
+        <v>17.56133913665739</v>
       </c>
       <c r="CL49" t="n">
-        <v>28.8325885130935</v>
+        <v>28.83258808224258</v>
       </c>
       <c r="CM49" t="n">
         <v>29.26650917734455</v>
       </c>
       <c r="CN49" t="n">
-        <v>32.09021934382206</v>
+        <v>32.09021933517218</v>
       </c>
       <c r="CO49" t="n">
-        <v>27.62963449401778</v>
+        <v>27.6296344633191</v>
       </c>
       <c r="CP49" t="n">
-        <v>14.228316384647</v>
+        <v>14.22831621396458</v>
       </c>
       <c r="CQ49" t="inlineStr"/>
       <c r="CR49" t="n">
-        <v>21.02487540894159</v>
+        <v>21.02487532207546</v>
       </c>
       <c r="CS49" t="n">
-        <v>22.5954868269282</v>
+        <v>22.59548679998825</v>
       </c>
       <c r="CT49" t="n">
-        <v>20.33593814423538</v>
+        <v>20.33593811998942</v>
       </c>
       <c r="CU49" t="n">
         <v>4</v>
@@ -30886,10 +30886,10 @@
         <v>2.9</v>
       </c>
       <c r="CX49" t="n">
-        <v>20.11776596376285</v>
+        <v>20.11776582054987</v>
       </c>
       <c r="CY49" t="n">
-        <v>24.18709409304578</v>
+        <v>24.18709357995585</v>
       </c>
       <c r="CZ49" t="inlineStr">
         <is>
@@ -31208,10 +31208,10 @@
         <v>32.52999877929688</v>
       </c>
       <c r="CJ50" t="n">
-        <v>11.0539601774189</v>
+        <v>11.05396013553541</v>
       </c>
       <c r="CK50" t="n">
-        <v>20.50509612911206</v>
+        <v>20.50509605141818</v>
       </c>
       <c r="CL50" t="n">
         <v>55.47264914101462</v>
@@ -31220,19 +31220,19 @@
         <v>52.30651498008846</v>
       </c>
       <c r="CN50" t="n">
-        <v>57.86673685990053</v>
+        <v>57.86673686875464</v>
       </c>
       <c r="CO50" t="n">
-        <v>28.13054896040698</v>
+        <v>28.13054885901494</v>
       </c>
       <c r="CP50" t="n">
-        <v>35.03833480437814</v>
+        <v>35.03833485737919</v>
       </c>
       <c r="CQ50" t="n">
         <v>54.48085949640561</v>
       </c>
       <c r="CR50" t="n">
-        <v>43.40010576732949</v>
+        <v>43.40010575058223</v>
       </c>
       <c r="CS50" t="n">
         <v>52.30651498008846</v>
@@ -31253,7 +31253,7 @@
         <v>44.71523285774048</v>
       </c>
       <c r="CY50" t="n">
-        <v>33.41563908988121</v>
+        <v>33.41563903839875</v>
       </c>
       <c r="CZ50" t="inlineStr">
         <is>
@@ -31288,7 +31288,7 @@
         <v>-0.823172146475537</v>
       </c>
       <c r="DL50" t="n">
-        <v>-11.18389206879866</v>
+        <v>-11.1839014300796</v>
       </c>
       <c r="DM50" t="b">
         <v>0</v>
@@ -31564,37 +31564,37 @@
         <v>44.06000137329102</v>
       </c>
       <c r="CJ51" t="n">
-        <v>31.96233902274301</v>
+        <v>31.96233910772903</v>
       </c>
       <c r="CK51" t="n">
-        <v>43.40419626504693</v>
+        <v>43.40419610462463</v>
       </c>
       <c r="CL51" t="n">
-        <v>49.69482714320432</v>
+        <v>49.69482682739612</v>
       </c>
       <c r="CM51" t="n">
         <v>47.301358204649</v>
       </c>
       <c r="CN51" t="n">
-        <v>69.17232321949791</v>
+        <v>69.17232304338198</v>
       </c>
       <c r="CO51" t="n">
-        <v>58.77995438993259</v>
+        <v>58.77995435502147</v>
       </c>
       <c r="CP51" t="n">
-        <v>24.46050917783012</v>
+        <v>24.46050898016625</v>
       </c>
       <c r="CQ51" t="n">
         <v>76.33330481362214</v>
       </c>
       <c r="CR51" t="n">
-        <v>50.13860152956575</v>
+        <v>50.13860142957382</v>
       </c>
       <c r="CS51" t="n">
-        <v>48.49809267392666</v>
+        <v>48.49809251602256</v>
       </c>
       <c r="CT51" t="n">
-        <v>43.648283406534</v>
+        <v>43.64828326442031</v>
       </c>
       <c r="CU51" t="n">
         <v>8</v>
@@ -31606,10 +31606,10 @@
         <v>3.1</v>
       </c>
       <c r="CX51" t="n">
-        <v>-0.9344483747715016</v>
+        <v>-0.9344486973173138</v>
       </c>
       <c r="CY51" t="n">
-        <v>13.79618694238069</v>
+        <v>13.79618671543581</v>
       </c>
       <c r="CZ51" t="inlineStr">
         <is>
@@ -31924,37 +31924,37 @@
         <v>10.65999984741211</v>
       </c>
       <c r="CJ52" t="n">
-        <v>8.155913722317502</v>
+        <v>8.155913709357318</v>
       </c>
       <c r="CK52" t="n">
-        <v>11.52280745218461</v>
+        <v>11.52280744863404</v>
       </c>
       <c r="CL52" t="n">
-        <v>17.21213831395306</v>
+        <v>17.21213833600043</v>
       </c>
       <c r="CM52" t="n">
         <v>24.17460734763337</v>
       </c>
       <c r="CN52" t="n">
-        <v>24.61732007122755</v>
+        <v>24.61732006262717</v>
       </c>
       <c r="CO52" t="n">
-        <v>21.03193964353841</v>
+        <v>21.03193964596731</v>
       </c>
       <c r="CP52" t="n">
-        <v>8.546606029956708</v>
+        <v>8.546606042798695</v>
       </c>
       <c r="CQ52" t="n">
         <v>9.746272614957581</v>
       </c>
       <c r="CR52" t="n">
-        <v>15.6259506494711</v>
+        <v>15.62595065099699</v>
       </c>
       <c r="CS52" t="n">
-        <v>14.36747288306883</v>
+        <v>14.36747289231724</v>
       </c>
       <c r="CT52" t="n">
-        <v>12.93072559476195</v>
+        <v>12.93072560308551</v>
       </c>
       <c r="CU52" t="n">
         <v>8</v>
@@ -31966,10 +31966,10 @@
         <v>3</v>
       </c>
       <c r="CX52" t="n">
-        <v>21.30136754083629</v>
+        <v>21.3013676189185</v>
       </c>
       <c r="CY52" t="n">
-        <v>46.58490500133126</v>
+        <v>46.58490501564543</v>
       </c>
       <c r="CZ52" t="inlineStr">
         <is>
@@ -32270,10 +32270,10 @@
         <v>53.7400016784668</v>
       </c>
       <c r="CJ53" t="n">
-        <v>10.50731956795014</v>
+        <v>10.50731956327966</v>
       </c>
       <c r="CK53" t="n">
-        <v>19.49107779854751</v>
+        <v>19.49107778988377</v>
       </c>
       <c r="CL53" t="n">
         <v>62.18821154931746</v>
@@ -32282,7 +32282,7 @@
         <v>46.54098234247379</v>
       </c>
       <c r="CN53" t="n">
-        <v>83.24912656142394</v>
+        <v>83.24912655571329</v>
       </c>
       <c r="CO53" t="n">
         <v>11.76833333333333</v>
@@ -32292,7 +32292,7 @@
       </c>
       <c r="CQ53" t="inlineStr"/>
       <c r="CR53" t="n">
-        <v>13.92224356661033</v>
+        <v>13.92224356216559</v>
       </c>
       <c r="CS53" t="n">
         <v>11.76833333333333</v>
@@ -32313,7 +32313,7 @@
         <v>-80.29121758616556</v>
       </c>
       <c r="CY53" t="n">
-        <v>-74.09333246785353</v>
+        <v>-74.09333247612435</v>
       </c>
       <c r="CZ53" t="inlineStr">
         <is>
@@ -32618,10 +32618,10 @@
         <v>29.46999931335449</v>
       </c>
       <c r="CJ54" t="n">
-        <v>15.40499614525348</v>
+        <v>15.40499610458543</v>
       </c>
       <c r="CK54" t="n">
-        <v>28.57626784944521</v>
+        <v>28.57626777400598</v>
       </c>
       <c r="CL54" t="n">
         <v>53.78477836114972</v>
@@ -32630,23 +32630,23 @@
         <v>48.59041952862963</v>
       </c>
       <c r="CN54" t="n">
-        <v>59.55728564090104</v>
+        <v>59.55728565180924</v>
       </c>
       <c r="CO54" t="n">
-        <v>36.60763962993459</v>
+        <v>36.60763963743898</v>
       </c>
       <c r="CP54" t="n">
-        <v>29.60722465810817</v>
+        <v>29.60722471425936</v>
       </c>
       <c r="CQ54" t="inlineStr"/>
       <c r="CR54" t="n">
-        <v>33.59342049644575</v>
+        <v>33.59342046929503</v>
       </c>
       <c r="CS54" t="n">
-        <v>32.5919537396899</v>
+        <v>32.59195370572248</v>
       </c>
       <c r="CT54" t="n">
-        <v>29.33275836572091</v>
+        <v>29.33275833515023</v>
       </c>
       <c r="CU54" t="n">
         <v>4</v>
@@ -32658,10 +32658,10 @@
         <v>3.5</v>
       </c>
       <c r="CX54" t="n">
-        <v>-0.4656971524644393</v>
+        <v>-0.4656972561993489</v>
       </c>
       <c r="CY54" t="n">
-        <v>13.99192833106959</v>
+        <v>13.99192823893953</v>
       </c>
       <c r="CZ54" t="inlineStr">
         <is>
@@ -32978,10 +32978,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="CJ55" t="n">
-        <v>12.95070196212595</v>
+        <v>12.95070191627523</v>
       </c>
       <c r="CK55" t="n">
-        <v>18.85622205685539</v>
+        <v>18.85622199009674</v>
       </c>
       <c r="CL55" t="n">
         <v>16.51297649354425</v>
@@ -32991,7 +32991,7 @@
       </c>
       <c r="CN55" t="inlineStr"/>
       <c r="CO55" t="n">
-        <v>13.95326101288333</v>
+        <v>14.12767677554437</v>
       </c>
       <c r="CP55" t="n">
         <v>4.241657423479087</v>
@@ -33000,7 +33000,7 @@
         <v>14.71449508364002</v>
       </c>
       <c r="CR55" t="n">
-        <v>15.99671598258106</v>
+        <v>16.02578525758967</v>
       </c>
       <c r="CS55" t="n">
         <v>15.61373578859213</v>
@@ -33021,7 +33021,7 @@
         <v>35.11887235740878</v>
       </c>
       <c r="CY55" t="n">
-        <v>53.81458239747236</v>
+        <v>54.09409466742301</v>
       </c>
       <c r="CZ55" t="inlineStr">
         <is>
@@ -33336,10 +33336,10 @@
         <v>33.16999816894531</v>
       </c>
       <c r="CJ56" t="n">
-        <v>11.720425091924</v>
+        <v>11.72042511594483</v>
       </c>
       <c r="CK56" t="n">
-        <v>21.74138854551903</v>
+        <v>21.74138859007767</v>
       </c>
       <c r="CL56" t="n">
         <v>40.50714062106224</v>
@@ -33348,25 +33348,25 @@
         <v>33.04065851780371</v>
       </c>
       <c r="CN56" t="n">
-        <v>42.38658027948908</v>
+        <v>42.38658024574756</v>
       </c>
       <c r="CO56" t="n">
-        <v>23.49250437719221</v>
+        <v>23.4925043726249</v>
       </c>
       <c r="CP56" t="n">
-        <v>25.3039647483814</v>
+        <v>25.30396470769012</v>
       </c>
       <c r="CQ56" t="n">
         <v>26.88952120736854</v>
       </c>
       <c r="CR56" t="n">
-        <v>28.13527292359253</v>
+        <v>28.13527292228995</v>
       </c>
       <c r="CS56" t="n">
-        <v>26.09674297787497</v>
+        <v>26.09674295752933</v>
       </c>
       <c r="CT56" t="n">
-        <v>23.48706868008747</v>
+        <v>23.48706866177639</v>
       </c>
       <c r="CU56" t="n">
         <v>8</v>
@@ -33378,10 +33378,10 @@
         <v>3.6</v>
       </c>
       <c r="CX56" t="n">
-        <v>-29.19183003731146</v>
+        <v>-29.1918300925152</v>
       </c>
       <c r="CY56" t="n">
-        <v>-15.17855147205416</v>
+        <v>-15.17855147598114</v>
       </c>
       <c r="CZ56" t="inlineStr">
         <is>
@@ -33688,10 +33688,10 @@
         <v>24.18000030517578</v>
       </c>
       <c r="CJ57" t="n">
-        <v>4.240146147937589</v>
+        <v>4.240146144826243</v>
       </c>
       <c r="CK57" t="n">
-        <v>7.865471104424226</v>
+        <v>7.865471098652681</v>
       </c>
       <c r="CL57" t="n">
         <v>28.58028582012302</v>
@@ -33700,13 +33700,13 @@
         <v>28.44859048200662</v>
       </c>
       <c r="CN57" t="n">
-        <v>25.50998699849393</v>
+        <v>25.50998700024037</v>
       </c>
       <c r="CO57" t="n">
-        <v>2.971261370054368</v>
+        <v>2.971261370125303</v>
       </c>
       <c r="CP57" t="n">
-        <v>18.46855615786347</v>
+        <v>18.46855616140368</v>
       </c>
       <c r="CQ57" t="n">
         <v>17.91045698312367</v>
@@ -34042,10 +34042,10 @@
         <v>50.25</v>
       </c>
       <c r="CJ58" t="n">
-        <v>8.363254056478963</v>
+        <v>8.363254038129242</v>
       </c>
       <c r="CK58" t="n">
-        <v>15.51383627476847</v>
+        <v>15.51383624072974</v>
       </c>
       <c r="CL58" t="n">
         <v>19.85129695885509</v>
@@ -34054,25 +34054,25 @@
         <v>12.34222338033302</v>
       </c>
       <c r="CN58" t="n">
-        <v>14.3460321347705</v>
+        <v>14.34603221229785</v>
       </c>
       <c r="CO58" t="n">
-        <v>20.79323226770526</v>
+        <v>20.79323227872933</v>
       </c>
       <c r="CP58" t="n">
-        <v>10.82557538308965</v>
+        <v>10.8255754366356</v>
       </c>
       <c r="CQ58" t="n">
         <v>13.23570535215743</v>
       </c>
       <c r="CR58" t="n">
-        <v>14.4088944760198</v>
+        <v>14.40889448723341</v>
       </c>
       <c r="CS58" t="n">
-        <v>13.79086874346397</v>
+        <v>13.79086878222764</v>
       </c>
       <c r="CT58" t="n">
-        <v>12.41178186911757</v>
+        <v>12.41178190400488</v>
       </c>
       <c r="CU58" t="n">
         <v>8</v>
@@ -34084,10 +34084,10 @@
         <v>2.5</v>
       </c>
       <c r="CX58" t="n">
-        <v>-75.2999365788705</v>
+        <v>-75.29993650944303</v>
       </c>
       <c r="CY58" t="n">
-        <v>-71.3255831322989</v>
+        <v>-71.32558310998324</v>
       </c>
       <c r="CZ58" t="inlineStr">
         <is>
@@ -34416,10 +34416,10 @@
         <v>4.760000228881836</v>
       </c>
       <c r="CJ59" t="n">
-        <v>1.10125697030609</v>
+        <v>1.10125696044029</v>
       </c>
       <c r="CK59" t="n">
-        <v>2.042831679917796</v>
+        <v>2.042831661616738</v>
       </c>
       <c r="CL59" t="n">
         <v>9.302360329304472</v>
@@ -34428,13 +34428,13 @@
         <v>8.759319099989012</v>
       </c>
       <c r="CN59" t="n">
-        <v>10.2293295664033</v>
+        <v>10.22932956608664</v>
       </c>
       <c r="CO59" t="n">
-        <v>4.217909909961553</v>
+        <v>4.217909911043806</v>
       </c>
       <c r="CP59" t="n">
-        <v>6.876020533800642</v>
+        <v>6.876020546406767</v>
       </c>
       <c r="CQ59" t="n">
         <v>6.539351670742607</v>
@@ -34486,7 +34486,7 @@
         <v>2.586214781232954</v>
       </c>
       <c r="DL59" t="n">
-        <v>-34.27075641632828</v>
+        <v>-34.27075202300205</v>
       </c>
       <c r="DM59" t="b">
         <v>0</v>
@@ -34762,37 +34762,37 @@
         <v>24.3700008392334</v>
       </c>
       <c r="CJ60" t="n">
-        <v>10.76553943163347</v>
+        <v>10.76553938301822</v>
       </c>
       <c r="CK60" t="n">
-        <v>14.158777331863</v>
+        <v>14.15877735782661</v>
       </c>
       <c r="CL60" t="n">
-        <v>17.23929054987344</v>
+        <v>17.23929065933547</v>
       </c>
       <c r="CM60" t="n">
         <v>21.14737695048065</v>
       </c>
       <c r="CN60" t="n">
-        <v>16.91392918072425</v>
+        <v>16.91392924497335</v>
       </c>
       <c r="CO60" t="n">
-        <v>22.7886029085935</v>
+        <v>22.78860292251445</v>
       </c>
       <c r="CP60" t="n">
-        <v>8.40013442978832</v>
+        <v>8.400134502388392</v>
       </c>
       <c r="CQ60" t="n">
         <v>18.63306280322801</v>
       </c>
       <c r="CR60" t="n">
-        <v>16.25583919827308</v>
+        <v>16.25583922797065</v>
       </c>
       <c r="CS60" t="n">
-        <v>17.07660986529885</v>
+        <v>17.07660995215441</v>
       </c>
       <c r="CT60" t="n">
-        <v>15.36894887876896</v>
+        <v>15.36894895693897</v>
       </c>
       <c r="CU60" t="n">
         <v>8</v>
@@ -34804,10 +34804,10 @@
         <v>2.7</v>
       </c>
       <c r="CX60" t="n">
-        <v>-36.93496779029073</v>
+        <v>-36.93496746952748</v>
       </c>
       <c r="CY60" t="n">
-        <v>-33.29569701079897</v>
+        <v>-33.29569688893781</v>
       </c>
       <c r="CZ60" t="inlineStr">
         <is>
@@ -35118,10 +35118,10 @@
         <v>4.409999847412109</v>
       </c>
       <c r="CJ61" t="n">
-        <v>2.864148126771817</v>
+        <v>2.864148121029345</v>
       </c>
       <c r="CK61" t="n">
-        <v>5.31299477516172</v>
+        <v>5.312994764509434</v>
       </c>
       <c r="CL61" t="n">
         <v>13.62062889934975</v>
@@ -35130,13 +35130,13 @@
         <v>15.2256151851382</v>
       </c>
       <c r="CN61" t="n">
-        <v>15.79234044163809</v>
+        <v>15.79234043116266</v>
       </c>
       <c r="CO61" t="n">
-        <v>9.861587028239244</v>
+        <v>9.861587028985307</v>
       </c>
       <c r="CP61" t="n">
-        <v>6.797592098362411</v>
+        <v>6.79759210355728</v>
       </c>
       <c r="CQ61" t="n">
         <v>1.534123064462555</v>
@@ -35464,37 +35464,37 @@
         <v>29.38999938964844</v>
       </c>
       <c r="CJ62" t="n">
-        <v>13.71847494278794</v>
+        <v>13.71847511261151</v>
       </c>
       <c r="CK62" t="n">
-        <v>14.34620341251251</v>
+        <v>14.34620344783268</v>
       </c>
       <c r="CL62" t="n">
-        <v>15.16121929449509</v>
+        <v>15.16121914413825</v>
       </c>
       <c r="CM62" t="n">
         <v>30.32006495022776</v>
       </c>
       <c r="CN62" t="n">
-        <v>14.36027033180938</v>
+        <v>14.36027025706168</v>
       </c>
       <c r="CO62" t="n">
-        <v>30.4690584004587</v>
+        <v>30.46905836478237</v>
       </c>
       <c r="CP62" t="n">
-        <v>6.111449047858403</v>
+        <v>6.111448897666443</v>
       </c>
       <c r="CQ62" t="n">
         <v>37.5668789909021</v>
       </c>
       <c r="CR62" t="n">
-        <v>17.78382005430711</v>
+        <v>17.78382002490296</v>
       </c>
       <c r="CS62" t="n">
-        <v>14.36027033180938</v>
+        <v>14.36027025706168</v>
       </c>
       <c r="CT62" t="n">
-        <v>12.92424329862844</v>
+        <v>12.92424323135551</v>
       </c>
       <c r="CU62" t="n">
         <v>7</v>
@@ -35506,10 +35506,10 @@
         <v>6.1</v>
       </c>
       <c r="CX62" t="n">
-        <v>-56.0250303945888</v>
+        <v>-56.02503062348614</v>
       </c>
       <c r="CY62" t="n">
-        <v>-39.49023333232591</v>
+        <v>-39.49023343237405</v>
       </c>
       <c r="CZ62" t="inlineStr">
         <is>
@@ -35544,7 +35544,7 @@
         <v>-4.508006105756812</v>
       </c>
       <c r="DL62" t="n">
-        <v>-28.45091748718991</v>
+        <v>-28.45092417641193</v>
       </c>
       <c r="DM62" t="b">
         <v>0</v>
@@ -36190,37 +36190,37 @@
         <v>18.73999977111816</v>
       </c>
       <c r="CJ64" t="n">
-        <v>8.790659640692011</v>
+        <v>8.790659630786015</v>
       </c>
       <c r="CK64" t="n">
-        <v>9.149702328356627</v>
+        <v>9.149702328877998</v>
       </c>
       <c r="CL64" t="n">
-        <v>9.503707803063788</v>
+        <v>9.503707814314847</v>
       </c>
       <c r="CM64" t="n">
         <v>16.79875791329259</v>
       </c>
       <c r="CN64" t="n">
-        <v>9.013907502659793</v>
+        <v>9.013907511228686</v>
       </c>
       <c r="CO64" t="n">
-        <v>17.3677507839341</v>
+        <v>17.36775078637179</v>
       </c>
       <c r="CP64" t="n">
-        <v>3.803999721349142</v>
+        <v>3.803999732681604</v>
       </c>
       <c r="CQ64" t="n">
         <v>16.19033501601518</v>
       </c>
       <c r="CR64" t="n">
-        <v>11.3273525886704</v>
+        <v>11.32735259169609</v>
       </c>
       <c r="CS64" t="n">
-        <v>9.326705065710208</v>
+        <v>9.326705071596422</v>
       </c>
       <c r="CT64" t="n">
-        <v>8.394034559139188</v>
+        <v>8.39403456443678</v>
       </c>
       <c r="CU64" t="n">
         <v>8</v>
@@ -36232,10 +36232,10 @@
         <v>4.6</v>
       </c>
       <c r="CX64" t="n">
-        <v>-55.20792603169633</v>
+        <v>-55.20792600342742</v>
       </c>
       <c r="CY64" t="n">
-        <v>-39.55521490385519</v>
+        <v>-39.55521488770957</v>
       </c>
       <c r="CZ64" t="inlineStr">
         <is>
@@ -36558,10 +36558,10 @@
         <v>8.199999809265137</v>
       </c>
       <c r="CJ65" t="n">
-        <v>0.4878659188433072</v>
+        <v>0.4878659172825146</v>
       </c>
       <c r="CK65" t="n">
-        <v>0.9049912794543348</v>
+        <v>0.9049912765590645</v>
       </c>
       <c r="CL65" t="n">
         <v>9.48908274871293</v>
@@ -36570,13 +36570,13 @@
         <v>8.714204226367567</v>
       </c>
       <c r="CN65" t="n">
-        <v>10.4504064314307</v>
+        <v>10.45040643284586</v>
       </c>
       <c r="CO65" t="n">
-        <v>0.736097797219379</v>
+        <v>0.736097797249408</v>
       </c>
       <c r="CP65" t="n">
-        <v>8.107035955682957</v>
+        <v>8.107035957772045</v>
       </c>
       <c r="CQ65" t="inlineStr"/>
       <c r="CR65" t="inlineStr"/>
@@ -36910,10 +36910,10 @@
         <v>35.31000137329102</v>
       </c>
       <c r="CJ66" t="n">
-        <v>10.11005125137146</v>
+        <v>10.11005123103499</v>
       </c>
       <c r="CK66" t="n">
-        <v>18.75414507129405</v>
+        <v>18.75414503356989</v>
       </c>
       <c r="CL66" t="n">
         <v>28.42390754532843</v>
@@ -36922,25 +36922,25 @@
         <v>21.09476497433801</v>
       </c>
       <c r="CN66" t="n">
-        <v>25.57406588887052</v>
+        <v>25.57406593779709</v>
       </c>
       <c r="CO66" t="n">
-        <v>22.76792270071332</v>
+        <v>22.76792270722653</v>
       </c>
       <c r="CP66" t="n">
-        <v>16.40074654167348</v>
+        <v>16.40074658329981</v>
       </c>
       <c r="CQ66" t="n">
         <v>26.23735511627599</v>
       </c>
       <c r="CR66" t="n">
-        <v>21.17036988623316</v>
+        <v>21.17036989110884</v>
       </c>
       <c r="CS66" t="n">
-        <v>21.93134383752566</v>
+        <v>21.93134384078227</v>
       </c>
       <c r="CT66" t="n">
-        <v>19.7382094537731</v>
+        <v>19.73820945670404</v>
       </c>
       <c r="CU66" t="n">
         <v>8</v>
@@ -36952,10 +36952,10 @@
         <v>2.8</v>
       </c>
       <c r="CX66" t="n">
-        <v>-44.1002302857361</v>
+        <v>-44.10023027743549</v>
       </c>
       <c r="CY66" t="n">
-        <v>-40.04426773473103</v>
+        <v>-40.04426772092281</v>
       </c>
       <c r="CZ66" t="inlineStr">
         <is>
@@ -37272,25 +37272,25 @@
         <v>2.230000019073486</v>
       </c>
       <c r="CJ67" t="n">
-        <v>0.6401421983704806</v>
+        <v>0.6401421986166664</v>
       </c>
       <c r="CK67" t="n">
-        <v>0.9077766957298101</v>
+        <v>0.9077766960282447</v>
       </c>
       <c r="CL67" t="n">
-        <v>3.427630423461861</v>
+        <v>3.427630423270509</v>
       </c>
       <c r="CM67" t="n">
         <v>7.066656151822504</v>
       </c>
       <c r="CN67" t="n">
-        <v>2.631160765163185</v>
+        <v>2.631160765510069</v>
       </c>
       <c r="CO67" t="n">
-        <v>2.231183282150885</v>
+        <v>2.231183282139693</v>
       </c>
       <c r="CP67" t="n">
-        <v>1.703043106085504</v>
+        <v>1.703043105974799</v>
       </c>
       <c r="CQ67" t="n">
         <v>7.171516514635575</v>
@@ -37596,10 +37596,10 @@
         <v>12.86999988555908</v>
       </c>
       <c r="CJ68" t="n">
-        <v>10.8840950702793</v>
+        <v>10.8840950185404</v>
       </c>
       <c r="CK68" t="n">
-        <v>15.84724242232666</v>
+        <v>15.84724234699483</v>
       </c>
       <c r="CL68" t="n">
         <v>15.47375708783982</v>
@@ -37616,13 +37616,13 @@
       </c>
       <c r="CQ68" t="inlineStr"/>
       <c r="CR68" t="n">
-        <v>12.38460697844478</v>
+        <v>12.3846069466771</v>
       </c>
       <c r="CS68" t="n">
-        <v>13.17892607905956</v>
+        <v>13.17892605319011</v>
       </c>
       <c r="CT68" t="n">
-        <v>11.86103347115361</v>
+        <v>11.8610334478711</v>
       </c>
       <c r="CU68" t="n">
         <v>4</v>
@@ -37634,10 +37634,10 @@
         <v>2.2</v>
       </c>
       <c r="CX68" t="n">
-        <v>-7.839676949318375</v>
+        <v>-7.839677130223633</v>
       </c>
       <c r="CY68" t="n">
-        <v>-3.771506693321269</v>
+        <v>-3.771506940156433</v>
       </c>
       <c r="CZ68" t="inlineStr">
         <is>
@@ -37948,10 +37948,10 @@
         <v>8.329999923706055</v>
       </c>
       <c r="CJ69" t="n">
-        <v>1.605082993522053</v>
+        <v>1.605082991390146</v>
       </c>
       <c r="CK69" t="n">
-        <v>2.977428952983407</v>
+        <v>2.977428949028721</v>
       </c>
       <c r="CL69" t="n">
         <v>24.04629607605778</v>
@@ -37960,13 +37960,13 @@
         <v>23.80972001921325</v>
       </c>
       <c r="CN69" t="n">
-        <v>25.67832652672064</v>
+        <v>25.67832652411906</v>
       </c>
       <c r="CO69" t="n">
-        <v>6.709160235195411</v>
+        <v>6.709160235324807</v>
       </c>
       <c r="CP69" t="n">
-        <v>17.91152719284142</v>
+        <v>17.91152719529346</v>
       </c>
       <c r="CQ69" t="n">
         <v>14.80472650453005</v>
@@ -38302,10 +38302,10 @@
         <v>21.25</v>
       </c>
       <c r="CJ70" t="n">
-        <v>5.876635916879793</v>
+        <v>5.876635895694473</v>
       </c>
       <c r="CK70" t="n">
-        <v>10.90115962581202</v>
+        <v>10.90115958651325</v>
       </c>
       <c r="CL70" t="n">
         <v>32.70180023228804</v>
@@ -38314,25 +38314,25 @@
         <v>33.68464293302805</v>
       </c>
       <c r="CN70" t="n">
-        <v>29.46401509087266</v>
+        <v>29.46401509231292</v>
       </c>
       <c r="CO70" t="n">
-        <v>25.11816867768864</v>
+        <v>25.11816868106843</v>
       </c>
       <c r="CP70" t="n">
-        <v>19.10716733404388</v>
+        <v>19.10716735660201</v>
       </c>
       <c r="CQ70" t="n">
         <v>13.22580990542387</v>
       </c>
       <c r="CR70" t="n">
-        <v>23.45753768559388</v>
+        <v>23.45753768389094</v>
       </c>
       <c r="CS70" t="n">
-        <v>25.11816867768864</v>
+        <v>25.11816868106843</v>
       </c>
       <c r="CT70" t="n">
-        <v>22.60635180991978</v>
+        <v>22.60635181296159</v>
       </c>
       <c r="CU70" t="n">
         <v>7</v>
@@ -38344,10 +38344,10 @@
         <v>5.7</v>
       </c>
       <c r="CX70" t="n">
-        <v>6.382832046681308</v>
+        <v>6.382832060995725</v>
       </c>
       <c r="CY70" t="n">
-        <v>10.38841263808883</v>
+        <v>10.388412630075</v>
       </c>
       <c r="CZ70" t="inlineStr">
         <is>
@@ -38658,25 +38658,25 @@
         <v>17.14999961853027</v>
       </c>
       <c r="CJ71" t="n">
-        <v>3.991825544547093</v>
+        <v>3.991825579895171</v>
       </c>
       <c r="CK71" t="n">
-        <v>6.867699802656627</v>
+        <v>6.867699846386528</v>
       </c>
       <c r="CL71" t="n">
-        <v>23.5742731070989</v>
+        <v>23.57427304845456</v>
       </c>
       <c r="CM71" t="n">
         <v>32.99378636564864</v>
       </c>
       <c r="CN71" t="n">
-        <v>16.6512710280782</v>
+        <v>16.65127104557533</v>
       </c>
       <c r="CO71" t="n">
-        <v>20.30231638082625</v>
+        <v>20.3023163770257</v>
       </c>
       <c r="CP71" t="n">
-        <v>11.6619197264765</v>
+        <v>11.66191970268017</v>
       </c>
       <c r="CQ71" t="n">
         <v>22.29340682675621</v>
@@ -38728,7 +38728,7 @@
         <v>-1.773638241028741</v>
       </c>
       <c r="DL71" t="n">
-        <v>-40.59847068549305</v>
+        <v>-40.59847466912285</v>
       </c>
       <c r="DM71" t="b">
         <v>0</v>
@@ -39004,10 +39004,10 @@
         <v>3.970000028610229</v>
       </c>
       <c r="CJ72" t="n">
-        <v>0.963039003020938</v>
+        <v>0.9630390068571858</v>
       </c>
       <c r="CK72" t="n">
-        <v>1.78643735060384</v>
+        <v>1.78643735772008</v>
       </c>
       <c r="CL72" t="n">
         <v>6.217789642917912</v>
@@ -39016,7 +39016,7 @@
         <v>4.127898727162465</v>
       </c>
       <c r="CN72" t="n">
-        <v>8.632688708208814</v>
+        <v>8.632688714557215</v>
       </c>
       <c r="CO72" t="n">
         <v>3.856907976544537</v>
@@ -39074,7 +39074,7 @@
         <v>-3.17072875722394</v>
       </c>
       <c r="DL72" t="n">
-        <v>-45.72659463574499</v>
+        <v>-45.72659102148787</v>
       </c>
       <c r="DM72" t="b">
         <v>0</v>
@@ -39350,35 +39350,35 @@
         <v>24.02000045776367</v>
       </c>
       <c r="CJ73" t="n">
-        <v>23.07830347489803</v>
+        <v>23.07830349855749</v>
       </c>
       <c r="CK73" t="n">
-        <v>28.90113962937307</v>
+        <v>28.90113963574514</v>
       </c>
       <c r="CL73" t="n">
-        <v>37.96117379287505</v>
+        <v>37.96117376232756</v>
       </c>
       <c r="CM73" t="n">
         <v>61.82732111992195</v>
       </c>
       <c r="CN73" t="n">
-        <v>67.85077928360379</v>
+        <v>67.85077930691541</v>
       </c>
       <c r="CO73" t="n">
-        <v>41.58975971529487</v>
+        <v>41.58975971192964</v>
       </c>
       <c r="CP73" t="n">
-        <v>18.10465224092203</v>
+        <v>18.10465221879003</v>
       </c>
       <c r="CQ73" t="inlineStr"/>
       <c r="CR73" t="n">
-        <v>39.90187560812696</v>
+        <v>39.90187560774103</v>
       </c>
       <c r="CS73" t="n">
-        <v>37.96117379287505</v>
+        <v>37.96117376232756</v>
       </c>
       <c r="CT73" t="n">
-        <v>34.16505641358755</v>
+        <v>34.1650563860948</v>
       </c>
       <c r="CU73" t="n">
         <v>7</v>
@@ -39390,10 +39390,10 @@
         <v>3.7</v>
       </c>
       <c r="CX73" t="n">
-        <v>42.2358691194147</v>
+        <v>42.235869004957</v>
       </c>
       <c r="CY73" t="n">
-        <v>66.11937904951206</v>
+        <v>66.11937904790533</v>
       </c>
       <c r="CZ73" t="inlineStr">
         <is>
@@ -39708,10 +39708,10 @@
         <v>25.07999992370605</v>
       </c>
       <c r="CJ74" t="n">
-        <v>4.600671626105012</v>
+        <v>4.600671628443599</v>
       </c>
       <c r="CK74" t="n">
-        <v>8.534245866424795</v>
+        <v>8.534245870762875</v>
       </c>
       <c r="CL74" t="n">
         <v>30.04611202433139</v>
@@ -39720,19 +39720,19 @@
         <v>25.48637760632342</v>
       </c>
       <c r="CN74" t="n">
-        <v>34.72259478943148</v>
+        <v>34.72259478656395</v>
       </c>
       <c r="CO74" t="n">
-        <v>11.67921020987782</v>
+        <v>11.77818656732017</v>
       </c>
       <c r="CP74" t="n">
-        <v>24.22287495786783</v>
+        <v>24.22287495420467</v>
       </c>
       <c r="CQ74" t="n">
         <v>25.07999992370605</v>
       </c>
       <c r="CR74" t="n">
-        <v>25.20619491858967</v>
+        <v>25.22269097707494</v>
       </c>
       <c r="CS74" t="n">
         <v>25.28318876501474</v>
@@ -39753,7 +39753,7 @@
         <v>-9.270853438061765</v>
       </c>
       <c r="CY74" t="n">
-        <v>0.5031698375897342</v>
+        <v>0.5689435957055844</v>
       </c>
       <c r="CZ74" t="inlineStr">
         <is>
@@ -40072,10 +40072,10 @@
         <v>12.42000007629395</v>
       </c>
       <c r="CJ75" t="n">
-        <v>2.054914839778009</v>
+        <v>2.054914839222684</v>
       </c>
       <c r="CK75" t="n">
-        <v>3.811867027788206</v>
+        <v>3.81186702675808</v>
       </c>
       <c r="CL75" t="n">
         <v>15.91537727378093</v>
@@ -40084,7 +40084,7 @@
         <v>12.64279048217724</v>
       </c>
       <c r="CN75" t="n">
-        <v>20.79969138310458</v>
+        <v>20.79969138235269</v>
       </c>
       <c r="CO75" t="n">
         <v>9.294207014285712</v>
@@ -40416,10 +40416,10 @@
         <v>55.20000076293945</v>
       </c>
       <c r="CJ76" t="n">
-        <v>40.14456963379362</v>
+        <v>40.14456976136904</v>
       </c>
       <c r="CK76" t="n">
-        <v>58.45049338680352</v>
+        <v>58.45049357255333</v>
       </c>
       <c r="CL76" t="n">
         <v>35.6793044086122</v>
@@ -40438,13 +40438,13 @@
         <v>48.81663041531538</v>
       </c>
       <c r="CR76" t="n">
-        <v>43.29518130621127</v>
+        <v>43.29518135843213</v>
       </c>
       <c r="CS76" t="n">
-        <v>41.36290899911504</v>
+        <v>41.36290906290274</v>
       </c>
       <c r="CT76" t="n">
-        <v>37.22661809920353</v>
+        <v>37.22661815661247</v>
       </c>
       <c r="CU76" t="n">
         <v>6</v>
@@ -40456,10 +40456,10 @@
         <v>6.4</v>
       </c>
       <c r="CX76" t="n">
-        <v>-32.56047539007102</v>
+        <v>-32.56047528606933</v>
       </c>
       <c r="CY76" t="n">
-        <v>-21.56670161628136</v>
+        <v>-21.56670152167834</v>
       </c>
       <c r="CZ76" t="inlineStr">
         <is>
@@ -40770,10 +40770,10 @@
         <v>28.85000038146973</v>
       </c>
       <c r="CJ77" t="n">
-        <v>13.47826689465524</v>
+        <v>13.47826685348382</v>
       </c>
       <c r="CK77" t="n">
-        <v>25.00218508958547</v>
+        <v>25.00218501321249</v>
       </c>
       <c r="CL77" t="n">
         <v>37.07686760955129</v>
@@ -40782,19 +40782,19 @@
         <v>25.84183193227743</v>
       </c>
       <c r="CN77" t="n">
-        <v>42.3331017452885</v>
+        <v>42.33310184137828</v>
       </c>
       <c r="CO77" t="n">
-        <v>42.16403727291196</v>
+        <v>42.16403729400348</v>
       </c>
       <c r="CP77" t="n">
-        <v>22.58047102668684</v>
+        <v>22.58047112222758</v>
       </c>
       <c r="CQ77" t="n">
         <v>25.39446734308974</v>
       </c>
       <c r="CR77" t="n">
-        <v>29.23390361425581</v>
+        <v>29.23390362615302</v>
       </c>
       <c r="CS77" t="n">
         <v>25.61814963768359</v>
@@ -40815,7 +40815,7 @@
         <v>-20.08202991662958</v>
       </c>
       <c r="CY77" t="n">
-        <v>1.330687097781325</v>
+        <v>1.330687139019471</v>
       </c>
       <c r="CZ77" t="inlineStr">
         <is>
@@ -41134,10 +41134,10 @@
         <v>15.07999992370605</v>
       </c>
       <c r="CJ78" t="n">
-        <v>2.43344312506592</v>
+        <v>2.433443121555086</v>
       </c>
       <c r="CK78" t="n">
-        <v>4.514036996997282</v>
+        <v>4.514036990484685</v>
       </c>
       <c r="CL78" t="n">
         <v>25.45350305593697</v>
@@ -41146,7 +41146,7 @@
         <v>19.52359161971606</v>
       </c>
       <c r="CN78" t="n">
-        <v>33.15518504541576</v>
+        <v>33.1551850391544</v>
       </c>
       <c r="CO78" t="n">
         <v>10.38593205872702</v>
@@ -41480,10 +41480,10 @@
         <v>14.56999969482422</v>
       </c>
       <c r="CJ79" t="n">
-        <v>9.52214931156133</v>
+        <v>9.522149329816033</v>
       </c>
       <c r="CK79" t="n">
-        <v>17.66358697294627</v>
+        <v>17.66358700680874</v>
       </c>
       <c r="CL79" t="n">
         <v>13.81907630325131</v>
@@ -41504,7 +41504,7 @@
         <v>12.2203515982404</v>
       </c>
       <c r="CR79" t="n">
-        <v>14.92971999312659</v>
+        <v>14.92971999964124</v>
       </c>
       <c r="CS79" t="n">
         <v>13.18184499442705</v>
@@ -41525,7 +41525,7 @@
         <v>-18.57473751904922</v>
       </c>
       <c r="CY79" t="n">
-        <v>2.468910815627234</v>
+        <v>2.468910860340001</v>
       </c>
       <c r="CZ79" t="inlineStr">
         <is>
@@ -41836,25 +41836,25 @@
         <v>26.20999908447266</v>
       </c>
       <c r="CJ80" t="n">
-        <v>11.93854588298402</v>
+        <v>11.93854590207555</v>
       </c>
       <c r="CK80" t="n">
-        <v>12.6158079204679</v>
+        <v>12.6158079293247</v>
       </c>
       <c r="CL80" t="n">
-        <v>13.88314120857086</v>
+        <v>13.88314119611614</v>
       </c>
       <c r="CM80" t="n">
         <v>32.29491627828039</v>
       </c>
       <c r="CN80" t="n">
-        <v>12.94974348843167</v>
+        <v>12.9497434877569</v>
       </c>
       <c r="CO80" t="n">
-        <v>24.67209428335043</v>
+        <v>24.67209428076111</v>
       </c>
       <c r="CP80" t="n">
-        <v>5.68081677406004</v>
+        <v>5.680816761846039</v>
       </c>
       <c r="CQ80" t="n">
         <v>61.56724104958222</v>
@@ -41906,7 +41906,7 @@
         <v>-2.04474013597955</v>
       </c>
       <c r="DL80" t="n">
-        <v>-19.17219117353147</v>
+        <v>-19.17220078617631</v>
       </c>
       <c r="DM80" t="b">
         <v>0</v>
@@ -42182,10 +42182,10 @@
         <v>6.960000038146973</v>
       </c>
       <c r="CJ81" t="n">
-        <v>1.25432438371691</v>
+        <v>1.254324383913709</v>
       </c>
       <c r="CK81" t="n">
-        <v>2.326771731794868</v>
+        <v>2.326771732159931</v>
       </c>
       <c r="CL81" t="n">
         <v>10.46765045464783</v>
@@ -42194,13 +42194,13 @@
         <v>10.28299479481327</v>
       </c>
       <c r="CN81" t="n">
-        <v>10.15256190813501</v>
+        <v>10.15256190808186</v>
       </c>
       <c r="CO81" t="n">
-        <v>1.873720564858048</v>
+        <v>1.873720564850183</v>
       </c>
       <c r="CP81" t="n">
-        <v>7.239168614939716</v>
+        <v>7.239168614709728</v>
       </c>
       <c r="CQ81" t="n">
         <v>11.45586349250206</v>
@@ -42528,10 +42528,10 @@
         <v>10.44999980926514</v>
       </c>
       <c r="CJ82" t="n">
-        <v>6.405398456774406</v>
+        <v>6.405398443240237</v>
       </c>
       <c r="CK82" t="n">
-        <v>11.88201413731652</v>
+        <v>11.88201411221064</v>
       </c>
       <c r="CL82" t="n">
         <v>7.980547404770202</v>
@@ -42552,7 +42552,7 @@
         <v>39.67377387971943</v>
       </c>
       <c r="CR82" t="n">
-        <v>10.2515615472606</v>
+        <v>10.25156154174059</v>
       </c>
       <c r="CS82" t="n">
         <v>7.980547404770202</v>
@@ -42573,7 +42573,7 @@
         <v>-31.26801152737755</v>
       </c>
       <c r="CY82" t="n">
-        <v>-1.898930771545082</v>
+        <v>-1.898930824368128</v>
       </c>
       <c r="CZ82" t="inlineStr">
         <is>
@@ -42884,35 +42884,35 @@
         <v>2.779999971389771</v>
       </c>
       <c r="CJ83" t="n">
-        <v>1.278437329055655</v>
+        <v>1.278437327266242</v>
       </c>
       <c r="CK83" t="n">
-        <v>1.746572825244264</v>
+        <v>1.746572823551555</v>
       </c>
       <c r="CL83" t="n">
-        <v>3.757394660048575</v>
+        <v>3.757394661666235</v>
       </c>
       <c r="CM83" t="n">
         <v>7.235833015165504</v>
       </c>
       <c r="CN83" t="n">
-        <v>3.789507992903873</v>
+        <v>3.789507991027392</v>
       </c>
       <c r="CO83" t="n">
-        <v>1.340404108695225</v>
+        <v>1.340404108748865</v>
       </c>
       <c r="CP83" t="n">
-        <v>1.852381280445798</v>
+        <v>1.852381281447297</v>
       </c>
       <c r="CQ83" t="inlineStr"/>
       <c r="CR83" t="n">
-        <v>2.294116366065565</v>
+        <v>2.294116365617931</v>
       </c>
       <c r="CS83" t="n">
-        <v>1.799477052845031</v>
+        <v>1.799477052499426</v>
       </c>
       <c r="CT83" t="n">
-        <v>1.619529347560528</v>
+        <v>1.619529347249483</v>
       </c>
       <c r="CU83" t="n">
         <v>6</v>
@@ -42924,10 +42924,10 @@
         <v>5.7</v>
       </c>
       <c r="CX83" t="n">
-        <v>-41.74354804935854</v>
+        <v>-41.7435480605472</v>
       </c>
       <c r="CY83" t="n">
-        <v>-17.47782770951986</v>
+        <v>-17.47782772562181</v>
       </c>
       <c r="CZ83" t="inlineStr">
         <is>
@@ -43236,10 +43236,10 @@
         <v>5.269999980926514</v>
       </c>
       <c r="CJ84" t="n">
-        <v>3.116563124188505</v>
+        <v>3.116563124987168</v>
       </c>
       <c r="CK84" t="n">
-        <v>4.537715908818464</v>
+        <v>4.537715909981317</v>
       </c>
       <c r="CL84" t="n">
         <v>4.409332244701186</v>
@@ -43588,10 +43588,10 @@
         <v>18.8700008392334</v>
       </c>
       <c r="CJ85" t="n">
-        <v>4.583569630183356</v>
+        <v>4.583569623365652</v>
       </c>
       <c r="CK85" t="n">
-        <v>8.502521663990125</v>
+        <v>8.502521651343285</v>
       </c>
       <c r="CL85" t="n">
         <v>32.85512629695696</v>
@@ -43600,13 +43600,13 @@
         <v>35.40227792012859</v>
       </c>
       <c r="CN85" t="n">
-        <v>28.64957925494921</v>
+        <v>28.64957925290605</v>
       </c>
       <c r="CO85" t="n">
-        <v>11.31302954733574</v>
+        <v>11.31302954777865</v>
       </c>
       <c r="CP85" t="n">
-        <v>19.33215014543062</v>
+        <v>19.33215015203016</v>
       </c>
       <c r="CQ85" t="n">
         <v>44.34329506457097</v>
@@ -44638,10 +44638,10 @@
         <v>23.96999931335449</v>
       </c>
       <c r="CJ88" t="n">
-        <v>12.07935626997116</v>
+        <v>12.07935627230632</v>
       </c>
       <c r="CK88" t="n">
-        <v>22.4072058807965</v>
+        <v>22.40720588512822</v>
       </c>
       <c r="CL88" t="n">
         <v>15.09517542309634</v>
@@ -44662,13 +44662,13 @@
         <v>23.16277622804454</v>
       </c>
       <c r="CR88" t="n">
-        <v>19.87730239547477</v>
+        <v>19.87730239630813</v>
       </c>
       <c r="CS88" t="n">
-        <v>18.75119065194642</v>
+        <v>18.75119065411228</v>
       </c>
       <c r="CT88" t="n">
-        <v>16.87607158675178</v>
+        <v>16.87607158870106</v>
       </c>
       <c r="CU88" t="n">
         <v>8</v>
@@ -44680,10 +44680,10 @@
         <v>2.9</v>
       </c>
       <c r="CX88" t="n">
-        <v>-29.59502682442901</v>
+        <v>-29.59502681629687</v>
       </c>
       <c r="CY88" t="n">
-        <v>-17.07424712189934</v>
+        <v>-17.07424711842267</v>
       </c>
       <c r="CZ88" t="inlineStr">
         <is>
@@ -44992,10 +44992,10 @@
         <v>14.03999996185303</v>
       </c>
       <c r="CJ89" t="n">
-        <v>6.060896433307069</v>
+        <v>6.060896413321658</v>
       </c>
       <c r="CK89" t="n">
-        <v>8.824665206895093</v>
+        <v>8.824665177796335</v>
       </c>
       <c r="CL89" t="n">
         <v>3.751695776034725</v>
@@ -45336,10 +45336,10 @@
         <v>7.210000038146973</v>
       </c>
       <c r="CJ90" t="n">
-        <v>3.000514734438178</v>
+        <v>3.000514733897427</v>
       </c>
       <c r="CK90" t="n">
-        <v>5.565954832382821</v>
+        <v>5.565954831379726</v>
       </c>
       <c r="CL90" t="n">
         <v>14.71995385291947</v>
@@ -45348,17 +45348,17 @@
         <v>15.82114567812849</v>
       </c>
       <c r="CN90" t="n">
-        <v>14.12742075885521</v>
+        <v>14.12742075852753</v>
       </c>
       <c r="CO90" t="n">
-        <v>15.4990939568486</v>
+        <v>15.49909395695808</v>
       </c>
       <c r="CP90" t="n">
-        <v>7.779395119124497</v>
+        <v>7.779395119651752</v>
       </c>
       <c r="CQ90" t="inlineStr"/>
       <c r="CR90" t="n">
-        <v>13.58940187317525</v>
+        <v>13.58940187323707</v>
       </c>
       <c r="CS90" t="n">
         <v>14.71995385291947</v>
@@ -45379,7 +45379,7 @@
         <v>83.74422187981506</v>
       </c>
       <c r="CY90" t="n">
-        <v>88.47991402601765</v>
+        <v>88.47991402687497</v>
       </c>
       <c r="CZ90" t="inlineStr">
         <is>
@@ -45674,10 +45674,10 @@
         <v>55.22999954223633</v>
       </c>
       <c r="CJ91" t="n">
-        <v>11.595475518545</v>
+        <v>11.59547553360199</v>
       </c>
       <c r="CK91" t="n">
-        <v>16.88301235500153</v>
+        <v>16.8830123769245</v>
       </c>
       <c r="CL91" t="inlineStr"/>
       <c r="CM91" t="inlineStr"/>
@@ -45688,13 +45688,13 @@
       <c r="CP91" t="inlineStr"/>
       <c r="CQ91" t="inlineStr"/>
       <c r="CR91" t="n">
-        <v>18.26872929118218</v>
+        <v>18.26872930350883</v>
       </c>
       <c r="CS91" t="n">
-        <v>16.88301235500153</v>
+        <v>16.8830123769245</v>
       </c>
       <c r="CT91" t="n">
-        <v>15.19471111950137</v>
+        <v>15.19471113923205</v>
       </c>
       <c r="CU91" t="n">
         <v>3</v>
@@ -45706,10 +45706,10 @@
         <v>2.3</v>
       </c>
       <c r="CX91" t="n">
-        <v>-72.48830120325923</v>
+        <v>-72.48830116753466</v>
       </c>
       <c r="CY91" t="n">
-        <v>-66.92245257541342</v>
+        <v>-66.92245255309464</v>
       </c>
       <c r="CZ91" t="inlineStr">
         <is>
@@ -46034,10 +46034,10 @@
         <v>3.660000085830688</v>
       </c>
       <c r="CJ92" t="n">
-        <v>33.40407250081697</v>
+        <v>33.4040723954788</v>
       </c>
       <c r="CK92" t="n">
-        <v>61.96455448901548</v>
+        <v>61.96455429361317</v>
       </c>
       <c r="CL92" t="n">
         <v>4.712828098858758</v>
@@ -46378,10 +46378,10 @@
         <v>7.739999771118164</v>
       </c>
       <c r="CJ93" t="n">
-        <v>4.982339145295868</v>
+        <v>4.98233914908061</v>
       </c>
       <c r="CK93" t="n">
-        <v>7.254285795550786</v>
+        <v>7.254285801061369</v>
       </c>
       <c r="CL93" t="n">
         <v>5.854254372336648</v>
@@ -46400,13 +46400,13 @@
         <v>7.739999771118164</v>
       </c>
       <c r="CR93" t="n">
-        <v>6.60602518954698</v>
+        <v>6.606025191096201</v>
       </c>
       <c r="CS93" t="n">
-        <v>6.554270083943717</v>
+        <v>6.554270086699008</v>
       </c>
       <c r="CT93" t="n">
-        <v>5.898843075549345</v>
+        <v>5.898843078029107</v>
       </c>
       <c r="CU93" t="n">
         <v>6</v>
@@ -46418,10 +46418,10 @@
         <v>5.9</v>
       </c>
       <c r="CX93" t="n">
-        <v>-23.78755490974434</v>
+        <v>-23.78755487770606</v>
       </c>
       <c r="CY93" t="n">
-        <v>-14.65083482046878</v>
+        <v>-14.650834800453</v>
       </c>
       <c r="CZ93" t="inlineStr">
         <is>
@@ -46732,10 +46732,10 @@
         <v>35.06000137329102</v>
       </c>
       <c r="CJ94" t="n">
-        <v>8.680155234935771</v>
+        <v>8.680155229124667</v>
       </c>
       <c r="CK94" t="n">
-        <v>16.10168796080586</v>
+        <v>16.10168795002626</v>
       </c>
       <c r="CL94" t="n">
         <v>40.64260876606351</v>
@@ -46744,19 +46744,19 @@
         <v>40.99197343130513</v>
       </c>
       <c r="CN94" t="n">
-        <v>34.02445210621705</v>
+        <v>34.02445210937452</v>
       </c>
       <c r="CO94" t="n">
-        <v>50.38380822080278</v>
+        <v>50.38380822237097</v>
       </c>
       <c r="CP94" t="n">
-        <v>22.89816533601257</v>
+        <v>22.89816534247127</v>
       </c>
       <c r="CQ94" t="n">
         <v>54.19026455668205</v>
       </c>
       <c r="CR94" t="n">
-        <v>37.03328005398414</v>
+        <v>37.03328005404195</v>
       </c>
       <c r="CS94" t="n">
         <v>40.64260876606351</v>
@@ -46777,7 +46777,7 @@
         <v>4.330708661417315</v>
       </c>
       <c r="CY94" t="n">
-        <v>5.628290369082478</v>
+        <v>5.628290369247368</v>
       </c>
       <c r="CZ94" t="inlineStr">
         <is>
@@ -47086,10 +47086,10 @@
         <v>79.11000061035156</v>
       </c>
       <c r="CJ95" t="n">
-        <v>59.14580346951593</v>
+        <v>59.14580355445189</v>
       </c>
       <c r="CK95" t="n">
-        <v>86.11628985161521</v>
+        <v>86.11628997528196</v>
       </c>
       <c r="CL95" t="n">
         <v>24.45731291164257</v>
@@ -47420,35 +47420,35 @@
         <v>19.96999931335449</v>
       </c>
       <c r="CJ96" t="n">
-        <v>11.90594417548597</v>
+        <v>11.90594419427869</v>
       </c>
       <c r="CK96" t="n">
-        <v>15.10171756820564</v>
+        <v>15.10171757961232</v>
       </c>
       <c r="CL96" t="n">
-        <v>22.67303324664305</v>
+        <v>22.67303322798067</v>
       </c>
       <c r="CM96" t="n">
         <v>41.91581127865282</v>
       </c>
       <c r="CN96" t="n">
-        <v>27.56465658095377</v>
+        <v>27.56465659290192</v>
       </c>
       <c r="CO96" t="n">
-        <v>15.61470914480003</v>
+        <v>15.61470914352245</v>
       </c>
       <c r="CP96" t="n">
-        <v>10.88226007555035</v>
+        <v>10.8822600623368</v>
       </c>
       <c r="CQ96" t="inlineStr"/>
       <c r="CR96" t="n">
-        <v>16.32385103378367</v>
+        <v>16.32385103634853</v>
       </c>
       <c r="CS96" t="n">
-        <v>15.35821335650283</v>
+        <v>15.35821336156738</v>
       </c>
       <c r="CT96" t="n">
-        <v>13.82239202085255</v>
+        <v>13.82239202541064</v>
       </c>
       <c r="CU96" t="n">
         <v>4</v>
@@ -47460,10 +47460,10 @@
         <v>1.9</v>
       </c>
       <c r="CX96" t="n">
-        <v>-30.78421384016206</v>
+        <v>-30.78421381733735</v>
       </c>
       <c r="CY96" t="n">
-        <v>-18.25812921852501</v>
+        <v>-18.25812920568144</v>
       </c>
       <c r="CZ96" t="inlineStr">
         <is>
@@ -47786,10 +47786,10 @@
         <v>19.39999961853027</v>
       </c>
       <c r="CJ97" t="n">
-        <v>2.002220648160565</v>
+        <v>2.00222064760638</v>
       </c>
       <c r="CK97" t="n">
-        <v>3.714119302337847</v>
+        <v>3.714119301309835</v>
       </c>
       <c r="CL97" t="n">
         <v>10.17214067849332</v>
@@ -47798,19 +47798,19 @@
         <v>8.489143658487551</v>
       </c>
       <c r="CN97" t="n">
-        <v>10.08225774604474</v>
+        <v>10.08225774716607</v>
       </c>
       <c r="CO97" t="n">
-        <v>7.542853166735031</v>
+        <v>7.542853166860683</v>
       </c>
       <c r="CP97" t="n">
-        <v>7.691046838187847</v>
+        <v>7.691046839085669</v>
       </c>
       <c r="CQ97" t="n">
         <v>13.63549921457183</v>
       </c>
       <c r="CR97" t="n">
-        <v>8.761008657836879</v>
+        <v>8.761008657996422</v>
       </c>
       <c r="CS97" t="n">
         <v>8.489143658487551</v>
@@ -47831,7 +47831,7 @@
         <v>-60.61737400581654</v>
       </c>
       <c r="CY97" t="n">
-        <v>-54.84016066954642</v>
+        <v>-54.84016066872404</v>
       </c>
       <c r="CZ97" t="inlineStr">
         <is>
@@ -48150,10 +48150,10 @@
         <v>16.01000022888184</v>
       </c>
       <c r="CJ98" t="n">
-        <v>8.061612848788368</v>
+        <v>8.061612863029582</v>
       </c>
       <c r="CK98" t="n">
-        <v>14.95429183450242</v>
+        <v>14.95429186091987</v>
       </c>
       <c r="CL98" t="n">
         <v>10.47567916210787</v>
@@ -48174,7 +48174,7 @@
         <v>10.00660187036776</v>
       </c>
       <c r="CR98" t="n">
-        <v>12.49701770427786</v>
+        <v>12.49701770936019</v>
       </c>
       <c r="CS98" t="n">
         <v>10.24114051623781</v>
@@ -48195,7 +48195,7 @@
         <v>-42.4295669403762</v>
       </c>
       <c r="CY98" t="n">
-        <v>-21.94242644835571</v>
+        <v>-21.94242641661096</v>
       </c>
       <c r="CZ98" t="inlineStr">
         <is>
@@ -48506,10 +48506,10 @@
         <v>7.170000076293945</v>
       </c>
       <c r="CJ99" t="n">
-        <v>3.214416907714287</v>
+        <v>3.2144169042457</v>
       </c>
       <c r="CK99" t="n">
-        <v>5.962743363810002</v>
+        <v>5.962743357375772</v>
       </c>
       <c r="CL99" t="inlineStr"/>
       <c r="CM99" t="inlineStr"/>
@@ -48520,13 +48520,13 @@
         <v>9.809989751681186</v>
       </c>
       <c r="CR99" t="n">
-        <v>6.329050007735159</v>
+        <v>6.32905000443422</v>
       </c>
       <c r="CS99" t="n">
-        <v>5.962743363810002</v>
+        <v>5.962743357375772</v>
       </c>
       <c r="CT99" t="n">
-        <v>5.366469027429003</v>
+        <v>5.366469021638195</v>
       </c>
       <c r="CU99" t="n">
         <v>3</v>
@@ -48538,10 +48538,10 @@
         <v>3.1</v>
       </c>
       <c r="CX99" t="n">
-        <v>-25.15384978624935</v>
+        <v>-25.15384986701375</v>
       </c>
       <c r="CY99" t="n">
-        <v>-11.72873165426045</v>
+        <v>-11.72873170029866</v>
       </c>
       <c r="CZ99" t="inlineStr">
         <is>
@@ -48860,37 +48860,37 @@
         <v>23.05999946594238</v>
       </c>
       <c r="CJ100" t="n">
-        <v>5.050688930984102</v>
+        <v>5.050688894473479</v>
       </c>
       <c r="CK100" t="n">
-        <v>7.175729499404693</v>
+        <v>7.175729491253662</v>
       </c>
       <c r="CL100" t="n">
-        <v>10.62745757954198</v>
+        <v>10.62745764429427</v>
       </c>
       <c r="CM100" t="n">
         <v>14.56873729010693</v>
       </c>
       <c r="CN100" t="n">
-        <v>7.163504679773879</v>
+        <v>7.16350471595643</v>
       </c>
       <c r="CO100" t="n">
-        <v>8.436256190564569</v>
+        <v>8.436256195175325</v>
       </c>
       <c r="CP100" t="n">
-        <v>5.281933263776005</v>
+        <v>5.281933301110308</v>
       </c>
       <c r="CQ100" t="n">
         <v>10.72687534044447</v>
       </c>
       <c r="CR100" t="n">
-        <v>8.628897846824579</v>
+        <v>8.628897859101858</v>
       </c>
       <c r="CS100" t="n">
-        <v>7.805992844984631</v>
+        <v>7.805992843214494</v>
       </c>
       <c r="CT100" t="n">
-        <v>7.025393560486169</v>
+        <v>7.025393558893044</v>
       </c>
       <c r="CU100" t="n">
         <v>8</v>
@@ -48902,10 +48902,10 @@
         <v>2.9</v>
       </c>
       <c r="CX100" t="n">
-        <v>-69.53428567566939</v>
+        <v>-69.534285682578</v>
       </c>
       <c r="CY100" t="n">
-        <v>-62.58066762070523</v>
+        <v>-62.58066756746464</v>
       </c>
       <c r="CZ100" t="inlineStr">
         <is>
@@ -49216,10 +49216,10 @@
         <v>46.40000152587891</v>
       </c>
       <c r="CJ101" t="n">
-        <v>10.15177888789609</v>
+        <v>10.15177888023848</v>
       </c>
       <c r="CK101" t="n">
-        <v>18.83154983704725</v>
+        <v>18.83154982284239</v>
       </c>
       <c r="CL101" t="n">
         <v>86.34831744633361</v>
@@ -49228,13 +49228,13 @@
         <v>76.25640482050953</v>
       </c>
       <c r="CN101" t="n">
-        <v>103.7331108683591</v>
+        <v>103.7331108709268</v>
       </c>
       <c r="CO101" t="n">
-        <v>16.14784584740784</v>
+        <v>16.14784584779482</v>
       </c>
       <c r="CP101" t="n">
-        <v>70.06583760681164</v>
+        <v>70.06583761789007</v>
       </c>
       <c r="CQ101" t="n">
         <v>22.72912505392368</v>
@@ -49574,25 +49574,25 @@
         <v>47.5</v>
       </c>
       <c r="CJ102" t="n">
-        <v>18.25668179951099</v>
+        <v>18.25668175043548</v>
       </c>
       <c r="CK102" t="n">
-        <v>20.19873858122815</v>
+        <v>20.19873855838754</v>
       </c>
       <c r="CL102" t="n">
-        <v>23.86378093170256</v>
+        <v>23.86378096886541</v>
       </c>
       <c r="CM102" t="n">
         <v>51.4328502242105</v>
       </c>
       <c r="CN102" t="n">
-        <v>19.8569420309627</v>
+        <v>19.85694204073761</v>
       </c>
       <c r="CO102" t="n">
-        <v>23.27481926693462</v>
+        <v>23.27481927100594</v>
       </c>
       <c r="CP102" t="n">
-        <v>10.33491120694863</v>
+        <v>10.33491124054768</v>
       </c>
       <c r="CQ102" t="n">
         <v>120.2965411332743</v>
@@ -49928,37 +49928,37 @@
         <v>52.59999847412109</v>
       </c>
       <c r="CJ103" t="n">
-        <v>16.06764460514058</v>
+        <v>16.06764462923644</v>
       </c>
       <c r="CK103" t="n">
-        <v>24.44956361377085</v>
+        <v>24.44956362765567</v>
       </c>
       <c r="CL103" t="n">
-        <v>44.11350739807757</v>
+        <v>44.11350735697461</v>
       </c>
       <c r="CM103" t="n">
         <v>61.25894385652082</v>
       </c>
       <c r="CN103" t="n">
-        <v>35.19545559592213</v>
+        <v>35.19545558868968</v>
       </c>
       <c r="CO103" t="n">
-        <v>26.50711330470835</v>
+        <v>26.50711330262747</v>
       </c>
       <c r="CP103" t="n">
-        <v>22.05510056978911</v>
+        <v>22.05510054888162</v>
       </c>
       <c r="CQ103" t="n">
         <v>21.52547978006953</v>
       </c>
       <c r="CR103" t="n">
-        <v>31.39660109049987</v>
+        <v>31.39660108633198</v>
       </c>
       <c r="CS103" t="n">
-        <v>25.4783384592396</v>
+        <v>25.47833846514157</v>
       </c>
       <c r="CT103" t="n">
-        <v>22.93050461331564</v>
+        <v>22.93050461862741</v>
       </c>
       <c r="CU103" t="n">
         <v>8</v>
@@ -49970,10 +49970,10 @@
         <v>3.8</v>
       </c>
       <c r="CX103" t="n">
-        <v>-56.40588350093333</v>
+        <v>-56.40588349083491</v>
       </c>
       <c r="CY103" t="n">
-        <v>-40.31064258310422</v>
+        <v>-40.31064259102797</v>
       </c>
       <c r="CZ103" t="inlineStr">
         <is>
@@ -50304,10 +50304,10 @@
         <v>11.97000026702881</v>
       </c>
       <c r="CJ104" t="n">
-        <v>2.129633592444588</v>
+        <v>2.129633594072685</v>
       </c>
       <c r="CK104" t="n">
-        <v>3.950470313984711</v>
+        <v>3.95047031700483</v>
       </c>
       <c r="CL104" t="n">
         <v>12.16276867623709</v>
@@ -50316,25 +50316,25 @@
         <v>13.48270925178679</v>
       </c>
       <c r="CN104" t="n">
-        <v>8.763285707986334</v>
+        <v>8.763285707352386</v>
       </c>
       <c r="CO104" t="n">
-        <v>5.737621689244132</v>
+        <v>5.737621689105064</v>
       </c>
       <c r="CP104" t="n">
-        <v>6.523398953552543</v>
+        <v>6.523398952055345</v>
       </c>
       <c r="CQ104" t="n">
         <v>11.97000026702881</v>
       </c>
       <c r="CR104" t="n">
-        <v>8.941464979974345</v>
+        <v>8.941464980081474</v>
       </c>
       <c r="CS104" t="n">
-        <v>8.763285707986334</v>
+        <v>8.763285707352386</v>
       </c>
       <c r="CT104" t="n">
-        <v>7.886957137187701</v>
+        <v>7.886957136617148</v>
       </c>
       <c r="CU104" t="n">
         <v>7</v>
@@ -50346,10 +50346,10 @@
         <v>6.3</v>
       </c>
       <c r="CX104" t="n">
-        <v>-34.11063524441006</v>
+        <v>-34.11063524917659</v>
       </c>
       <c r="CY104" t="n">
-        <v>-25.30104611105581</v>
+        <v>-25.30104611016084</v>
       </c>
       <c r="CZ104" t="inlineStr">
         <is>
@@ -50660,10 +50660,10 @@
         <v>3.029999971389771</v>
       </c>
       <c r="CJ105" t="n">
-        <v>0.6343933975249364</v>
+        <v>0.6343934001269186</v>
       </c>
       <c r="CK105" t="n">
-        <v>1.176799752408757</v>
+        <v>1.176799757235434</v>
       </c>
       <c r="CL105" t="n">
         <v>3.469965395066072</v>
@@ -50672,13 +50672,13 @@
         <v>4.010566432856011</v>
       </c>
       <c r="CN105" t="n">
-        <v>2.423903796138632</v>
+        <v>2.423903795800963</v>
       </c>
       <c r="CO105" t="n">
-        <v>2.635949510627439</v>
+        <v>2.635949510297419</v>
       </c>
       <c r="CP105" t="n">
-        <v>1.740689722574122</v>
+        <v>1.740689720382836</v>
       </c>
       <c r="CQ105" t="n">
         <v>9.095071583324174</v>
@@ -51004,10 +51004,10 @@
         <v>55.18999862670898</v>
       </c>
       <c r="CJ106" t="n">
-        <v>62.46314026979618</v>
+        <v>62.46314028313628</v>
       </c>
       <c r="CK106" t="n">
-        <v>90.94633223282325</v>
+        <v>90.94633225224644</v>
       </c>
       <c r="CL106" t="n">
         <v>24.38300703983744</v>
@@ -52010,10 +52010,10 @@
         <v>97.61000061035156</v>
       </c>
       <c r="CJ109" t="n">
-        <v>4.982479598989772</v>
+        <v>4.982479594055986</v>
       </c>
       <c r="CK109" t="n">
-        <v>9.242499656126029</v>
+        <v>9.242499646973855</v>
       </c>
       <c r="CL109" t="n">
         <v>42.72654470059987</v>
@@ -52022,13 +52022,13 @@
         <v>42.39662181432417</v>
       </c>
       <c r="CN109" t="n">
-        <v>35.18195897675254</v>
+        <v>35.18195898345704</v>
       </c>
       <c r="CO109" t="n">
-        <v>18.14750691019174</v>
+        <v>18.14750691065068</v>
       </c>
       <c r="CP109" t="n">
-        <v>29.28029175662619</v>
+        <v>29.28029176227478</v>
       </c>
       <c r="CQ109" t="n">
         <v>44.08436660991484</v>
@@ -52702,10 +52702,10 @@
         <v>17.03000068664551</v>
       </c>
       <c r="CJ111" t="n">
-        <v>3.19753416429778</v>
+        <v>3.197534148511609</v>
       </c>
       <c r="CK111" t="n">
-        <v>5.931425874772382</v>
+        <v>5.931425845489035</v>
       </c>
       <c r="CL111" t="n">
         <v>14.94354364887768</v>
@@ -52714,23 +52714,23 @@
         <v>15.89715452361429</v>
       </c>
       <c r="CN111" t="n">
-        <v>10.65040731362152</v>
+        <v>10.65040732395905</v>
       </c>
       <c r="CO111" t="n">
-        <v>13.03125309326087</v>
+        <v>13.03125309596235</v>
       </c>
       <c r="CP111" t="n">
-        <v>7.843954306873619</v>
+        <v>7.843954322571387</v>
       </c>
       <c r="CQ111" t="inlineStr"/>
       <c r="CR111" t="n">
-        <v>11.38295646017006</v>
+        <v>11.38295646007897</v>
       </c>
       <c r="CS111" t="n">
-        <v>11.8408302034412</v>
+        <v>11.8408302099607</v>
       </c>
       <c r="CT111" t="n">
-        <v>10.65674718309708</v>
+        <v>10.65674718896463</v>
       </c>
       <c r="CU111" t="n">
         <v>6</v>
@@ -52742,10 +52742,10 @@
         <v>5</v>
       </c>
       <c r="CX111" t="n">
-        <v>-37.42368318602696</v>
+        <v>-37.42368315157275</v>
       </c>
       <c r="CY111" t="n">
-        <v>-33.1593893058602</v>
+        <v>-33.15938930639511</v>
       </c>
       <c r="CZ111" t="inlineStr">
         <is>
@@ -53056,25 +53056,25 @@
         <v>14.78999996185303</v>
       </c>
       <c r="CJ112" t="n">
-        <v>3.73405039066887</v>
+        <v>3.734050398308371</v>
       </c>
       <c r="CK112" t="n">
-        <v>4.75096548122225</v>
+        <v>4.750965489671978</v>
       </c>
       <c r="CL112" t="n">
-        <v>14.39113216129318</v>
+        <v>14.39113215744538</v>
       </c>
       <c r="CM112" t="n">
         <v>37.23867291481046</v>
       </c>
       <c r="CN112" t="n">
-        <v>9.87187888903129</v>
+        <v>9.871878896172158</v>
       </c>
       <c r="CO112" t="n">
-        <v>48.8961294912506</v>
+        <v>48.89612948995465</v>
       </c>
       <c r="CP112" t="n">
-        <v>6.917256501148352</v>
+        <v>6.917256498439079</v>
       </c>
       <c r="CQ112" t="n">
         <v>27.46854012923095</v>
@@ -53402,25 +53402,25 @@
         <v>14.8100004196167</v>
       </c>
       <c r="CJ113" t="n">
-        <v>1.386019550120213</v>
+        <v>1.386019550199767</v>
       </c>
       <c r="CK113" t="n">
-        <v>2.562681327460941</v>
+        <v>2.562681327558651</v>
       </c>
       <c r="CL113" t="n">
-        <v>8.677574916854656</v>
+        <v>8.677574916687442</v>
       </c>
       <c r="CM113" t="n">
         <v>10.7066274318662</v>
       </c>
       <c r="CN113" t="n">
-        <v>4.787218444579653</v>
+        <v>4.787218444534618</v>
       </c>
       <c r="CO113" t="n">
-        <v>7.688860390947499</v>
+        <v>7.688860390937072</v>
       </c>
       <c r="CP113" t="n">
-        <v>4.223256306370001</v>
+        <v>4.223256306310635</v>
       </c>
       <c r="CQ113" t="n">
         <v>11.50778129173654</v>
@@ -53748,10 +53748,10 @@
         <v>11.21000003814697</v>
       </c>
       <c r="CJ114" t="n">
-        <v>2.436021021368591</v>
+        <v>2.436021028890328</v>
       </c>
       <c r="CK114" t="n">
-        <v>4.518818994638736</v>
+        <v>4.518819008591558</v>
       </c>
       <c r="CL114" t="n">
         <v>12.15486910846541</v>
@@ -53760,13 +53760,13 @@
         <v>12.67593560098585</v>
       </c>
       <c r="CN114" t="n">
-        <v>9.597028731131367</v>
+        <v>9.597028727312301</v>
       </c>
       <c r="CO114" t="n">
-        <v>0.7922538304855716</v>
+        <v>0.7922538303855846</v>
       </c>
       <c r="CP114" t="n">
-        <v>6.728795260843049</v>
+        <v>6.728795253025859</v>
       </c>
       <c r="CQ114" t="n">
         <v>7.42587936633825</v>
@@ -54094,10 +54094,10 @@
         <v>18.32999992370605</v>
       </c>
       <c r="CJ115" t="n">
-        <v>11.72168818132747</v>
+        <v>11.72168818250049</v>
       </c>
       <c r="CK115" t="n">
-        <v>14.62662829583036</v>
+        <v>14.62662829729409</v>
       </c>
       <c r="CL115" t="inlineStr"/>
       <c r="CM115" t="inlineStr"/>
@@ -54432,25 +54432,25 @@
         <v>8.859999656677246</v>
       </c>
       <c r="CJ116" t="n">
-        <v>2.278494629330833</v>
+        <v>2.278494623157033</v>
       </c>
       <c r="CK116" t="n">
-        <v>2.457217340227376</v>
+        <v>2.45721733528569</v>
       </c>
       <c r="CL116" t="n">
-        <v>3.198208818727315</v>
+        <v>3.198208820961282</v>
       </c>
       <c r="CM116" t="n">
         <v>9.985934437661033</v>
       </c>
       <c r="CN116" t="n">
-        <v>1.868987657814233</v>
+        <v>1.868987657126194</v>
       </c>
       <c r="CO116" t="n">
-        <v>5.90666505812452</v>
+        <v>5.906665058598582</v>
       </c>
       <c r="CP116" t="n">
-        <v>1.344337860029525</v>
+        <v>1.34433786214294</v>
       </c>
       <c r="CQ116" t="n">
         <v>14.36284499478099</v>
@@ -54790,10 +54790,10 @@
         <v>4.820000171661377</v>
       </c>
       <c r="CJ117" t="n">
-        <v>1.482729247113988</v>
+        <v>1.48272923710268</v>
       </c>
       <c r="CK117" t="n">
-        <v>1.545333370881023</v>
+        <v>1.545333360447015</v>
       </c>
       <c r="CL117" t="inlineStr"/>
       <c r="CM117" t="inlineStr"/>
@@ -55126,10 +55126,10 @@
         <v>3.339999914169312</v>
       </c>
       <c r="CJ118" t="n">
-        <v>1.645463647537267</v>
+        <v>1.645463646645273</v>
       </c>
       <c r="CK118" t="n">
-        <v>3.052335066181629</v>
+        <v>3.052335064526982</v>
       </c>
       <c r="CL118" t="n">
         <v>1.157901592431799</v>
@@ -55138,7 +55138,7 @@
         <v>4.60268789222791</v>
       </c>
       <c r="CN118" t="n">
-        <v>1.607705130258211</v>
+        <v>1.607705129931474</v>
       </c>
       <c r="CO118" t="n">
         <v>0.7445919647652398</v>
@@ -55472,10 +55472,10 @@
         <v>6.53000020980835</v>
       </c>
       <c r="CJ119" t="n">
-        <v>1.050039163837102</v>
+        <v>1.050039162149615</v>
       </c>
       <c r="CK119" t="n">
-        <v>1.947822648917824</v>
+        <v>1.947822645787535</v>
       </c>
       <c r="CL119" t="inlineStr"/>
       <c r="CM119" t="inlineStr"/>
@@ -55808,25 +55808,25 @@
         <v>3.680000066757202</v>
       </c>
       <c r="CJ120" t="n">
-        <v>1.260908967182172</v>
+        <v>1.260908966934838</v>
       </c>
       <c r="CK120" t="n">
-        <v>1.270673790768796</v>
+        <v>1.270673790609688</v>
       </c>
       <c r="CL120" t="n">
-        <v>1.29785784028776</v>
+        <v>1.29785784037983</v>
       </c>
       <c r="CM120" t="n">
         <v>4.028317282462615</v>
       </c>
       <c r="CN120" t="n">
-        <v>0.8819378175442726</v>
+        <v>0.8819378175307835</v>
       </c>
       <c r="CO120" t="n">
-        <v>2.295529039487124</v>
+        <v>2.295529039506988</v>
       </c>
       <c r="CP120" t="n">
-        <v>0.492374554746859</v>
+        <v>0.492374554845021</v>
       </c>
       <c r="CQ120" t="n">
         <v>5.189162701709523</v>
@@ -56158,10 +56158,10 @@
         <v>5.369999885559082</v>
       </c>
       <c r="CJ121" t="n">
-        <v>5.323748900765144</v>
+        <v>5.323748898285821</v>
       </c>
       <c r="CK121" t="n">
-        <v>7.75137839951405</v>
+        <v>7.751378395904156</v>
       </c>
       <c r="CL121" t="inlineStr"/>
       <c r="CM121" t="inlineStr"/>
@@ -56170,13 +56170,13 @@
       <c r="CP121" t="inlineStr"/>
       <c r="CQ121" t="inlineStr"/>
       <c r="CR121" t="n">
-        <v>6.537563650139598</v>
+        <v>6.537563647094988</v>
       </c>
       <c r="CS121" t="n">
-        <v>6.537563650139598</v>
+        <v>6.537563647094988</v>
       </c>
       <c r="CT121" t="n">
-        <v>5.883807285125638</v>
+        <v>5.883807282385489</v>
       </c>
       <c r="CU121" t="n">
         <v>2</v>
@@ -56188,10 +56188,10 @@
         <v>1.5</v>
       </c>
       <c r="CX121" t="n">
-        <v>9.568108203284664</v>
+        <v>9.568108152257683</v>
       </c>
       <c r="CY121" t="n">
-        <v>21.74234244809408</v>
+        <v>21.74234239139743</v>
       </c>
       <c r="CZ121" t="inlineStr">
         <is>
@@ -56502,10 +56502,10 @@
         <v>5.369999885559082</v>
       </c>
       <c r="CJ122" t="n">
-        <v>5.911211558752878</v>
+        <v>5.911211502510021</v>
       </c>
       <c r="CK122" t="n">
-        <v>10.53904923450904</v>
+        <v>10.53904913423413</v>
       </c>
       <c r="CL122" t="inlineStr"/>
       <c r="CM122" t="inlineStr"/>
@@ -56514,13 +56514,13 @@
       <c r="CP122" t="inlineStr"/>
       <c r="CQ122" t="inlineStr"/>
       <c r="CR122" t="n">
-        <v>8.225130396630961</v>
+        <v>8.225130318372074</v>
       </c>
       <c r="CS122" t="n">
-        <v>8.225130396630961</v>
+        <v>8.225130318372074</v>
       </c>
       <c r="CT122" t="n">
-        <v>7.402617356967865</v>
+        <v>7.402617286534866</v>
       </c>
       <c r="CU122" t="n">
         <v>2</v>
@@ -56532,10 +56532,10 @@
         <v>1.8</v>
       </c>
       <c r="CX122" t="n">
-        <v>37.85135036734108</v>
+        <v>37.85134905573959</v>
       </c>
       <c r="CY122" t="n">
-        <v>53.16816707482342</v>
+        <v>53.16816561748843</v>
       </c>
       <c r="CZ122" t="inlineStr">
         <is>
@@ -56832,10 +56832,10 @@
         <v>22.35000038146973</v>
       </c>
       <c r="CJ123" t="n">
-        <v>38.78271061982778</v>
+        <v>38.78271039068792</v>
       </c>
       <c r="CK123" t="n">
-        <v>71.94192819978053</v>
+        <v>71.94192777472607</v>
       </c>
       <c r="CL123" t="n">
         <v>19.80852876618554</v>
@@ -56854,7 +56854,7 @@
       </c>
       <c r="CQ123" t="inlineStr"/>
       <c r="CR123" t="n">
-        <v>25.97687186935874</v>
+        <v>25.97687183116876</v>
       </c>
       <c r="CS123" t="n">
         <v>23.0354806164258</v>
@@ -56875,7 +56875,7 @@
         <v>-7.239676953330354</v>
       </c>
       <c r="CY123" t="n">
-        <v>16.2276126442308</v>
+        <v>16.22761247335842</v>
       </c>
       <c r="CZ123" t="inlineStr">
         <is>
@@ -57190,25 +57190,25 @@
         <v>9.090000152587891</v>
       </c>
       <c r="CJ124" t="n">
-        <v>3.513201112935806</v>
+        <v>3.513201119059634</v>
       </c>
       <c r="CK124" t="n">
-        <v>3.627571357824406</v>
+        <v>3.627571363176227</v>
       </c>
       <c r="CL124" t="n">
-        <v>4.393334529074348</v>
+        <v>4.393334527897931</v>
       </c>
       <c r="CM124" t="n">
         <v>18.92946868244077</v>
       </c>
       <c r="CN124" t="n">
-        <v>3.454654098869899</v>
+        <v>3.454654102576232</v>
       </c>
       <c r="CO124" t="n">
-        <v>7.742523562363575</v>
+        <v>7.742523562116036</v>
       </c>
       <c r="CP124" t="n">
-        <v>1.736838692296091</v>
+        <v>1.736838691094351</v>
       </c>
       <c r="CQ124" t="n">
         <v>21.77146113239846</v>
@@ -57536,10 +57536,10 @@
         <v>11.25</v>
       </c>
       <c r="CJ125" t="n">
-        <v>0.7656099595307407</v>
+        <v>0.7656099601700878</v>
       </c>
       <c r="CK125" t="n">
-        <v>1.420206474929524</v>
+        <v>1.420206476115513</v>
       </c>
       <c r="CL125" t="n">
         <v>15.28846153846153</v>
@@ -57548,13 +57548,13 @@
         <v>15.93648555693364</v>
       </c>
       <c r="CN125" t="n">
-        <v>13.40806790964709</v>
+        <v>13.4080679095125</v>
       </c>
       <c r="CO125" t="n">
-        <v>1.648078624699698</v>
+        <v>1.648078624686113</v>
       </c>
       <c r="CP125" t="n">
-        <v>10.81933391672918</v>
+        <v>10.81933391606753</v>
       </c>
       <c r="CQ125" t="inlineStr"/>
       <c r="CR125" t="inlineStr"/>
@@ -58214,25 +58214,25 @@
         <v>18.46054267883301</v>
       </c>
       <c r="CJ127" t="n">
-        <v>0.5760472916087859</v>
+        <v>0.5760472932911865</v>
       </c>
       <c r="CK127" t="n">
-        <v>0.7744861386649863</v>
+        <v>0.7744861407733471</v>
       </c>
       <c r="CL127" t="n">
-        <v>4.57982377230311</v>
+        <v>4.57982377139482</v>
       </c>
       <c r="CM127" t="n">
         <v>11.45343257282958</v>
       </c>
       <c r="CN127" t="n">
-        <v>1.757660189885675</v>
+        <v>1.757660189573192</v>
       </c>
       <c r="CO127" t="n">
-        <v>0.6742367133690663</v>
+        <v>0.6742367133564557</v>
       </c>
       <c r="CP127" t="n">
-        <v>2.24784791347073</v>
+        <v>2.247847912891849</v>
       </c>
       <c r="CQ127" t="n">
         <v>18.46054267883301</v>
@@ -58560,10 +58560,10 @@
         <v>5.239999771118164</v>
       </c>
       <c r="CJ128" t="n">
-        <v>1.294299778429281</v>
+        <v>1.294299770481585</v>
       </c>
       <c r="CK128" t="n">
-        <v>2.166187174625732</v>
+        <v>2.16618716132418</v>
       </c>
       <c r="CL128" t="inlineStr"/>
       <c r="CM128" t="inlineStr"/>
@@ -58574,13 +58574,13 @@
         <v>6.020931258896678</v>
       </c>
       <c r="CR128" t="n">
-        <v>1.730243476527507</v>
+        <v>1.730243465902883</v>
       </c>
       <c r="CS128" t="n">
-        <v>1.730243476527507</v>
+        <v>1.730243465902883</v>
       </c>
       <c r="CT128" t="n">
-        <v>1.557219128874756</v>
+        <v>1.557219119312594</v>
       </c>
       <c r="CU128" t="n">
         <v>2</v>
@@ -58592,10 +58592,10 @@
         <v>4.7</v>
       </c>
       <c r="CX128" t="n">
-        <v>-70.28207639515868</v>
+        <v>-70.2820765776427</v>
       </c>
       <c r="CY128" t="n">
-        <v>-66.98008488350965</v>
+        <v>-66.98008508626965</v>
       </c>
       <c r="CZ128" t="inlineStr">
         <is>
@@ -59248,37 +59248,37 @@
         <v>17.54999923706055</v>
       </c>
       <c r="CJ130" t="n">
-        <v>2.114176577072921</v>
+        <v>2.114176575312376</v>
       </c>
       <c r="CK130" t="n">
-        <v>3.730125101339508</v>
+        <v>3.730125099653793</v>
       </c>
       <c r="CL130" t="n">
-        <v>9.632950375549862</v>
+        <v>9.632950379218226</v>
       </c>
       <c r="CM130" t="n">
         <v>11.96027571768681</v>
       </c>
       <c r="CN130" t="n">
-        <v>5.58425064532182</v>
+        <v>5.584250646508504</v>
       </c>
       <c r="CO130" t="n">
-        <v>5.535381010910674</v>
+        <v>5.535381011065644</v>
       </c>
       <c r="CP130" t="n">
-        <v>4.741756133513761</v>
+        <v>4.741756134934453</v>
       </c>
       <c r="CQ130" t="n">
         <v>15.78993633088096</v>
       </c>
       <c r="CR130" t="n">
-        <v>6.86412316405374</v>
+        <v>6.864123164844572</v>
       </c>
       <c r="CS130" t="n">
-        <v>5.559815828116247</v>
+        <v>5.559815828787074</v>
       </c>
       <c r="CT130" t="n">
-        <v>5.003834245304622</v>
+        <v>5.003834245908367</v>
       </c>
       <c r="CU130" t="n">
         <v>6</v>
@@ -59290,10 +59290,10 @@
         <v>7.5</v>
       </c>
       <c r="CX130" t="n">
-        <v>-71.48812271890039</v>
+        <v>-71.48812271546024</v>
       </c>
       <c r="CY130" t="n">
-        <v>-60.88818539912704</v>
+        <v>-60.88818539462088</v>
       </c>
       <c r="CZ130" t="inlineStr">
         <is>
@@ -59596,10 +59596,10 @@
         <v>4.329999923706055</v>
       </c>
       <c r="CJ131" t="n">
-        <v>0.9106060409813845</v>
+        <v>0.9106060404203472</v>
       </c>
       <c r="CK131" t="n">
-        <v>1.689174206020468</v>
+        <v>1.689174204979744</v>
       </c>
       <c r="CL131" t="inlineStr"/>
       <c r="CM131" t="inlineStr"/>
@@ -59608,13 +59608,13 @@
       <c r="CP131" t="inlineStr"/>
       <c r="CQ131" t="inlineStr"/>
       <c r="CR131" t="n">
-        <v>1.299890123500926</v>
+        <v>1.299890122700046</v>
       </c>
       <c r="CS131" t="n">
-        <v>1.299890123500926</v>
+        <v>1.299890122700046</v>
       </c>
       <c r="CT131" t="n">
-        <v>1.169901111150834</v>
+        <v>1.169901110430041</v>
       </c>
       <c r="CU131" t="n">
         <v>2</v>
@@ -59626,10 +59626,10 @@
         <v>1.9</v>
       </c>
       <c r="CX131" t="n">
-        <v>-72.98149811167865</v>
+        <v>-72.98149812832513</v>
       </c>
       <c r="CY131" t="n">
-        <v>-69.9794423463096</v>
+        <v>-69.97944236480569</v>
       </c>
       <c r="CZ131" t="inlineStr">
         <is>
@@ -59942,10 +59942,10 @@
         <v>1.179999947547913</v>
       </c>
       <c r="CJ132" t="n">
-        <v>0.3468781100550173</v>
+        <v>0.3468781107904809</v>
       </c>
       <c r="CK132" t="n">
-        <v>0.6434588941520571</v>
+        <v>0.6434588955163419</v>
       </c>
       <c r="CL132" t="inlineStr"/>
       <c r="CM132" t="inlineStr"/>
@@ -59954,13 +59954,13 @@
       <c r="CP132" t="inlineStr"/>
       <c r="CQ132" t="inlineStr"/>
       <c r="CR132" t="n">
-        <v>0.4951685021035372</v>
+        <v>0.4951685031534114</v>
       </c>
       <c r="CS132" t="n">
-        <v>0.4951685021035372</v>
+        <v>0.4951685031534114</v>
       </c>
       <c r="CT132" t="n">
-        <v>0.4456516518931835</v>
+        <v>0.4456516528380703</v>
       </c>
       <c r="CU132" t="n">
         <v>2</v>
@@ -59972,10 +59972,10 @@
         <v>1.9</v>
       </c>
       <c r="CX132" t="n">
-        <v>-62.23290917772788</v>
+        <v>-62.23290909765274</v>
       </c>
       <c r="CY132" t="n">
-        <v>-58.03656575303098</v>
+        <v>-58.03656566405859</v>
       </c>
       <c r="CZ132" t="inlineStr">
         <is>
@@ -60284,10 +60284,10 @@
         <v>5.46999979019165</v>
       </c>
       <c r="CJ133" t="n">
-        <v>1.043475834410068</v>
+        <v>1.043475834901575</v>
       </c>
       <c r="CK133" t="n">
-        <v>1.935647672830676</v>
+        <v>1.935647673742422</v>
       </c>
       <c r="CL133" t="inlineStr"/>
       <c r="CM133" t="inlineStr"/>
@@ -60298,13 +60298,13 @@
         <v>3.086391414577443</v>
       </c>
       <c r="CR133" t="n">
-        <v>2.021838307272729</v>
+        <v>2.02183830774048</v>
       </c>
       <c r="CS133" t="n">
-        <v>1.935647672830676</v>
+        <v>1.935647673742422</v>
       </c>
       <c r="CT133" t="n">
-        <v>1.742082905547608</v>
+        <v>1.742082906368179</v>
       </c>
       <c r="CU133" t="n">
         <v>3</v>
@@ -60316,10 +60316,10 @@
         <v>3</v>
       </c>
       <c r="CX133" t="n">
-        <v>-68.15204803716142</v>
+        <v>-68.15204802216012</v>
       </c>
       <c r="CY133" t="n">
-        <v>-63.03768949135754</v>
+        <v>-63.03768948280635</v>
       </c>
       <c r="CZ133" t="inlineStr">
         <is>
@@ -60970,10 +60970,10 @@
         <v>36.70999908447266</v>
       </c>
       <c r="CJ135" t="n">
-        <v>8.268344974597303</v>
+        <v>8.268344951263142</v>
       </c>
       <c r="CK135" t="n">
-        <v>12.03871028301367</v>
+        <v>12.03871024903914</v>
       </c>
       <c r="CL135" t="n">
         <v>7.906067311627989</v>
@@ -61314,25 +61314,25 @@
         <v>4.920000076293945</v>
       </c>
       <c r="CJ136" t="n">
-        <v>1.5276379239492</v>
+        <v>1.527637932395726</v>
       </c>
       <c r="CK136" t="n">
-        <v>1.686462928178328</v>
+        <v>1.686462935439307</v>
       </c>
       <c r="CL136" t="n">
-        <v>2.469546775203932</v>
+        <v>2.469546772181964</v>
       </c>
       <c r="CM136" t="n">
         <v>7.731331217553538</v>
       </c>
       <c r="CN136" t="n">
-        <v>1.727800683676478</v>
+        <v>1.727800686840143</v>
       </c>
       <c r="CO136" t="n">
-        <v>1.781870301602292</v>
+        <v>1.781870301356896</v>
       </c>
       <c r="CP136" t="n">
-        <v>1.066963715284887</v>
+        <v>1.066963712542131</v>
       </c>
       <c r="CQ136" t="n">
         <v>0.3081571864153818</v>
@@ -61658,10 +61658,10 @@
         <v>2.220000028610229</v>
       </c>
       <c r="CJ137" t="n">
-        <v>0.623261018319346</v>
+        <v>0.6232610167747747</v>
       </c>
       <c r="CK137" t="n">
-        <v>0.9074680426729679</v>
+        <v>0.9074680404240721</v>
       </c>
       <c r="CL137" t="n">
         <v>0.3656057054243292</v>
@@ -61724,7 +61724,7 @@
         <v>8.292686841375918</v>
       </c>
       <c r="DL137" t="n">
-        <v>-47.8191363881519</v>
+        <v>-47.81913051232355</v>
       </c>
       <c r="DM137" t="b">
         <v>0</v>
@@ -62316,10 +62316,10 @@
         <v>6.869999885559082</v>
       </c>
       <c r="CJ139" t="n">
-        <v>1.885299353493193</v>
+        <v>1.885299352181143</v>
       </c>
       <c r="CK139" t="n">
-        <v>2.74499585868609</v>
+        <v>2.744995856775744</v>
       </c>
       <c r="CL139" t="n">
         <v>1.690276763894357</v>
@@ -63304,25 +63304,25 @@
         <v>4.840000152587891</v>
       </c>
       <c r="CJ142" t="n">
-        <v>0.8111693281433602</v>
+        <v>0.8111693300150393</v>
       </c>
       <c r="CK142" t="n">
-        <v>0.8137713589376933</v>
+        <v>0.8137713607003161</v>
       </c>
       <c r="CL142" t="n">
-        <v>0.8563537349717655</v>
+        <v>0.8563537348506844</v>
       </c>
       <c r="CM142" t="n">
         <v>6.37726014905843</v>
       </c>
       <c r="CN142" t="n">
-        <v>0.2850987640246648</v>
+        <v>0.2850987644646573</v>
       </c>
       <c r="CO142" t="n">
-        <v>0.4553788358692876</v>
+        <v>0.4553788358614025</v>
       </c>
       <c r="CP142" t="n">
-        <v>0.322203075798793</v>
+        <v>0.3222030756686739</v>
       </c>
       <c r="CQ142" t="inlineStr"/>
       <c r="CR142" t="inlineStr"/>
@@ -63650,10 +63650,10 @@
         <v>18.76000022888184</v>
       </c>
       <c r="CJ143" t="n">
-        <v>28.4898616802575</v>
+        <v>28.489861771673</v>
       </c>
       <c r="CK143" t="n">
-        <v>38.11310384781115</v>
+        <v>38.11310397010477</v>
       </c>
       <c r="CL143" t="n">
         <v>2.597626784658967</v>
@@ -63662,7 +63662,7 @@
         <v>7.205629833517744</v>
       </c>
       <c r="CN143" t="n">
-        <v>6.649616928793319</v>
+        <v>6.649616947338703</v>
       </c>
       <c r="CO143" t="n">
         <v>3.046690502845772</v>
@@ -63996,10 +63996,10 @@
         <v>3.710000038146973</v>
       </c>
       <c r="CJ144" t="n">
-        <v>0.6711165068656856</v>
+        <v>0.6711165051703604</v>
       </c>
       <c r="CK144" t="n">
-        <v>1.244921120235847</v>
+        <v>1.244921117091018</v>
       </c>
       <c r="CL144" t="inlineStr"/>
       <c r="CM144" t="inlineStr"/>
@@ -64010,13 +64010,13 @@
         <v>3.383752809074293</v>
       </c>
       <c r="CR144" t="n">
-        <v>0.9580188135507661</v>
+        <v>0.9580188111306893</v>
       </c>
       <c r="CS144" t="n">
-        <v>0.9580188135507661</v>
+        <v>0.9580188111306893</v>
       </c>
       <c r="CT144" t="n">
-        <v>0.8622169321956895</v>
+        <v>0.8622169300176205</v>
       </c>
       <c r="CU144" t="n">
         <v>2</v>
@@ -64028,10 +64028,10 @@
         <v>5</v>
       </c>
       <c r="CX144" t="n">
-        <v>-76.75965166225876</v>
+        <v>-76.75965172096681</v>
       </c>
       <c r="CY144" t="n">
-        <v>-74.17739073584306</v>
+        <v>-74.17739080107424</v>
       </c>
       <c r="CZ144" t="inlineStr">
         <is>
@@ -64340,10 +64340,10 @@
         <v>18.79000091552734</v>
       </c>
       <c r="CJ145" t="n">
-        <v>9.52516124920559</v>
+        <v>9.525161240857251</v>
       </c>
       <c r="CK145" t="n">
-        <v>13.86863477884334</v>
+        <v>13.86863476668816</v>
       </c>
       <c r="CL145" t="n">
         <v>4.657197557709351</v>
@@ -65372,10 +65372,10 @@
         <v>10.85999965667725</v>
       </c>
       <c r="CJ148" t="n">
-        <v>5.802515941910595</v>
+        <v>5.80251593549784</v>
       </c>
       <c r="CK148" t="n">
-        <v>10.62075325367487</v>
+        <v>10.62075324193716</v>
       </c>
       <c r="CL148" t="inlineStr"/>
       <c r="CM148" t="inlineStr"/>
@@ -65386,13 +65386,13 @@
         <v>3.332701500657688</v>
       </c>
       <c r="CR148" t="n">
-        <v>6.585323565414385</v>
+        <v>6.585323559364228</v>
       </c>
       <c r="CS148" t="n">
-        <v>5.802515941910595</v>
+        <v>5.80251593549784</v>
       </c>
       <c r="CT148" t="n">
-        <v>5.222264347719536</v>
+        <v>5.222264341948056</v>
       </c>
       <c r="CU148" t="n">
         <v>3</v>
@@ -65404,10 +65404,10 @@
         <v>3.2</v>
       </c>
       <c r="CX148" t="n">
-        <v>-51.91284978992942</v>
+        <v>-51.91284984307381</v>
       </c>
       <c r="CY148" t="n">
-        <v>-39.36165954328171</v>
+        <v>-39.36165959899219</v>
       </c>
       <c r="CZ148" t="inlineStr">
         <is>
@@ -66064,10 +66064,10 @@
         <v>15.42000007629395</v>
       </c>
       <c r="CJ150" t="n">
-        <v>3.945356593272785</v>
+        <v>3.94535658871015</v>
       </c>
       <c r="CK150" t="n">
-        <v>5.744439199805174</v>
+        <v>5.744439193161979</v>
       </c>
       <c r="CL150" t="inlineStr"/>
       <c r="CM150" t="inlineStr"/>
@@ -66078,7 +66078,7 @@
         <v>5.488479853420727</v>
       </c>
       <c r="CR150" t="n">
-        <v>5.059425215499562</v>
+        <v>5.059425211764285</v>
       </c>
       <c r="CS150" t="n">
         <v>5.488479853420727</v>
@@ -66099,7 +66099,7 @@
         <v>-67.96607105292668</v>
       </c>
       <c r="CY150" t="n">
-        <v>-67.18920109943637</v>
+        <v>-67.18920112365997</v>
       </c>
       <c r="CZ150" t="inlineStr">
         <is>
